--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370473041144992</v>
+        <v>8.370450796103992</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367769845565084</v>
+        <v>8.367789256385073</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394917116844049</v>
+        <v>8.394878233008219</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410969495375216</v>
+        <v>8.410950252898752</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424191667692529</v>
+        <v>8.424192069635273</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42824003053968</v>
+        <v>8.428257610440159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426832264068111</v>
+        <v>8.426866987364827</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431059603232747</v>
+        <v>8.431115368811188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.427710565686466</v>
+        <v>8.427896960104484</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.437520080111961</v>
+        <v>8.437721040430048</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.44386129660484</v>
+        <v>8.444078290481349</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43701862707932</v>
+        <v>8.43723387806221</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41667951029674</v>
+        <v>8.416907821914688</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.398164445549183</v>
+        <v>8.39846988144156</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.370737056708396</v>
+        <v>8.371005881421549</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.332864109852412</v>
+        <v>8.333151466065752</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.276343331956413</v>
+        <v>8.276738197994955</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.221648501363136</v>
+        <v>8.222058674002371</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.170969020815839</v>
+        <v>8.171190190709677</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.12886104686851</v>
+        <v>8.128997677050711</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133839464501049</v>
+        <v>8.133772898946415</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187907467713565</v>
+        <v>8.18769177503723</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.2236556545745</v>
+        <v>8.223065222376764</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.209455263163164</v>
+        <v>8.20872582458378</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.181368742826338</v>
+        <v>8.18059449186083</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.136100525914296</v>
+        <v>8.135396403425887</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.111350096818235</v>
+        <v>8.110809235592008</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.120280254380077</v>
+        <v>8.119914543809834</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163657844573329</v>
+        <v>8.163734494157334</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19076534852956</v>
+        <v>8.190908840384648</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.169869276775982</v>
+        <v>8.170173554420399</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.190009698565575</v>
+        <v>8.19065898925742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.186000295551725</v>
+        <v>8.187236939877483</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.214743426155602</v>
+        <v>8.216206648221272</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.299303663771594</v>
+        <v>8.301302753661531</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.267417011724477</v>
+        <v>8.268665198289764</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.263872199241057</v>
+        <v>8.265579372524098</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.247682326018197</v>
+        <v>8.249395037451649</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.255466679038328</v>
+        <v>8.257438418758984</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.284780417921015</v>
+        <v>8.287245197270003</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.303244505001876</v>
+        <v>8.305902397125793</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.210141745879238</v>
+        <v>8.212741219337524</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.124587138444438</v>
+        <v>8.126750250294311</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.041047141842453</v>
+        <v>8.042363752866907</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007357317132975</v>
+        <v>8.000357372617831</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.975643427987187</v>
+        <v>7.961889687455564</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.962009547286288</v>
+        <v>7.949250808940388</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.981620314504881</v>
+        <v>7.967266279835044</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.950555747514311</v>
+        <v>7.943881871829221</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.926201135432748</v>
+        <v>7.927744827484402</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.922197973829138</v>
+        <v>7.927240800516808</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.971854832586245</v>
+        <v>7.967663557079284</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.984998249812817</v>
+        <v>7.974763931711021</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.992717210820293</v>
+        <v>7.97585379777988</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.991719696793182</v>
+        <v>7.970564934343697</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.982546141846931</v>
+        <v>7.952826692502291</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.974878570907117</v>
+        <v>7.935133566014287</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.961548941076318</v>
+        <v>7.913576012925938</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,15 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.9183</v>
+        <v>7.889166270231035</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>7.803895029574912</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370450796103992</v>
+        <v>8.370440507232722</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367789256385073</v>
+        <v>8.367798215433947</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394878233008219</v>
+        <v>8.394860278072905</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410950252898752</v>
+        <v>8.410941376022722</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424192069635273</v>
+        <v>8.424192273531094</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428257610440159</v>
+        <v>8.428265755879936</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426866987364827</v>
+        <v>8.426883055433995</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431115368811188</v>
+        <v>8.431141155496267</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.427896960104484</v>
+        <v>8.427983088596502</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.437721040430048</v>
+        <v>8.437813969913316</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444078290481349</v>
+        <v>8.444178638560551</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43723387806221</v>
+        <v>8.437333418175353</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.416907821914688</v>
+        <v>8.417013512986756</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.39846988144156</v>
+        <v>8.398611233213918</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371005881421549</v>
+        <v>8.371130264269285</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333151466065752</v>
+        <v>8.333284643577407</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.276738197994955</v>
+        <v>8.276921326889305</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222058674002371</v>
+        <v>8.222249364672123</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171190190709677</v>
+        <v>8.171292951689674</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.128997677050711</v>
+        <v>8.12906120552671</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133772898946415</v>
+        <v>8.133742847877102</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18769177503723</v>
+        <v>8.187592571497927</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.223065222376764</v>
+        <v>8.222791605958438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.20872582458378</v>
+        <v>8.208387162489171</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.18059449186083</v>
+        <v>8.180234458649338</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.135396403425887</v>
+        <v>8.135068163965101</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.110809235592008</v>
+        <v>8.110555900835131</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.119914543809834</v>
+        <v>8.11974158859724</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163734494157334</v>
+        <v>8.163767421576416</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.190908840384648</v>
+        <v>8.190975137017606</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170173554420399</v>
+        <v>8.170313983474678</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19065898925742</v>
+        <v>8.190961753096879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.187236939877483</v>
+        <v>8.187814329368939</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.216206648221272</v>
+        <v>8.21688961952786</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.301302753661531</v>
+        <v>8.302233820492077</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.268665198289764</v>
+        <v>8.26924173573928</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.265579372524098</v>
+        <v>8.266368543125465</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.249395037451649</v>
+        <v>8.250184736058191</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.257438418758984</v>
+        <v>8.258348040641</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.287245197270003</v>
+        <v>8.288383782338865</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.305902397125793</v>
+        <v>8.307131514835296</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.212741219337524</v>
+        <v>8.213947533854542</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.126750250294311</v>
+        <v>8.127756615553761</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.042363752866907</v>
+        <v>8.042979272125812</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.000357372617831</v>
+        <v>8.000870085804541</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.961889687455564</v>
+        <v>7.962147507566577</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.949250808940388</v>
+        <v>7.943422525864286</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.967266279835044</v>
+        <v>7.958456550232984</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.943881871829221</v>
+        <v>7.936511650670976</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.927744827484402</v>
+        <v>7.919708491766926</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.927240800516808</v>
+        <v>7.918236806596204</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.967663557079284</v>
+        <v>7.953297351676785</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.974763931711021</v>
+        <v>7.957172436745055</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.97585379777988</v>
+        <v>7.953483146049774</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.970564934343697</v>
+        <v>7.942867396381645</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.952826692502291</v>
+        <v>7.916286773140406</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.935133566014287</v>
+        <v>7.889162421868861</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.913576012925938</v>
+        <v>7.854717814215571</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.889166270231035</v>
+        <v>7.80803501332646</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,15 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.803895029574912</v>
+        <v>7.672040655614116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>7.502648394817996</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.958456550232984</v>
+        <v>7.958459095742585</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.936511650670976</v>
+        <v>7.936539065392139</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.919708491766926</v>
+        <v>7.919826048775629</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.918236806596204</v>
+        <v>7.918523031045954</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.953297351676785</v>
+        <v>7.95374972750069</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.957172436745055</v>
+        <v>7.957966530660017</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.953483146049774</v>
+        <v>7.954615257131514</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.942867396381645</v>
+        <v>7.944560407642879</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.916286773140406</v>
+        <v>7.918704156842452</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.889162421868861</v>
+        <v>7.892132223881584</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.854717814215571</v>
+        <v>7.858302510614854</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.80803501332646</v>
+        <v>7.818026035439686</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.672040655614116</v>
+        <v>7.683681637422093</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.502648394817996</v>
+        <v>7.519466520598829</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.958459095742585</v>
+        <v>7.958434853364565</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.936539065392139</v>
+        <v>7.936472983193717</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.919826048775629</v>
+        <v>7.91964007693417</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.918523031045954</v>
+        <v>7.91824614299004</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.95374972750069</v>
+        <v>7.953396206293346</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.957966530660017</v>
+        <v>7.957634714446241</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.954615257131514</v>
+        <v>7.954414603785781</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.944560407642879</v>
+        <v>7.944481393883009</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.918704156842452</v>
+        <v>7.918753827028368</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.892132223881584</v>
+        <v>7.892317020296112</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.858302510614854</v>
+        <v>7.85851324293369</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.818026035439686</v>
+        <v>7.818505997823888</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.683681637422093</v>
+        <v>7.716318497823887</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,15 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.519466520598829</v>
+        <v>7.614130997823887</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>7.472975251396345</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370440507232722</v>
+        <v>8.370430719951509</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367798215433947</v>
+        <v>8.36780672660292</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394860278072905</v>
+        <v>8.394843216016927</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410941376022722</v>
+        <v>8.410932945590893</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424192273531094</v>
+        <v>8.424192478064432</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428265755879936</v>
+        <v>8.428273512615091</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426883055433995</v>
+        <v>8.426898344653477</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431141155496267</v>
+        <v>8.431165681302481</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.427983088596502</v>
+        <v>8.428064968719438</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.437813969913316</v>
+        <v>8.437902357192316</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444178638560551</v>
+        <v>8.444274084313179</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437333418175353</v>
+        <v>8.437428094272573</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417013512986756</v>
+        <v>8.417114104418697</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.398611233213918</v>
+        <v>8.39874573989812</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371130264269285</v>
+        <v>8.37124860853981</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333284643577407</v>
+        <v>8.333411485068062</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.276921326889305</v>
+        <v>8.277095816173352</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222249364672123</v>
+        <v>8.222431329436148</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171292951689674</v>
+        <v>8.171390974686268</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.12906120552671</v>
+        <v>8.129121832794427</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133742847877102</v>
+        <v>8.133714696341741</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187592571497927</v>
+        <v>8.187498536863947</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.222791605958438</v>
+        <v>8.222531025541393</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.208387162489171</v>
+        <v>8.208064269288622</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.180234458649338</v>
+        <v>8.179890858489472</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.135068163965101</v>
+        <v>8.134754428589357</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.110555900835131</v>
+        <v>8.110313057225948</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11974158859724</v>
+        <v>8.119574828647471</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163767421576416</v>
+        <v>8.163797250904697</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.190975137017606</v>
+        <v>8.191038145238213</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170313983474678</v>
+        <v>8.170447369160492</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.190961753096879</v>
+        <v>8.191251179161434</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.187814329368939</v>
+        <v>8.188366743426307</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.21688961952786</v>
+        <v>8.21754292699101</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.302233820492077</v>
+        <v>8.303123265288315</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.26924173573928</v>
+        <v>8.269789697900947</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.266368543125465</v>
+        <v>8.267118960046348</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.250184736058191</v>
+        <v>8.250934445285294</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.258348040641</v>
+        <v>8.259211889108249</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.288383782338865</v>
+        <v>8.289465951838771</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.307131514835296</v>
+        <v>8.308300523522714</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.213947533854542</v>
+        <v>8.215097330693727</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.127756615553761</v>
+        <v>8.128717321853053</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.042979272125812</v>
+        <v>8.043568616219861</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.000870085804541</v>
+        <v>8.001361465633693</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.962147507566577</v>
+        <v>7.962394622250742</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943422525864286</v>
+        <v>7.938425720628841</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.958434853364565</v>
+        <v>7.950867312306791</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.936472983193717</v>
+        <v>7.930542669977836</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.91964007693417</v>
+        <v>7.91485765324984</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.91824614299004</v>
+        <v>7.915247819663612</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.953396206293346</v>
+        <v>7.949270528113561</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.957634714446241</v>
+        <v>7.95476177564082</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.954414603785781</v>
+        <v>7.952563523786328</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.944481393883009</v>
+        <v>7.945106418928843</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.918753827028368</v>
+        <v>7.927460665353703</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.892317020296112</v>
+        <v>7.907798625109494</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.85851324293369</v>
+        <v>7.882292822867259</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.818505997823888</v>
+        <v>7.853085811053561</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.716318497823887</v>
+        <v>7.759797693725575</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.614130997823887</v>
+        <v>7.710509070470909</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,15 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.472975251396345</v>
+        <v>7.668687110639365</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>7.770874610639365</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370430719951509</v>
+        <v>8.370421398460598</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36780672660292</v>
+        <v>8.367814822627201</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394843216016927</v>
+        <v>8.394826981939676</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410932945590893</v>
+        <v>8.410924928816634</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424192478064432</v>
+        <v>8.42419268246422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428273512615091</v>
+        <v>8.428280907798383</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426898344653477</v>
+        <v>8.426912910273851</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431165681302481</v>
+        <v>8.431189036426431</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428064968719438</v>
+        <v>8.42814290679331</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.437902357192316</v>
+        <v>8.437986527057516</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444274084313179</v>
+        <v>8.444364978101882</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437428094272573</v>
+        <v>8.437518254056828</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417114104418697</v>
+        <v>8.417209956007511</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.39874573989812</v>
+        <v>8.398873886089014</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37124860853981</v>
+        <v>8.371361342725558</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333411485068062</v>
+        <v>8.333532431211735</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277095816173352</v>
+        <v>8.277262261266166</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222431329436148</v>
+        <v>8.222605149771663</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171390974686268</v>
+        <v>8.171484578289443</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129121832794427</v>
+        <v>8.129179752245491</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133714696341741</v>
+        <v>8.133688279620714</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187498536863947</v>
+        <v>8.187409281663939</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.222531025541393</v>
+        <v>8.222282575924407</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.208064269288622</v>
+        <v>8.207756077320681</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.179890858489472</v>
+        <v>8.179562603007206</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.134754428589357</v>
+        <v>8.134454271856255</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.110313057225948</v>
+        <v>8.110080088061846</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.119574828647471</v>
+        <v>8.119413976188991</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163797250904697</v>
+        <v>8.16382430065528</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191038145238213</v>
+        <v>8.191098094681456</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170447369160492</v>
+        <v>8.170574217018419</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.191251179161434</v>
+        <v>8.191528109541728</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.188366743426307</v>
+        <v>8.18889574076824</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.21754292699101</v>
+        <v>8.218168430939444</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.303123265288315</v>
+        <v>8.303973788235261</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.269789697900947</v>
+        <v>8.270311149838594</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.267118960046348</v>
+        <v>8.267833393952106</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.250934445285294</v>
+        <v>8.251647098160742</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.259211889108249</v>
+        <v>8.260033301846759</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.289465951838771</v>
+        <v>8.290495753899712</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.308300523522714</v>
+        <v>8.309413689646725</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.215097330693727</v>
+        <v>8.216194449625917</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.128717321853053</v>
+        <v>8.129635361564839</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.043568616219861</v>
+        <v>8.044133375805302</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.001361465633693</v>
+        <v>8.001832781254981</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.962394622250742</v>
+        <v>7.962631674872318</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.938425720628841</v>
+        <v>7.938595337741802</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950867312306791</v>
+        <v>7.940387160303403</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.930542669977836</v>
+        <v>7.919327498388451</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.91485765324984</v>
+        <v>7.903641130123715</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.915247819663612</v>
+        <v>7.899914153059965</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.949270528113561</v>
+        <v>7.927067421795873</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.95476177564082</v>
+        <v>7.926754085394875</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.952563523786328</v>
+        <v>7.917546543373509</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.945106418928843</v>
+        <v>7.903929969320094</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.927460665353703</v>
+        <v>7.881059494263748</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.907798625109494</v>
+        <v>7.851407309731021</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.882292822867259</v>
+        <v>7.816392222467602</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.853085811053561</v>
+        <v>7.771956340316524</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.759797693725575</v>
+        <v>7.643319129442823</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.710509070470909</v>
+        <v>7.540272983322533</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.668687110639365</v>
+        <v>7.478755456986164</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.770874610639365</v>
+        <v>7.52538968495999</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -696,7 +696,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370421398460598</v>
+        <v>8.370412510287291</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -704,7 +704,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367814822627201</v>
+        <v>8.367822533130468</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -712,7 +712,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394826981939676</v>
+        <v>8.394811517074043</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -720,7 +720,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410924928816634</v>
+        <v>8.410917296041232</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -728,7 +728,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42419268246422</v>
+        <v>8.424192886095794</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -736,7 +736,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428280907798383</v>
+        <v>8.428287966113068</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -744,7 +744,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426912910273851</v>
+        <v>8.426926802443838</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -752,7 +752,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431189036426431</v>
+        <v>8.431211302668768</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -760,7 +760,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.42814290679331</v>
+        <v>8.428217180419779</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -768,7 +768,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.437986527057516</v>
+        <v>8.438066774080056</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -776,7 +776,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444364978101882</v>
+        <v>8.444451637707362</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -784,7 +784,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437518254056828</v>
+        <v>8.437604212889578</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -792,7 +792,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417209956007511</v>
+        <v>8.417301394534897</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -800,7 +800,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.398873886089014</v>
+        <v>8.398996111770899</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -808,7 +808,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371361342725558</v>
+        <v>8.371468855788555</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -816,7 +816,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333532431211735</v>
+        <v>8.333647882831011</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -824,7 +824,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277262261266166</v>
+        <v>8.277421204272535</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -832,7 +832,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222605149771663</v>
+        <v>8.222771356991844</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -840,7 +840,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171484578289443</v>
+        <v>8.171574053309289</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -848,7 +848,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129179752245491</v>
+        <v>8.129235140540226</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -856,7 +856,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133688279620714</v>
+        <v>8.133663450839853</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -864,7 +864,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187409281663939</v>
+        <v>8.187324454248493</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -872,7 +872,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.222282575924407</v>
+        <v>8.22204543339102</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -880,7 +880,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.207756077320681</v>
+        <v>8.207461612387085</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -888,7 +888,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.179562603007206</v>
+        <v>8.179248696789276</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -896,7 +896,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.134454271856255</v>
+        <v>8.13416684398433</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -904,7 +904,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.110080088061846</v>
+        <v>8.109856421869161</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -912,7 +912,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.119413976188991</v>
+        <v>8.119258756472462</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -920,7 +920,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16382430065528</v>
+        <v>8.163848851556411</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -928,7 +928,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191098094681456</v>
+        <v>8.191155194879585</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -936,7 +936,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170574217018419</v>
+        <v>8.170694986300209</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -944,7 +944,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.191528109541728</v>
+        <v>8.191793318835526</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -952,7 +952,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.18889574076824</v>
+        <v>8.189402755635754</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -960,7 +960,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.218168430939444</v>
+        <v>8.218767842222945</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -968,7 +968,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.303973788235261</v>
+        <v>8.304787863530771</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -976,7 +976,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.270311149838594</v>
+        <v>8.270807963026391</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -984,7 +984,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.267833393952106</v>
+        <v>8.268514358922328</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -992,7 +992,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.251647098160742</v>
+        <v>8.252325350256886</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1000,7 +1000,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.260033301846759</v>
+        <v>8.260815302541346</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1008,7 +1008,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.290495753899712</v>
+        <v>8.291476862175283</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1016,7 +1016,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.309413689646725</v>
+        <v>8.31047488854322</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1024,7 +1024,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.216194449625917</v>
+        <v>8.217242394027835</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1032,7 +1032,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.129635361564839</v>
+        <v>8.130513475430362</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1040,7 +1040,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.044133375805302</v>
+        <v>8.044675019515257</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1048,7 +1048,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.001832781254981</v>
+        <v>8.00228520642515</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1056,7 +1056,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.962631674872318</v>
+        <v>7.962859259070458</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1064,7 +1064,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.938595337741802</v>
+        <v>7.938757650821078</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1072,7 +1072,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.940387160303403</v>
+        <v>7.940726248870783</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1080,7 +1080,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.919327498388451</v>
+        <v>7.911503172624203</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1088,7 +1088,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.903641130123715</v>
+        <v>7.895463292200029</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1096,7 +1096,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.899914153059965</v>
+        <v>7.891423205073123</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1104,7 +1104,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.927067421795873</v>
+        <v>7.913414926281368</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.926754085394875</v>
+        <v>7.910074168251535</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1120,7 +1120,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.917546543373509</v>
+        <v>7.897643096459525</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1128,7 +1128,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.903929969320094</v>
+        <v>7.881725117799231</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1136,7 +1136,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.881059494263748</v>
+        <v>7.859369323601678</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1144,7 +1144,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.851407309731021</v>
+        <v>7.833356749508265</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1152,7 +1152,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.816392222467602</v>
+        <v>7.802295382718354</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1160,7 +1160,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.771956340316524</v>
+        <v>7.761753244619529</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1168,7 +1168,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.643319129442823</v>
+        <v>7.646826355123711</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.540272983322533</v>
+        <v>7.555428273811292</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1184,7 +1184,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.478755456986164</v>
+        <v>7.494104660875832</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1192,7 +1192,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.52538968495999</v>
+        <v>7.510650021945404</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>44743</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>44778</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>44806</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>44834</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>44869</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>44897</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>44932</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>44960</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>44988</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>45016</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>45051</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>45079</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>45107</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>45142</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>45170</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>45205</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>45233</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>45261</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>45296</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>45324</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>45352</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>45387</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>45415</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>45443</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>45478</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>45506</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>45541</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>45569</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>45597</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>45632</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>45660</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>45688</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>45716</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>45751</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>45779</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>45814</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>45821</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>45828</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>45835</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>45842</v>
       </c>
       <c r="B41">
@@ -692,507 +718,515 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370412510287291</v>
+        <v>8.370404025908286</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367822533130468</v>
+        <v>8.367829884985696</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394811517074043</v>
+        <v>8.394796768079408</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410917296041232</v>
+        <v>8.410910020370208</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424192886095794</v>
+        <v>8.424193088438365</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428287966113068</v>
+        <v>8.428294710047211</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426926802443838</v>
+        <v>8.426940066785567</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431211302668768</v>
+        <v>8.431232554388199</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428217180419779</v>
+        <v>8.428288041766388</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438066774080056</v>
+        <v>8.438143366043713</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444451637707362</v>
+        <v>8.444534352026743</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437604212889578</v>
+        <v>8.437686257462616</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417301394534897</v>
+        <v>8.417388717463359</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.398996111770899</v>
+        <v>8.399112817327065</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371468855788555</v>
+        <v>8.371571501608269</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333647882831011</v>
+        <v>8.333758205292625</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277421204272535</v>
+        <v>8.277573139800793</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222771356991844</v>
+        <v>8.222930437497981</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171574053309289</v>
+        <v>8.171659665721482</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129235140540226</v>
+        <v>8.129288159369347</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133663450839853</v>
+        <v>8.133640078675906</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187324454248493</v>
+        <v>8.187243736343042</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.22204543339102</v>
+        <v>8.221818846789677</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.207461612387085</v>
+        <v>8.207179983834315</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.179248696789276</v>
+        <v>8.178948227788471</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.13416684398433</v>
+        <v>8.133891363443421</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.109856421869161</v>
+        <v>8.109641528606268</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.119258756472462</v>
+        <v>8.119108907765774</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163848851556411</v>
+        <v>8.163871151670312</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191155194879585</v>
+        <v>8.191209637325132</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170694986300209</v>
+        <v>8.17081009504578</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.191793318835526</v>
+        <v>8.192047520545755</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.189402755635754</v>
+        <v>8.189889109673258</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.218767842222945</v>
+        <v>8.219342736598179</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.304787863530771</v>
+        <v>8.305567762257706</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.270807963026391</v>
+        <v>8.271281837437014</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.268514358922328</v>
+        <v>8.269164141330601</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.252325350256886</v>
+        <v>8.252971611472898</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.260815302541346</v>
+        <v>8.261560636655821</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.291476862175283</v>
+        <v>8.292412617760492</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.31047488854322</v>
+        <v>8.311487647881457</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.217242394027835</v>
+        <v>8.218244366514234</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.130513475430362</v>
+        <v>8.131354177976053</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.044675019515257</v>
+        <v>8.045194904916331</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.00228520642515</v>
+        <v>8.002719827913998</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.962859259070458</v>
+        <v>7.963077923390876</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.938757650821078</v>
+        <v>7.93891312334526</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.940726248870783</v>
+        <v>7.941050854402246</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.911503172624203</v>
+        <v>7.911675202947157</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.895463292200029</v>
+        <v>7.885840011455169</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.891423205073123</v>
+        <v>7.880689225005279</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.913414926281368</v>
+        <v>7.899779895636845</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.910074168251535</v>
+        <v>7.891883279330384</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.897643096459525</v>
+        <v>7.875213611620349</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.881725117799231</v>
+        <v>7.855080549073996</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.859369323601678</v>
+        <v>7.829197884375918</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.833356749508265</v>
+        <v>7.800993391857932</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.802295382718354</v>
+        <v>7.768692222802547</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.761753244619529</v>
+        <v>7.722680418686327</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.646826355123711</v>
+        <v>7.607510523311349</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.555428273811292</v>
+        <v>7.513541719568929</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.494104660875832</v>
+        <v>7.440856161441166</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.510650021945404</v>
+        <v>7.474624771295979</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>7.372437271295978</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370404025908286</v>
+        <v>8.370395918422307</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367829884985696</v>
+        <v>8.367836902626943</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394796768079408</v>
+        <v>8.394782686430098</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410910020370208</v>
+        <v>8.410903077359114</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424193088438365</v>
+        <v>8.424193289066382</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428294710047211</v>
+        <v>8.42830116013223</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426940066785567</v>
+        <v>8.426952744893734</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431232554388199</v>
+        <v>8.431252859328373</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428288041766388</v>
+        <v>8.428355720410694</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438143366043713</v>
+        <v>8.438216546919881</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444534352026743</v>
+        <v>8.444613384279752</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437686257462616</v>
+        <v>8.437764648981116</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417388717463359</v>
+        <v>8.417472196147392</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399112817327065</v>
+        <v>8.399224367890209</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371571501608269</v>
+        <v>8.371669602843141</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333758205292625</v>
+        <v>8.333863732335026</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277573139800793</v>
+        <v>8.277718520037546</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.222930437497981</v>
+        <v>8.223082837391129</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171659665721482</v>
+        <v>8.171741659248163</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129288159369347</v>
+        <v>8.129338956998881</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133640078675906</v>
+        <v>8.133618045400874</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187243736343042</v>
+        <v>8.187166839209574</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.221818846789677</v>
+        <v>8.221602129754316</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.207179983834315</v>
+        <v>8.206910375859996</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.178948227788471</v>
+        <v>8.178660358876627</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.133891363443421</v>
+        <v>8.133627110375631</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.109641528606268</v>
+        <v>8.109434916200367</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.119108907765774</v>
+        <v>8.118964181166216</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163871151670312</v>
+        <v>8.16389142073302</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191209637325132</v>
+        <v>8.191261597297629</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17081009504578</v>
+        <v>8.170919924519525</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.192047520545755</v>
+        <v>8.192291372797619</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.189889109673258</v>
+        <v>8.190356022516269</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.219342736598179</v>
+        <v>8.219894567529911</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.305567762257706</v>
+        <v>8.306315572569751</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.271281837437014</v>
+        <v>8.271734320682942</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.269164141330601</v>
+        <v>8.269784824928742</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.252971611472898</v>
+        <v>8.253588073579635</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.261560636655821</v>
+        <v>8.26227180246695</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.292412617760492</v>
+        <v>8.293306065653743</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.311487647881457</v>
+        <v>8.312455185498333</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.218244366514234</v>
+        <v>8.219203300190017</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.131354177976053</v>
+        <v>8.132159779977176</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.045194904916331</v>
+        <v>8.045694288382773</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.002719827913998</v>
+        <v>8.003137653092583</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.963077923390876</v>
+        <v>7.96328817541864</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.93891312334526</v>
+        <v>7.939062180227393</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.941050854402246</v>
+        <v>7.94136188281846</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.911675202947157</v>
+        <v>7.911839025693187</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.885840011455169</v>
+        <v>7.885945562923643</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.880689225005279</v>
+        <v>7.869724187451082</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.899779895636845</v>
+        <v>7.885297808713911</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.891883279330384</v>
+        <v>7.876378711126955</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.875213611620349</v>
+        <v>7.855360509599532</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.855080549073996</v>
+        <v>7.83179220135515</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.829197884375918</v>
+        <v>7.803103754748557</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.800993391857932</v>
+        <v>7.773382876645654</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.768692222802547</v>
+        <v>7.739456309996106</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.722680418686327</v>
+        <v>7.692317143638519</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.607510523311349</v>
+        <v>7.575632334979428</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.513541719568929</v>
+        <v>7.490258394500292</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.440856161441166</v>
+        <v>7.424632982897768</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.474624771295979</v>
+        <v>7.436509350843421</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,15 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.372437271295978</v>
+        <v>7.334321850843421</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>7.23213435084342</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370395918422307</v>
+        <v>8.370388163265403</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367836902626943</v>
+        <v>8.367843608319694</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394782686430098</v>
+        <v>8.394769227884645</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410903077359114</v>
+        <v>8.410896444741175</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424193289066382</v>
+        <v>8.424193487634078</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42830116013223</v>
+        <v>8.42830733515104</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426952744893734</v>
+        <v>8.426964874770167</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431252859328373</v>
+        <v>8.431272279336987</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428355720410694</v>
+        <v>8.428420425811556</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438216546919881</v>
+        <v>8.438286539454985</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444613384279752</v>
+        <v>8.444688974797419</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437764648981116</v>
+        <v>8.437839625932172</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417472196147392</v>
+        <v>8.417552078632292</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399224367890209</v>
+        <v>8.399331097132533</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371669602843141</v>
+        <v>8.371763454293882</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333863732335026</v>
+        <v>8.333964769411615</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277718520037546</v>
+        <v>8.277857759187327</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223082837391129</v>
+        <v>8.223228966531639</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171741659248163</v>
+        <v>8.171820257625416</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129338956998881</v>
+        <v>8.129387669628642</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133618045400874</v>
+        <v>8.133597245209012</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187166839209574</v>
+        <v>8.18709350032268</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.221602129754316</v>
+        <v>8.221394653899788</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.206910375859996</v>
+        <v>8.206652039873003</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.178660358876627</v>
+        <v>8.178384320390832</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.133627110375631</v>
+        <v>8.133373420744043</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.109434916200367</v>
+        <v>8.109236127392176</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118964181166216</v>
+        <v>8.118824340283334</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16389142073302</v>
+        <v>8.163909853846377</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191261597297629</v>
+        <v>8.191311235482829</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.170919924519525</v>
+        <v>8.17102482309633</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.192291372797619</v>
+        <v>8.192525483452112</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.190356022516269</v>
+        <v>8.190804621240314</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.219894567529911</v>
+        <v>8.220424677600311</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.306315572569751</v>
+        <v>8.307033217546714</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.271734320682942</v>
+        <v>8.272166824658106</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.269784824928742</v>
+        <v>8.270378312702242</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.253588073579635</v>
+        <v>8.254176734167107</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.26227180246695</v>
+        <v>8.262951078065342</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.293306065653743</v>
+        <v>8.294159986566315</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.312455185498333</v>
+        <v>8.313380442434573</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.219203300190017</v>
+        <v>8.220121886129441</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.132159779977176</v>
+        <v>8.132932408350577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.045694288382773</v>
+        <v>8.046174333997389</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.003137653092583</v>
+        <v>8.003539616785485</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96328817541864</v>
+        <v>7.96349048547245</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.939062180227393</v>
+        <v>7.939205211763586</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.94136188281846</v>
+        <v>7.941660166232277</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.911839025693187</v>
+        <v>7.911995208614181</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.885945562923643</v>
+        <v>7.886045066242601</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.869724187451082</v>
+        <v>7.869878349968369</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.885297808713911</v>
+        <v>7.885659154127103</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.876378711126955</v>
+        <v>7.865152583860338</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.855360509599532</v>
+        <v>7.843562785159233</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.83179220135515</v>
+        <v>7.820461433156142</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.803103754748557</v>
+        <v>7.789355321370642</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.773382876645654</v>
+        <v>7.758918410373526</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.739456309996106</v>
+        <v>7.724903663450544</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.692317143638519</v>
+        <v>7.678184221431275</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.575632334979428</v>
+        <v>7.568868012552917</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.490258394500292</v>
+        <v>7.488933458579899</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.424632982897768</v>
+        <v>7.417758162707313</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.436509350843421</v>
+        <v>7.417020625669772</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.334321850843421</v>
+        <v>7.288904280204564</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,15 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.23213435084342</v>
+        <v>7.23869385060812</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>7.236640492378058</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.843562785159233</v>
+        <v>7.843663470065672</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.820461433156142</v>
+        <v>7.821006080472241</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.789355321370642</v>
+        <v>7.790891973186238</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.758918410373526</v>
+        <v>7.760827658021975</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.724903663450544</v>
+        <v>7.727413172056174</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.678184221431275</v>
+        <v>7.681417031803596</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.568868012552917</v>
+        <v>7.573551607145701</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.488933458579899</v>
+        <v>7.494904718929066</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.417758162707313</v>
+        <v>7.425986724867047</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.417020625669772</v>
+        <v>7.427662298351204</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.288904280204564</v>
+        <v>7.311074600592478</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.23869385060812</v>
+        <v>7.283090498393469</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.236640492378058</v>
+        <v>7.355513760303791</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370388163265403</v>
+        <v>8.370380737962508</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367843608319694</v>
+        <v>8.367850022396059</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394769227884645</v>
+        <v>8.394756352023675</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410896444741175</v>
+        <v>8.410890102190443</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424193487634078</v>
+        <v>8.424193683862606</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42830733515104</v>
+        <v>8.428313252320184</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426964874770167</v>
+        <v>8.426976491203375</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431272279336987</v>
+        <v>8.431290870993159</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428420425811556</v>
+        <v>8.428482349463273</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438286539454985</v>
+        <v>8.438353547427905</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444688974797419</v>
+        <v>8.444761343455301</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437839625932172</v>
+        <v>8.437911406500326</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417552078632292</v>
+        <v>8.417628592100982</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399331097132533</v>
+        <v>8.399433310577816</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371763454293882</v>
+        <v>8.371853325841828</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.333964769411615</v>
+        <v>8.334061596619522</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277857759187327</v>
+        <v>8.277991237367715</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223228966531639</v>
+        <v>8.223369202121495</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171820257625416</v>
+        <v>8.171895666600612</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129387669628642</v>
+        <v>8.129434422589846</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133597245209012</v>
+        <v>8.133577582780624</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18709350032268</v>
+        <v>8.187023480481734</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.221394653899788</v>
+        <v>8.221195842853158</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.206652039873003</v>
+        <v>8.206404287762773</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.178384320390832</v>
+        <v>8.178119403541341</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.133373420744043</v>
+        <v>8.133129681119991</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.109236127392176</v>
+        <v>8.10904473686327</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118824340283334</v>
+        <v>8.118689160833004</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163909853846377</v>
+        <v>8.163926624629273</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191311235482829</v>
+        <v>8.191358699409795</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17102482309633</v>
+        <v>8.171125109673721</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.192525483452112</v>
+        <v>8.192750414684633</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.190804621240314</v>
+        <v>8.191235948806042</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.220424677600311</v>
+        <v>8.220934308694162</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.307033217546714</v>
+        <v>8.307722471022878</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.272166824658106</v>
+        <v>8.272580640051459</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.270378312702242</v>
+        <v>8.27094634596928</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.254176734167107</v>
+        <v>8.254739417527126</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.262951078065342</v>
+        <v>8.26360054491759</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.294159986566315</v>
+        <v>8.294976924751541</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.313380442434573</v>
+        <v>8.314266111862667</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.220121886129441</v>
+        <v>8.221002597596684</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.132932408350577</v>
+        <v>8.133674023805096</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.046174333997389</v>
+        <v>8.046636121578771</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.003539616785485</v>
+        <v>8.003926587461795</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96349048547245</v>
+        <v>7.963685289912738</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.939205211763586</v>
+        <v>7.939342577103717</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.941660166232277</v>
+        <v>7.941946470295594</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.911995208614181</v>
+        <v>7.91214426876599</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886045066242601</v>
+        <v>7.88613899093069</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.869878349968369</v>
+        <v>7.870024367870567</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.885659154127103</v>
+        <v>7.886004679521792</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865152583860338</v>
+        <v>7.855396471761123</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.843663470065672</v>
+        <v>7.833569359665812</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.821006080472241</v>
+        <v>7.811773332628629</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.790891973186238</v>
+        <v>7.780548033085452</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.760827658021975</v>
+        <v>7.750320715956247</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.727413172056174</v>
+        <v>7.717478313620012</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.681417031803596</v>
+        <v>7.672579048834781</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.573551607145701</v>
+        <v>7.571934780005954</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.494904718929066</v>
+        <v>7.498352306685934</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.425986724867047</v>
+        <v>7.426984679152181</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.427662298351204</v>
+        <v>7.421378355311502</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.311074600592478</v>
+        <v>7.32335467527721</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.283090498393469</v>
+        <v>7.310052163095303</v>
       </c>
     </row>
     <row r="107" spans="1:2">

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370380737962508</v>
+        <v>8.370373621910074</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367850022396059</v>
+        <v>8.367856163460017</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394756352023675</v>
+        <v>8.394744021846281</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410890102190443</v>
+        <v>8.410884031115147</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424193683862606</v>
+        <v>8.424193877529321</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428313252320184</v>
+        <v>8.428318927449673</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426976491203375</v>
+        <v>8.426987626100958</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431290870993159</v>
+        <v>8.431308686156379</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428482349463273</v>
+        <v>8.428541666779065</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438353547427905</v>
+        <v>8.438417757625515</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444761343455301</v>
+        <v>8.444830691802993</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437911406500326</v>
+        <v>8.437980190681564</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417628592100982</v>
+        <v>8.417701945019337</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399433310577816</v>
+        <v>8.399531288504313</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371853325841828</v>
+        <v>8.371939465023631</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334061596619522</v>
+        <v>8.334154471272516</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.277991237367715</v>
+        <v>8.278119304036105</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223369202121495</v>
+        <v>8.223503891873076</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171895666600612</v>
+        <v>8.171968075696187</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129434422589846</v>
+        <v>8.12947933140353</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133577582780624</v>
+        <v>8.133558972044973</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.187023480481734</v>
+        <v>8.186956561294288</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.221195842853158</v>
+        <v>8.221005167004176</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.206404287762773</v>
+        <v>8.206166485955125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.178119403541341</v>
+        <v>8.177864954568737</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.133129681119991</v>
+        <v>8.132895324031395</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10904473686327</v>
+        <v>8.108860348621659</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118689160833004</v>
+        <v>8.118558430173152</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163926624629273</v>
+        <v>8.163941887915838</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191358699409795</v>
+        <v>8.19140412472796</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171125109673721</v>
+        <v>8.171221076674989</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.192750414684633</v>
+        <v>8.192966687089408</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.191235948806042</v>
+        <v>8.191650971618555</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.220934308694162</v>
+        <v>8.221424611105919</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.307722471022878</v>
+        <v>8.308384971648495</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.272580640051459</v>
+        <v>8.272976949042437</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.27094634596928</v>
+        <v>8.271490521118839</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.254739417527126</v>
+        <v>8.255277792916136</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.26360054491759</v>
+        <v>8.264222108486461</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.294976924751541</v>
+        <v>8.295759212418059</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.314266111862667</v>
+        <v>8.315114664486181</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.221002597596684</v>
+        <v>8.221847711444532</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.133674023805096</v>
+        <v>8.13438643653245</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.046636121578771</v>
+        <v>8.04708065392504</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.003926587461795</v>
+        <v>8.004299372832239</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.963685289912738</v>
+        <v>7.963872994109114</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.939342577103717</v>
+        <v>7.939474607310733</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.941946470295594</v>
+        <v>7.942221500688007</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91214426876599</v>
+        <v>7.912286677994123</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88613899093069</v>
+        <v>7.886227761259348</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870024367870567</v>
+        <v>7.870162836003896</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.886004679521792</v>
+        <v>7.886335391335255</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.855396471761123</v>
+        <v>7.855853123839723</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.833569359665812</v>
+        <v>7.824965205957969</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.811773332628629</v>
+        <v>7.80378753718084</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.780548033085452</v>
+        <v>7.774401347006112</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750320715956247</v>
+        <v>7.745096102414164</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.717478313620012</v>
+        <v>7.713905800217131</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.672579048834781</v>
+        <v>7.670634393056818</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.571934780005954</v>
+        <v>7.57704159195938</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.498352306685934</v>
+        <v>7.507805682811059</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.426984679152181</v>
+        <v>7.440314745795226</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.421378355311502</v>
+        <v>7.425533053681471</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.32335467527721</v>
+        <v>7.340017152678706</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.310052163095303</v>
+        <v>7.320275465663368</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,15 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.355513760303791</v>
+        <v>7.341371155134877</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>7.279551779040616</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370373621910074</v>
+        <v>8.37036679618525</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367856163460017</v>
+        <v>8.367862048567087</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394744021846281</v>
+        <v>8.394732203416435</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410884031115147</v>
+        <v>8.410878214476845</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424193877529321</v>
+        <v>8.424194068458796</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428318927449673</v>
+        <v>8.428324375083667</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426987626100958</v>
+        <v>8.426998308781643</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431308686156379</v>
+        <v>8.431325772448298</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428541666779065</v>
+        <v>8.428598538742673</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438417757625515</v>
+        <v>8.438479341576461</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444830691802993</v>
+        <v>8.444897204933183</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.437980190681564</v>
+        <v>8.438046162138706</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417701945019337</v>
+        <v>8.417772329022489</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399531288504313</v>
+        <v>8.399625288496088</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.371939465023631</v>
+        <v>8.372022099293627</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334154471272516</v>
+        <v>8.334243630167434</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278119304036105</v>
+        <v>8.278242281012263</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223503891873076</v>
+        <v>8.223633356818496</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.171968075696187</v>
+        <v>8.172037659770906</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.12947933140353</v>
+        <v>8.129522502718171</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133558972044973</v>
+        <v>8.133541335111223</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186956561294288</v>
+        <v>8.186892542976441</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.221005167004176</v>
+        <v>8.220822138876207</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.206166485955125</v>
+        <v>8.205938050150381</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.177864954568737</v>
+        <v>8.177620369554132</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.132895324031395</v>
+        <v>8.13266982380479</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.108860348621659</v>
+        <v>8.108682593622568</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118558430173152</v>
+        <v>8.118431946804083</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163941887915838</v>
+        <v>8.163955782072726</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19140412472796</v>
+        <v>8.191447636343639</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171221076674989</v>
+        <v>8.171312992698367</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.192966687089408</v>
+        <v>8.19317478336332</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.191650971618555</v>
+        <v>8.192050586304148</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.221424611105919</v>
+        <v>8.221896651695893</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.308384971648495</v>
+        <v>8.309022235407554</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.272976949042437</v>
+        <v>8.273356836437857</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.271490521118839</v>
+        <v>8.272012304320011</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.255277792916136</v>
+        <v>8.255793390571256</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.264222108486461</v>
+        <v>8.264817516326229</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.295759212418059</v>
+        <v>8.296508991202675</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.315114664486181</v>
+        <v>8.315928370899105</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.221847711444532</v>
+        <v>8.222659327063269</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.13438643653245</v>
+        <v>8.135071320182576</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.04708065392504</v>
+        <v>8.047508863355539</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.004299372832239</v>
+        <v>8.004658724913345</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.963872994109114</v>
+        <v>7.964053975106646</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.939474607310733</v>
+        <v>7.93960160806463</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.942221500688007</v>
+        <v>7.942485908861751</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.912286677994123</v>
+        <v>7.912422867728074</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886227761259348</v>
+        <v>7.886311761407713</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870162836003896</v>
+        <v>7.870294294723976</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.886335391335255</v>
+        <v>7.886652213178651</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.855853123839723</v>
+        <v>7.856291382681484</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.824965205957969</v>
+        <v>7.818434606113792</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.80378753718084</v>
+        <v>7.798026129702995</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.774401347006112</v>
+        <v>7.770351393650705</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.745096102414164</v>
+        <v>7.742256609605259</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.713905800217131</v>
+        <v>7.712786854629272</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.670634393056818</v>
+        <v>7.671190505191751</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.57704159195938</v>
+        <v>7.58391990871144</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.507805682811059</v>
+        <v>7.51849064963168</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.440314745795226</v>
+        <v>7.454534465171609</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.425533053681471</v>
+        <v>7.433414422612608</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.340017152678706</v>
+        <v>7.362622384309168</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.320275465663368</v>
+        <v>7.34472716084448</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.341371155134877</v>
+        <v>7.354407492039875</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.279551779040616</v>
+        <v>7.33163627426211</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37036679618525</v>
+        <v>8.370360243377959</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367862048567087</v>
+        <v>8.36786769338204</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394732203416435</v>
+        <v>8.39472086555238</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410878214476845</v>
+        <v>8.410872636631753</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424194068458796</v>
+        <v>8.424194256515307</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428324375083667</v>
+        <v>8.428329608624605</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.426998308781643</v>
+        <v>8.4270085662325</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431325772448298</v>
+        <v>8.43134217367669</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428598538742673</v>
+        <v>8.428653113360719</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438479341576461</v>
+        <v>8.438538457077071</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444897204933183</v>
+        <v>8.444961053126693</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438046162138706</v>
+        <v>8.438109489834366</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417772329022489</v>
+        <v>8.417839920577761</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399625288496088</v>
+        <v>8.399715547691521</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372022099293627</v>
+        <v>8.372101438017161</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334243630167434</v>
+        <v>8.334329291585773</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278242281012263</v>
+        <v>8.278360465151156</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223633356818496</v>
+        <v>8.223757893805919</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172037659770906</v>
+        <v>8.172104580405119</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129522502718171</v>
+        <v>8.129564035142275</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133541335111223</v>
+        <v>8.133524601341801</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186892542976441</v>
+        <v>8.186831242424869</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.220822138876207</v>
+        <v>8.22064630903413</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.205938050150381</v>
+        <v>8.205718440654842</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.177620369554132</v>
+        <v>8.1773850897999</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.13266982380479</v>
+        <v>8.132452692842492</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.108682593622568</v>
+        <v>8.108511127603002</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118431946804083</v>
+        <v>8.118309519850406</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163955782072726</v>
+        <v>8.163968430995109</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191447636343639</v>
+        <v>8.191489349432857</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171312992698367</v>
+        <v>8.171401104859171</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19317478336332</v>
+        <v>8.193375151616451</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.192050586304148</v>
+        <v>8.192435625794669</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.221896651695893</v>
+        <v>8.222351421206547</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.309022235407554</v>
+        <v>8.309635666783649</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.273356836437857</v>
+        <v>8.273721299468384</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.272012304320011</v>
+        <v>8.27251304448259</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.255793390571256</v>
+        <v>8.256287615793665</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.264817516326229</v>
+        <v>8.265388374004402</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.296508991202675</v>
+        <v>8.297228231104762</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.315928370899105</v>
+        <v>8.316709321318674</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.222659327063269</v>
+        <v>8.223439383197373</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.135071320182576</v>
+        <v>8.135730224334122</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.047508863355539</v>
+        <v>8.04792161762343</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.004658724913345</v>
+        <v>8.005005344613199</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.964053975106646</v>
+        <v>7.964228584025495</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.93960160806463</v>
+        <v>7.939723862058594</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.942485908861751</v>
+        <v>7.942740297140198</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.912422867728074</v>
+        <v>7.912553233183013</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886311761407713</v>
+        <v>7.886391339944833</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870294294723976</v>
+        <v>7.870419235832724</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.886652213178651</v>
+        <v>7.886955994113642</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.856291382681484</v>
+        <v>7.856712327183342</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.818434606113792</v>
+        <v>7.814455383569278</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.798026129702995</v>
+        <v>7.795086586977765</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.770351393650705</v>
+        <v>7.769096679397358</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.742256609605259</v>
+        <v>7.742687270472918</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.712786854629272</v>
+        <v>7.715148637844787</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.671190505191751</v>
+        <v>7.675390675684897</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.58391990871144</v>
+        <v>7.59401967231057</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.51849064963168</v>
+        <v>7.531977660959976</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.454534465171609</v>
+        <v>7.471192048023362</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.433414422612608</v>
+        <v>7.445529673521083</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.362622384309168</v>
+        <v>7.38676785149269</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.34472716084448</v>
+        <v>7.370272893394384</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.354407492039875</v>
+        <v>7.372934168410589</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.33163627426211</v>
+        <v>7.368160628793988</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370360243377959</v>
+        <v>8.37034789356751</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36786769338204</v>
+        <v>8.367878318657697</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39472086555238</v>
+        <v>8.394699518956141</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410872636631753</v>
+        <v>8.410862140897803</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424194256515307</v>
+        <v>8.42419462362813</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428329608624605</v>
+        <v>8.428339481974911</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.4270085662325</v>
+        <v>8.427027903071689</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43134217367669</v>
+        <v>8.431373079306042</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428653113360719</v>
+        <v>8.428755905235768</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438538457077071</v>
+        <v>8.438649853174468</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.444961053126693</v>
+        <v>8.445081370310437</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438109489834366</v>
+        <v>8.438228824770576</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417839920577761</v>
+        <v>8.417967365026453</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399715547691521</v>
+        <v>8.399885701711437</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372101438017161</v>
+        <v>8.372250986204843</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334329291585773</v>
+        <v>8.334490912975554</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278360465151156</v>
+        <v>8.27858353146441</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223757893805919</v>
+        <v>8.223993263477656</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172104580405119</v>
+        <v>8.172231018538412</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129564035142275</v>
+        <v>8.129642541918367</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133524601341801</v>
+        <v>8.133493592281285</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186831242424869</v>
+        <v>8.186716135644389</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.22064630903413</v>
+        <v>8.22031461532344</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.205718440654842</v>
+        <v>8.205303740391619</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.1773850897999</v>
+        <v>8.17694041310763</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.132452692842492</v>
+        <v>8.132041759006324</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.108511127603002</v>
+        <v>8.108185797706218</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118309519850406</v>
+        <v>8.118076121669882</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163968430995109</v>
+        <v>8.163990426472983</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191489349432857</v>
+        <v>8.191567797412166</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171401104859171</v>
+        <v>8.171566810858351</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.193375151616451</v>
+        <v>8.193754341145361</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.192435625794669</v>
+        <v>8.193165024727509</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.222351421206547</v>
+        <v>8.223212768151589</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.309635666783649</v>
+        <v>8.310796151653484</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.273721299468384</v>
+        <v>8.274407554316596</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.27251304448259</v>
+        <v>8.273456272416428</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.256287615793665</v>
+        <v>8.257217018516316</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.265388374004402</v>
+        <v>8.266462233856435</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.297228231104762</v>
+        <v>8.298582214584485</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.316709321318674</v>
+        <v>8.318180515927988</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.223439383197373</v>
+        <v>8.224911856873467</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.135730224334122</v>
+        <v>8.136975737823235</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.04792161762343</v>
+        <v>8.048703940441754</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.005005344613199</v>
+        <v>8.005662959512117</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.964228584025495</v>
+        <v>7.964559973251821</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.939723862058594</v>
+        <v>7.93995515814377</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.942740297140198</v>
+        <v>7.943221204379492</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.912553233183013</v>
+        <v>7.912797912758602</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886391339944833</v>
+        <v>7.886538471366249</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870419235832724</v>
+        <v>7.870651320174676</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.886955994113642</v>
+        <v>7.88752749978978</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.856712327183342</v>
+        <v>7.85750618644364</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814455383569278</v>
+        <v>7.806480136385948</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.795086586977765</v>
+        <v>7.788901690376655</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.769096679397358</v>
+        <v>7.765975185094608</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.742687270472918</v>
+        <v>7.742828828432207</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.715148637844787</v>
+        <v>7.7184860482779</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.675390675684897</v>
+        <v>7.681491822371963</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.59401967231057</v>
+        <v>7.608841057277857</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.531977660959976</v>
+        <v>7.55190927698363</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.471192048023362</v>
+        <v>7.49690834849908</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.445529673521083</v>
+        <v>7.468584445504712</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.38676785149269</v>
+        <v>7.425266616187469</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.370272893394384</v>
+        <v>7.409331062081685</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.372934168410589</v>
+        <v>7.405513992996173</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.368160628793988</v>
+        <v>7.406088167089518</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37034789356751</v>
+        <v>8.370342068057521</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367878318657697</v>
+        <v>8.367883324664467</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394699518956141</v>
+        <v>8.394689459324661</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410862140897803</v>
+        <v>8.4108571975177</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42419462362813</v>
+        <v>8.424194802559462</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428339481974911</v>
+        <v>8.428344143808342</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427027903071689</v>
+        <v>8.427037026693602</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431373079306042</v>
+        <v>8.431387655409946</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428755905235768</v>
+        <v>8.428804364422309</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438649853174468</v>
+        <v>8.438702392064524</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445081370310437</v>
+        <v>8.445138118053505</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438228824770576</v>
+        <v>8.438285108595547</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.417967365026453</v>
+        <v>8.418027507428413</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399885701711437</v>
+        <v>8.399965985359069</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372250986204843</v>
+        <v>8.372321538821163</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334490912975554</v>
+        <v>8.334567231911301</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.27858353146441</v>
+        <v>8.278688902560789</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.223993263477656</v>
+        <v>8.224104587777223</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172231018538412</v>
+        <v>8.172290803239102</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129642541918367</v>
+        <v>8.129679679564923</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133493592281285</v>
+        <v>8.133479205231751</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186716135644389</v>
+        <v>8.186662032340504</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.22031461532344</v>
+        <v>8.220158012132584</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.205303740391619</v>
+        <v>8.205107758110648</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.17694041310763</v>
+        <v>8.176730089940609</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.132041759006324</v>
+        <v>8.131847142926773</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.108185797706218</v>
+        <v>8.108031352330826</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.118076121669882</v>
+        <v>8.117964817123664</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163990426472983</v>
+        <v>8.163999962857714</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191567797412166</v>
+        <v>8.191604721669691</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171566810858351</v>
+        <v>8.171644809055845</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.193754341145361</v>
+        <v>8.193933911075684</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.193165024727509</v>
+        <v>8.193510778140183</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.223212768151589</v>
+        <v>8.223621002423307</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.310796151653484</v>
+        <v>8.31134554133558</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.274407554316596</v>
+        <v>8.274730975605035</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.273456272416428</v>
+        <v>8.273900968366862</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.257217018516316</v>
+        <v>8.257654486655952</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.266462233856435</v>
+        <v>8.266967855723898</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.298582214584485</v>
+        <v>8.299220181313011</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.318180515927988</v>
+        <v>8.318874186150895</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.224911856873467</v>
+        <v>8.225607475352215</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.136975737823235</v>
+        <v>8.137564920608792</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.048703940441754</v>
+        <v>8.049074967334693</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.005662959512117</v>
+        <v>8.005975136504041</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.964559973251821</v>
+        <v>7.9647173446154</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.93995515814377</v>
+        <v>7.940064668708181</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.943221204379492</v>
+        <v>7.943448720759847</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.912797912758602</v>
+        <v>7.912912867330044</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886538471366249</v>
+        <v>7.886606576118908</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870651320174676</v>
+        <v>7.870759247873598</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.88752749978978</v>
+        <v>7.887796611633444</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.85750618644364</v>
+        <v>7.8578808785717</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.806480136385948</v>
+        <v>7.803397459275509</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.788901690376655</v>
+        <v>7.78671363993844</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.765975185094608</v>
+        <v>7.76528350762595</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.742828828432207</v>
+        <v>7.743982116177956</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.7184860482779</v>
+        <v>7.721173756352862</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.681491822371963</v>
+        <v>7.685438233811786</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.608841057277857</v>
+        <v>7.616278777729323</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.55190927698363</v>
+        <v>7.561364114055009</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.49690834849908</v>
+        <v>7.510349200528653</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.468584445504712</v>
+        <v>7.482184701232382</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.425266616187469</v>
+        <v>7.444608322926339</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.409331062081685</v>
+        <v>7.429641598861837</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.405513992996173</v>
+        <v>7.424237161047214</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.406088167089518</v>
+        <v>7.42393159350889</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370342068057521</v>
+        <v>8.370336458231762</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367883324664467</v>
+        <v>8.367888141675865</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394689459324661</v>
+        <v>8.394679778056485</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.4108571975177</v>
+        <v>8.41085244174265</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424194802559462</v>
+        <v>8.424194978359578</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428344143808342</v>
+        <v>8.428348635760532</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427037026693602</v>
+        <v>8.427045813890135</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431387655409946</v>
+        <v>8.431401690410533</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428804364422309</v>
+        <v>8.428851012016562</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438702392064524</v>
+        <v>8.438752981086198</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445138118053505</v>
+        <v>8.445192760517209</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438285108595547</v>
+        <v>8.438339303963582</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418027507428413</v>
+        <v>8.418085438585935</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.399965985359069</v>
+        <v>8.400043308809437</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372321538821163</v>
+        <v>8.372389484811139</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334567231911301</v>
+        <v>8.334640773945287</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278688902560789</v>
+        <v>8.278790462211406</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224104587777223</v>
+        <v>8.224211970711792</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172290803239102</v>
+        <v>8.172348460760199</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129679679564923</v>
+        <v>8.129715506029417</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133479205231751</v>
+        <v>8.133465496677248</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186662032340504</v>
+        <v>8.186610050165729</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.220158012132584</v>
+        <v>8.220007123158673</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.205107758110648</v>
+        <v>8.204918812854299</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.176730089940609</v>
+        <v>8.176527213323141</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.131847142926773</v>
+        <v>8.131659264570272</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.108031352330826</v>
+        <v>8.107882029809703</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117964817123664</v>
+        <v>8.117856901348587</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.163999962857714</v>
+        <v>8.164008636091687</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191604721669691</v>
+        <v>8.191640227507291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171644809055845</v>
+        <v>8.171719815209846</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.193933911075684</v>
+        <v>8.194107254903566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.193510778140183</v>
+        <v>8.193844752755119</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.223621002423307</v>
+        <v>8.224015289432568</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.31134554133558</v>
+        <v>8.3118757862328</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.274730975605035</v>
+        <v>8.275042244256959</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.273900968366862</v>
+        <v>8.274329054640397</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.257654486655952</v>
+        <v>8.25807518199311</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.266967855723898</v>
+        <v>8.267454187605685</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.299220181313011</v>
+        <v>8.299834080348946</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.318874186150895</v>
+        <v>8.319541978457996</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.225607475352215</v>
+        <v>8.226277958775707</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.137564920608792</v>
+        <v>8.138133287796768</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.049074967334693</v>
+        <v>8.049433464125297</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.005975136504041</v>
+        <v>8.006276951237938</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.9647173446154</v>
+        <v>7.9648695293775</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940064668708181</v>
+        <v>7.940170372663796</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.943448720759847</v>
+        <v>7.943668218929249</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.912912867330044</v>
+        <v>7.913023283940124</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886606576118908</v>
+        <v>7.886671368620379</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870759247873598</v>
+        <v>7.870862234423221</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.887796611633444</v>
+        <v>7.888055467630346</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.8578808785717</v>
+        <v>7.858241823888485</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.803397459275509</v>
+        <v>7.80380199469856</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.78671363993844</v>
+        <v>7.783120727955835</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.76528350762595</v>
+        <v>7.76290269450239</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.743982116177956</v>
+        <v>7.743289682851767</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.721173756352862</v>
+        <v>7.722579646016385</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.685438233811786</v>
+        <v>7.689012280456115</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.616278777729323</v>
+        <v>7.623548110639553</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.561364114055009</v>
+        <v>7.57031153678964</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.510349200528653</v>
+        <v>7.520015703955451</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.482184701232382</v>
+        <v>7.492611254962621</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.444608322926339</v>
+        <v>7.457423481183388</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.429641598861837</v>
+        <v>7.44193557786632</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.424237161047214</v>
+        <v>7.431802589240774</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,15 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.42393159350889</v>
+        <v>7.426095872561828</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>7.396976663637603</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370336458231762</v>
+        <v>8.370331052330979</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367888141675865</v>
+        <v>8.367892780190463</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394679778056485</v>
+        <v>8.394670454215666</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41085244174265</v>
+        <v>8.410847863104754</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424194978359578</v>
+        <v>8.424195151014128</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428348635760532</v>
+        <v>8.42835296694672</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427045813890135</v>
+        <v>8.42705428292509</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431401690410533</v>
+        <v>8.431415213874956</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428851012016562</v>
+        <v>8.42889594765516</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438752981086198</v>
+        <v>8.438801726755045</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445192760517209</v>
+        <v>8.445245412663352</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438339303963582</v>
+        <v>8.438391524938174</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418085438585935</v>
+        <v>8.418141278133961</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400043308809437</v>
+        <v>8.40011783265267</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372389484811139</v>
+        <v>8.372454965850675</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334640773945287</v>
+        <v>8.334711687739727</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278790462211406</v>
+        <v>8.278888413179319</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224211970711792</v>
+        <v>8.224315617183176</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172348460760199</v>
+        <v>8.172404102322698</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129715506029417</v>
+        <v>8.129750089371825</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133465496677248</v>
+        <v>8.133452422016628</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186610050165729</v>
+        <v>8.186560067643985</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.220007123158673</v>
+        <v>8.219861642158733</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204918812854299</v>
+        <v>8.20473653393897</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.176527213323141</v>
+        <v>8.176331396879768</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.131659264570272</v>
+        <v>8.131477782875413</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107882029809703</v>
+        <v>8.107737583492217</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117856901348587</v>
+        <v>8.117752228891977</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164008636091687</v>
+        <v>8.164016519437645</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191640227507291</v>
+        <v>8.191674393249858</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171719815209846</v>
+        <v>8.1717919959138</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.194107254903566</v>
+        <v>8.194274687055037</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.193844752755119</v>
+        <v>8.194167535080858</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.224015289432568</v>
+        <v>8.224396325822877</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.3118757862328</v>
+        <v>8.312387863915013</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.275042244256959</v>
+        <v>8.275342031082195</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.274329054640397</v>
+        <v>8.274741441787821</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.25807518199311</v>
+        <v>8.258480045222182</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.267454187605685</v>
+        <v>8.267922306332817</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.299834080348946</v>
+        <v>8.300425239901331</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.319541978457996</v>
+        <v>8.320185307104531</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.226277958775707</v>
+        <v>8.226924637326976</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.138133287796768</v>
+        <v>8.138681914495086</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.049433464125297</v>
+        <v>8.049780046616799</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.006276951237938</v>
+        <v>8.00656890427738</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.9648695293775</v>
+        <v>7.965016777607174</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940170372663796</v>
+        <v>7.94027246545175</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.943668218929249</v>
+        <v>7.943880114617779</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913023283940124</v>
+        <v>7.913129424166104</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886671368620379</v>
+        <v>7.886733069148239</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870862234423221</v>
+        <v>7.870960595217717</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888055467630346</v>
+        <v>7.888304638564206</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.858241823888485</v>
+        <v>7.85858975942048</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.80380199469856</v>
+        <v>7.804193153659813</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.783120727955835</v>
+        <v>7.779117004208146</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.76290269450239</v>
+        <v>7.759843779520881</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.743289682851767</v>
+        <v>7.741654086232225</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722579646016385</v>
+        <v>7.722533820686889</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.689012280456115</v>
+        <v>7.690688242162789</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.623548110639553</v>
+        <v>7.62818999712181</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.57031153678964</v>
+        <v>7.576185367862124</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.520015703955451</v>
+        <v>7.526416190302285</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.492611254962621</v>
+        <v>7.499475313864215</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.457423481183388</v>
+        <v>7.465198736374132</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.44193557786632</v>
+        <v>7.448904256950454</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.431802589240774</v>
+        <v>7.434474958810025</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.426095872561828</v>
+        <v>7.423708373633445</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.396976663637603</v>
+        <v>7.382525454472781</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759843779520881</v>
+        <v>7.759843553103157</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.741654086232225</v>
+        <v>7.741596321070119</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722533820686889</v>
+        <v>7.722286900975396</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.690688242162789</v>
+        <v>7.690260685043206</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.62818999712181</v>
+        <v>7.62753267948628</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.576185367862124</v>
+        <v>7.575419138240452</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.526416190302285</v>
+        <v>7.525277248195533</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.499475313864215</v>
+        <v>7.497227305475604</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.465198736374132</v>
+        <v>7.462748322293756</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.448904256950454</v>
+        <v>7.446792580661242</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.434474958810025</v>
+        <v>7.433118238056765</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.423708373633445</v>
+        <v>7.422495806728811</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.382525454472781</v>
+        <v>7.379217554841387</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759843553103157</v>
+        <v>7.759849238141298</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.741596321070119</v>
+        <v>7.741666157808524</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722286900975396</v>
+        <v>7.722580253660843</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.690260685043206</v>
+        <v>7.690771564126413</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.62753267948628</v>
+        <v>7.628322402810629</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.575419138240452</v>
+        <v>7.576343757327956</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.525277248195533</v>
+        <v>7.526648834712283</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.497227305475604</v>
+        <v>7.498176646640887</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.462748322293756</v>
+        <v>7.463747217978309</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.446792580661242</v>
+        <v>7.446084575082201</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.433118238056765</v>
+        <v>7.433484900631758</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.422495806728811</v>
+        <v>7.422670981502023</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.379217554841387</v>
+        <v>7.379137874906581</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370331052330979</v>
+        <v>8.370325839435385</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367892780190463</v>
+        <v>8.367897249943791</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394670454215666</v>
+        <v>8.394661468381752</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410847863104754</v>
+        <v>8.410843451899801</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195151014128</v>
+        <v>8.424195320522616</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42835296694672</v>
+        <v>8.428357145841796</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.42705428292509</v>
+        <v>8.427062450764257</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431415213874956</v>
+        <v>8.431428253255737</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.42889594765516</v>
+        <v>8.428939263805542</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438801726755045</v>
+        <v>8.43884872797096</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445245412663352</v>
+        <v>8.445296181237303</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438391524938174</v>
+        <v>8.438441877429199</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418141278133961</v>
+        <v>8.418195137238081</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40011783265267</v>
+        <v>8.400189706080784</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372454965850675</v>
+        <v>8.372518113542167</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334711687739727</v>
+        <v>8.334780111544402</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278888413179319</v>
+        <v>8.278982944121202</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224315617183176</v>
+        <v>8.224415718186815</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172404102322698</v>
+        <v>8.172457831549696</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129750089371825</v>
+        <v>8.129783493034134</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133452422016628</v>
+        <v>8.1334399403517</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186560067643985</v>
+        <v>8.186511972345663</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219861642158733</v>
+        <v>8.21972128432588</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.20473653393897</v>
+        <v>8.204560576150785</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.176331396879768</v>
+        <v>8.176142280353577</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.131477782875413</v>
+        <v>8.131302379210727</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107737583492217</v>
+        <v>8.10759778200763</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117752228891977</v>
+        <v>8.117650661941159</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164016519437645</v>
+        <v>8.164023679175724</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191674393249858</v>
+        <v>8.191707291681228</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.1717919959138</v>
+        <v>8.171861505770483</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.194274687055037</v>
+        <v>8.194436501413122</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.194167535080858</v>
+        <v>8.194479673703864</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.224396325822877</v>
+        <v>8.22476476303682</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.312387863915013</v>
+        <v>8.312882686924281</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.275342031082195</v>
+        <v>8.275630958517189</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.274741441787821</v>
+        <v>8.275138975203575</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.258480045222182</v>
+        <v>8.258869948371522</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.267922306332817</v>
+        <v>8.268373210480121</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.300425239901331</v>
+        <v>8.300994892788854</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.320185307104531</v>
+        <v>8.320805485635756</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.226924637326976</v>
+        <v>8.227548749511154</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.138681914495086</v>
+        <v>8.139211803654074</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.049780046616799</v>
+        <v>8.050115291525509</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.00656890427738</v>
+        <v>8.006851464955965</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965016777607174</v>
+        <v>7.965159323696813</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94027246545175</v>
+        <v>7.940371129329412</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.943880114617779</v>
+        <v>7.944084795356933</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913129424166104</v>
+        <v>7.913231529995577</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886733069148239</v>
+        <v>7.886791879676372</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.870960595217717</v>
+        <v>7.871054620247655</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888304638564206</v>
+        <v>7.888544653935782</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.85858975942048</v>
+        <v>7.858925370835578</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.804193153659813</v>
+        <v>7.804571575811944</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.779117004208146</v>
+        <v>7.776469395001702</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759849238141298</v>
+        <v>7.758256576334383</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.741666157808524</v>
+        <v>7.74148771012687</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722580253660843</v>
+        <v>7.724306990981446</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.690771564126413</v>
+        <v>7.694410067739335</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.628322402810629</v>
+        <v>7.635061866458711</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.576343757327956</v>
+        <v>7.584462754981432</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.526648834712283</v>
+        <v>7.535690828133529</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.498176646640887</v>
+        <v>7.507357593263791</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.463747217978309</v>
+        <v>7.474302168470043</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.446084575082201</v>
+        <v>7.454614082510643</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.433484900631758</v>
+        <v>7.439489291622351</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.422670981502023</v>
+        <v>7.425133718189865</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.379137874906581</v>
+        <v>7.386462622882908</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370325839435385</v>
+        <v>8.370320809391103</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367897249943791</v>
+        <v>8.367901559976399</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394661468381752</v>
+        <v>8.394652802515182</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410843451899801</v>
+        <v>8.410839199118936</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195320522616</v>
+        <v>8.424195486896096</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428357145841796</v>
+        <v>8.428361180335523</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427062450764257</v>
+        <v>8.427070333188693</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431428253255737</v>
+        <v>8.431440834076414</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428939263805542</v>
+        <v>8.428981046398864</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.43884872797096</v>
+        <v>8.43889407668653</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445296181237303</v>
+        <v>8.445345165488796</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438441877429199</v>
+        <v>8.438490459908314</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418195137238081</v>
+        <v>8.41824711933031</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400189706080784</v>
+        <v>8.400259067880301</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372518113542167</v>
+        <v>8.372579050293272</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334780111544402</v>
+        <v>8.334846174091462</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.278982944121202</v>
+        <v>8.279074230790943</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224415718186815</v>
+        <v>8.224512451967035</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172457831549696</v>
+        <v>8.172509745102278</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129783493034134</v>
+        <v>8.129815776224405</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.1334399403517</v>
+        <v>8.133428014119277</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186511972345663</v>
+        <v>8.186465660065346</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.21972128432588</v>
+        <v>8.219585784451432</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204560576150785</v>
+        <v>8.204390617605082</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.176142280353577</v>
+        <v>8.175959527449679</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.131302379210727</v>
+        <v>8.131132755579097</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10759778200763</v>
+        <v>8.107462408128203</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117650661941159</v>
+        <v>8.117552069887372</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164023679175724</v>
+        <v>8.164030175358628</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191707291681228</v>
+        <v>8.191738990515532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171861505770483</v>
+        <v>8.171928488439365</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.194436501413122</v>
+        <v>8.194592972943648</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.194479673703864</v>
+        <v>8.194781682270847</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22476476303682</v>
+        <v>8.22512121088541</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.312882686924281</v>
+        <v>8.313361108058382</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.275630958517189</v>
+        <v>8.275909604899219</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.275138975203575</v>
+        <v>8.275522440833878</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.258869948371522</v>
+        <v>8.259245700924437</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.268373210480121</v>
+        <v>8.26880782731266</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.300994892788854</v>
+        <v>8.301544184804193</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.320805485635756</v>
+        <v>8.321403735652485</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.227548749511154</v>
+        <v>8.228151449872097</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.139211803654074</v>
+        <v>8.139723891965332</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.050115291525509</v>
+        <v>8.050439739477575</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.006851464955965</v>
+        <v>8.007125073730883</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965159323696813</v>
+        <v>7.965297387559858</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940371129329412</v>
+        <v>7.940466534466486</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944084795356933</v>
+        <v>7.944282622826286</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913231529995577</v>
+        <v>7.913329825615026</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886791879676372</v>
+        <v>7.886847985682497</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871054620247655</v>
+        <v>7.871144576545667</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888544653935782</v>
+        <v>7.888776005604125</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.858925370835578</v>
+        <v>7.859249296805748</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.804571575811944</v>
+        <v>7.804937861595977</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.776469395001702</v>
+        <v>7.772873420711992</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.758256576334383</v>
+        <v>7.755372050324574</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.74148771012687</v>
+        <v>7.73985948043219</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.724306990981446</v>
+        <v>7.724234797405266</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.694410067739335</v>
+        <v>7.695711466225585</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.635061866458711</v>
+        <v>7.63900672884707</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.584462754981432</v>
+        <v>7.589089124179382</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.535690828133529</v>
+        <v>7.540837740914569</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.507357593263791</v>
+        <v>7.513615747599687</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.474302168470043</v>
+        <v>7.479684928236106</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.454614082510643</v>
+        <v>7.459773687968549</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.439489291622351</v>
+        <v>7.440434198602905</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.425133718189865</v>
+        <v>7.42202925686437</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.386462622882908</v>
+        <v>7.377841173786887</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755372050324574</v>
+        <v>7.755376803410591</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.73985948043219</v>
+        <v>7.739869893824737</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.724234797405266</v>
+        <v>7.724274678829124</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.695711466225585</v>
+        <v>7.695782757319801</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.63900672884707</v>
+        <v>7.639118943072019</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.589089124179382</v>
+        <v>7.589222599559887</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.540837740914569</v>
+        <v>7.541033776598233</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.513615747599687</v>
+        <v>7.512519443314197</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.479684928236106</v>
+        <v>7.478492024369372</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.459773687968549</v>
+        <v>7.457487106208792</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.440434198602905</v>
+        <v>7.439642259406426</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.42202925686437</v>
+        <v>7.421231618862</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.377841173786887</v>
+        <v>7.376205778260667</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370320809391103</v>
+        <v>8.37031595274415</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367901559976399</v>
+        <v>8.36790571869474</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394652802515182</v>
+        <v>8.394644439836789</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410839199118936</v>
+        <v>8.410835096387551</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195486896096</v>
+        <v>8.424195650155212</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428361180335523</v>
+        <v>8.428365077782159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427070333188693</v>
+        <v>8.427077944896309</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431440834076414</v>
+        <v>8.431452980097966</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.428981046398864</v>
+        <v>8.429021375397078</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.43889407668653</v>
+        <v>8.438937858506254</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445345165488796</v>
+        <v>8.445392457818199</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438490459908314</v>
+        <v>8.438537364050385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41824711933031</v>
+        <v>8.418297320769506</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400259067880301</v>
+        <v>8.400326047323052</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372579050293272</v>
+        <v>8.372637890105324</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334846174091462</v>
+        <v>8.334909995399647</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279074230790943</v>
+        <v>8.279162437122292</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224512451967035</v>
+        <v>8.224605985059515</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172509745102278</v>
+        <v>8.172559933252831</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129815776224405</v>
+        <v>8.129846994263257</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133428014119277</v>
+        <v>8.133416608765467</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186465660065346</v>
+        <v>8.186421034087148</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219585784451432</v>
+        <v>8.219454895272364</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204390617605082</v>
+        <v>8.204226357817189</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175959527449679</v>
+        <v>8.175782823887435</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.131132755579097</v>
+        <v>8.130968632989973</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107462408128203</v>
+        <v>8.107331257729143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117552069887372</v>
+        <v>8.117456328911427</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164030175358628</v>
+        <v>8.16403606247504</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191738990515532</v>
+        <v>8.191769552822327</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171928488439365</v>
+        <v>8.171993077577286</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.194592972943648</v>
+        <v>8.19474435917175</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.194781682270847</v>
+        <v>8.195074042197566</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22512121088541</v>
+        <v>8.22546624078846</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.313361108058382</v>
+        <v>8.313823925150929</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.275909604899219</v>
+        <v>8.276178508296198</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.275522440833878</v>
+        <v>8.275892570296843</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.259245700924437</v>
+        <v>8.259608055300005</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.26880782731266</v>
+        <v>8.269227019008671</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.301544184804193</v>
+        <v>8.302074182218176</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.321403735652485</v>
+        <v>8.32198119468098</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.228151449872097</v>
+        <v>8.228733815947319</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.139723891965332</v>
+        <v>8.140219055196939</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.050439739477575</v>
+        <v>8.050753897740332</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007125073730883</v>
+        <v>8.007390144331545</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965297387559858</v>
+        <v>7.965431175721455</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940466534466486</v>
+        <v>7.940558839933257</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944282622826286</v>
+        <v>7.944473934970091</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913329825615026</v>
+        <v>7.913424519007134</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886847985682497</v>
+        <v>7.886901557750296</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871144576545667</v>
+        <v>7.871230710360189</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888776005604125</v>
+        <v>7.888999151051525</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.859249296805748</v>
+        <v>7.859562132935876</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.804937861595977</v>
+        <v>7.805292575117154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772873420711992</v>
+        <v>7.768858657613178</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755376803410591</v>
+        <v>7.75157112147706</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.739869893824737</v>
+        <v>7.737001266016739</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.724274678829124</v>
+        <v>7.722220022693196</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.695782757319801</v>
+        <v>7.694818149110092</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.639118943072019</v>
+        <v>7.639394645896756</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.589222599559887</v>
+        <v>7.590356585973321</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.541033776598233</v>
+        <v>7.542906009601645</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.512519443314197</v>
+        <v>7.514333368486097</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.478492024369372</v>
+        <v>7.479194989272182</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.457487106208792</v>
+        <v>7.458092325454367</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.439642259406426</v>
+        <v>7.439908420650715</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.421231618862</v>
+        <v>7.421393956695178</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.376205778260667</v>
+        <v>7.382584929510902</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37031595274415</v>
+        <v>8.370306724976128</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36790571869474</v>
+        <v>8.367913612966117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394644439836789</v>
+        <v>8.394628562592002</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410835096387551</v>
+        <v>8.410827310422757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195650155212</v>
+        <v>8.424195967451121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428365077782159</v>
+        <v>8.428372488537194</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427077944896309</v>
+        <v>8.427092410075902</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431452980097966</v>
+        <v>8.431476054856867</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429021375397078</v>
+        <v>8.429097965613431</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438937858506254</v>
+        <v>8.439021035311585</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445392457818199</v>
+        <v>8.445482305490817</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438537364050385</v>
+        <v>8.438626473438569</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418297320769506</v>
+        <v>8.418392735263353</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400326047323052</v>
+        <v>8.400453333377945</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372637890105324</v>
+        <v>8.372749697068031</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334909995399647</v>
+        <v>8.33503135508102</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279162437122292</v>
+        <v>8.279330211163046</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224605985059515</v>
+        <v>8.224784062345275</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172559933252831</v>
+        <v>8.172655465550884</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129846994263257</v>
+        <v>8.129906438580822</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133416608765467</v>
+        <v>8.133395235823514</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186421034087148</v>
+        <v>8.18633648774335</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219454895272364</v>
+        <v>8.219206040890384</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204226357817189</v>
+        <v>8.203913829291869</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175782823887435</v>
+        <v>8.175446407329986</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130968632989973</v>
+        <v>8.130655861277772</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107331257729143</v>
+        <v>8.107080870753778</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117456328911427</v>
+        <v>8.117272936530773</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16403606247504</v>
+        <v>8.164046203078454</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191769552822327</v>
+        <v>8.19182749917532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171993077577286</v>
+        <v>8.172115564868751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19474435917175</v>
+        <v>8.19503282655301</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.195074042197566</v>
+        <v>8.195631595200602</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22546624078846</v>
+        <v>8.226124157891281</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.313823925150929</v>
+        <v>8.314705689312895</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.276178508296198</v>
+        <v>8.27668905734347</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.275892570296843</v>
+        <v>8.276595502702515</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.259608055300005</v>
+        <v>8.260295322879465</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.269227019008671</v>
+        <v>8.270022283219463</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.302074182218176</v>
+        <v>8.303080200514023</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.32198119468098</v>
+        <v>8.323077911277895</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.228733815947319</v>
+        <v>8.229841507432276</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.140219055196939</v>
+        <v>8.141161833423535</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.050753897740332</v>
+        <v>8.051353222210153</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007390144331545</v>
+        <v>8.007896203903321</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965431175721455</v>
+        <v>7.965686689980079</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940558839933257</v>
+        <v>7.940734737910246</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944473934970091</v>
+        <v>7.944838257673789</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913424519007134</v>
+        <v>7.913603858449145</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886901557750296</v>
+        <v>7.887001716316683</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871230710360189</v>
+        <v>7.871392403018506</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888999151051525</v>
+        <v>7.889422498633311</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.859562132935876</v>
+        <v>7.860156723683185</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.805292575117154</v>
+        <v>7.805969375707132</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.768858657613178</v>
+        <v>7.765519221071348</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.75157112147706</v>
+        <v>7.745146865960503</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.737001266016739</v>
+        <v>7.731351979339567</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722220022693196</v>
+        <v>7.716950399859645</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.694818149110092</v>
+        <v>7.690512902717963</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.639394645896756</v>
+        <v>7.63748765009395</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.590356585973321</v>
+        <v>7.590176230554386</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.542906009601645</v>
+        <v>7.544125862678993</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.514333368486097</v>
+        <v>7.515469453043906</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.479194989272182</v>
+        <v>7.48030864190408</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.458092325454367</v>
+        <v>7.456831801712712</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.439908420650715</v>
+        <v>7.438264809562085</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.421393956695178</v>
+        <v>7.419429205612632</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,15 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.382584929510902</v>
+        <v>7.386437747599469</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>7.368163157433445</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370306724976128</v>
+        <v>8.37031595274415</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367913612966117</v>
+        <v>8.36790571869474</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394628562592002</v>
+        <v>8.394644439836789</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410827310422757</v>
+        <v>8.410835096387551</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195967451121</v>
+        <v>8.424195650155212</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428372488537194</v>
+        <v>8.428365077782159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427092410075902</v>
+        <v>8.427077944896309</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431476054856867</v>
+        <v>8.431452980097966</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429097965613431</v>
+        <v>8.429021375397078</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439021035311585</v>
+        <v>8.438937858506254</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445482305490817</v>
+        <v>8.445392457818199</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438626473438569</v>
+        <v>8.438537364050385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418392735263353</v>
+        <v>8.418297320769506</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400453333377945</v>
+        <v>8.400326047323052</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372749697068031</v>
+        <v>8.372637890105324</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33503135508102</v>
+        <v>8.334909995399647</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279330211163046</v>
+        <v>8.279162437122292</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224784062345275</v>
+        <v>8.224605985059515</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172655465550884</v>
+        <v>8.172559933252831</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129906438580822</v>
+        <v>8.129846994263257</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133395235823514</v>
+        <v>8.133416608765467</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18633648774335</v>
+        <v>8.186421034087148</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219206040890384</v>
+        <v>8.219454895272364</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203913829291869</v>
+        <v>8.204226357817189</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175446407329986</v>
+        <v>8.175782823887435</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130655861277772</v>
+        <v>8.130968632989973</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107080870753778</v>
+        <v>8.107331257729143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117272936530773</v>
+        <v>8.117456328911427</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164046203078454</v>
+        <v>8.16403606247504</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19182749917532</v>
+        <v>8.191769552822327</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172115564868751</v>
+        <v>8.171993077577286</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19503282655301</v>
+        <v>8.19474435917175</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.195631595200602</v>
+        <v>8.195074042197566</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.226124157891281</v>
+        <v>8.22546624078846</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.314705689312895</v>
+        <v>8.313823925150929</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27668905734347</v>
+        <v>8.276178508296198</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.276595502702515</v>
+        <v>8.275892570296843</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.260295322879465</v>
+        <v>8.259608055300005</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.270022283219463</v>
+        <v>8.269227019008671</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.303080200514023</v>
+        <v>8.302074182218176</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.323077911277895</v>
+        <v>8.32198119468098</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.229841507432276</v>
+        <v>8.228733815947319</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.141161833423535</v>
+        <v>8.140219055196939</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.051353222210153</v>
+        <v>8.050753897740332</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007896203903321</v>
+        <v>8.007390144331545</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965686689980079</v>
+        <v>7.965431175721455</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940734737910246</v>
+        <v>7.940558839933257</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944838257673789</v>
+        <v>7.944473934970091</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913603858449145</v>
+        <v>7.913424519007134</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887001716316683</v>
+        <v>7.886901557750296</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871392403018506</v>
+        <v>7.871230710360189</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.889422498633311</v>
+        <v>7.888999151051525</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.860156723683185</v>
+        <v>7.859562132935876</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.805969375707132</v>
+        <v>7.805292575117154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.765519221071348</v>
+        <v>7.773204377802397</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.745146865960503</v>
+        <v>7.751784886657694</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.731351979339567</v>
+        <v>7.736295597486405</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.716950399859645</v>
+        <v>7.721416408055848</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.690512902717963</v>
+        <v>7.693945266019925</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.63748765009395</v>
+        <v>7.639535035707175</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.590176230554386</v>
+        <v>7.591372485905419</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.544125862678993</v>
+        <v>7.54352800416868</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.515469453043906</v>
+        <v>7.515610715166812</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.48030864190408</v>
+        <v>7.482053986007365</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.456831801712712</v>
+        <v>7.457544277729927</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.438264809562085</v>
+        <v>7.435950055073662</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.419429205612632</v>
+        <v>7.413108223784091</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.386437747599469</v>
+        <v>7.358821127551531</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.368163157433445</v>
+        <v>7.384320887144549</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.736295597486405</v>
+        <v>7.73627745008573</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.721416408055848</v>
+        <v>7.721387378877013</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.693945266019925</v>
+        <v>7.693925957725775</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.639535035707175</v>
+        <v>7.638582760604594</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.591372485905419</v>
+        <v>7.589630003565337</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.54352800416868</v>
+        <v>7.542237107965464</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.515610715166812</v>
+        <v>7.514605476907005</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.482053986007365</v>
+        <v>7.481296373560628</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.457544277729927</v>
+        <v>7.457410861795627</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.435950055073662</v>
+        <v>7.435375054441384</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.413108223784091</v>
+        <v>7.412585713271914</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.358821127551531</v>
+        <v>7.357957258909269</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.384320887144549</v>
+        <v>7.38325885932322</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37031595274415</v>
+        <v>8.370311260681181</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36790571869474</v>
+        <v>8.367909733925794</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394644439836789</v>
+        <v>8.394636364719663</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410835096387551</v>
+        <v>8.410831135910472</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195650155212</v>
+        <v>8.424195810328527</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428365077782159</v>
+        <v>8.428368845045107</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427077944896309</v>
+        <v>8.427085299593204</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431452980097966</v>
+        <v>8.431464713468314</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429021375397078</v>
+        <v>8.429060325302052</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438937858506254</v>
+        <v>8.438980153224829</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445392457818199</v>
+        <v>8.445438144357098</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438537364050385</v>
+        <v>8.438582675309704</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418297320769506</v>
+        <v>8.418345831435323</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400326047323052</v>
+        <v>8.40039076496706</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372637890105324</v>
+        <v>8.372694739282082</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334909995399647</v>
+        <v>8.334971687498395</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279162437122292</v>
+        <v>8.279247716204496</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224605985059515</v>
+        <v>8.224696473233582</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172559933252831</v>
+        <v>8.172608480402769</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129846994263257</v>
+        <v>8.129877198896956</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133416608765467</v>
+        <v>8.13340569245681</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186421034087148</v>
+        <v>8.186378004527109</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219454895272364</v>
+        <v>8.219328385982712</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204226357817189</v>
+        <v>8.204067515960601</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175782823887435</v>
+        <v>8.175611875638429</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130968632989973</v>
+        <v>8.130809749981626</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107331257729143</v>
+        <v>8.107204138836352</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117456328911427</v>
+        <v>8.11736332159121</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16403606247504</v>
+        <v>8.16404139003367</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191769552822327</v>
+        <v>8.191799037410471</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.171993077577286</v>
+        <v>8.172055397684771</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19474435917175</v>
+        <v>8.194890901524445</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.195074042197566</v>
+        <v>8.19535720513252</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22546624078846</v>
+        <v>8.225800388720304</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.313823925150929</v>
+        <v>8.314271885402807</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.276178508296198</v>
+        <v>8.276438169944893</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.275892570296843</v>
+        <v>8.276250045483888</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.259608055300005</v>
+        <v>8.259957711770198</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.269227019008671</v>
+        <v>8.269631588244968</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.302074182218176</v>
+        <v>8.302585878524697</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.32198119468098</v>
+        <v>8.322538923251734</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.228733815947319</v>
+        <v>8.229296854547046</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.140219055196939</v>
+        <v>8.14069811302617</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.050753897740332</v>
+        <v>8.051058242714415</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007390144331545</v>
+        <v>8.007647065723184</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965431175721455</v>
+        <v>7.965560882312989</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940558839933257</v>
+        <v>7.940648194593136</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944473934970091</v>
+        <v>7.944659047909607</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913424519007134</v>
+        <v>7.9135158033801</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.886901557750296</v>
+        <v>7.88695275299238</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871230710360189</v>
+        <v>7.871313249091362</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.888999151051525</v>
+        <v>7.8892145163165</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.859562132935876</v>
+        <v>7.859864435307905</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.805292575117154</v>
+        <v>7.805636246780368</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773204377802397</v>
+        <v>7.773525480025136</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751784886657694</v>
+        <v>7.749531295365526</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.73627745008573</v>
+        <v>7.734246779631433</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.721387378877013</v>
+        <v>7.72018496704299</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.693925957725775</v>
+        <v>7.693897098872604</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.638582760604594</v>
+        <v>7.639986715035942</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.589630003565337</v>
+        <v>7.59203326627542</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.542237107965464</v>
+        <v>7.545449773876206</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.514605476907005</v>
+        <v>7.517571872001858</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.481296373560628</v>
+        <v>7.48521496377177</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.457410861795627</v>
+        <v>7.458092118578807</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.435375054441384</v>
+        <v>7.433985864034</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.412585713271914</v>
+        <v>7.408086398063132</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.357957258909269</v>
+        <v>7.350818955834172</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.38325885932322</v>
+        <v>7.403313387915771</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370311260681181</v>
+        <v>8.370302337942082</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367909733925794</v>
+        <v>8.367917362626018</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394636364719663</v>
+        <v>8.394621019849577</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410831135910472</v>
+        <v>8.410823613145412</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195810328527</v>
+        <v>8.424196121563384</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428368845045107</v>
+        <v>8.428376014257021</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427085299593204</v>
+        <v>8.42709928830557</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431464713468314</v>
+        <v>8.431487023575826</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429060325302052</v>
+        <v>8.429134361241282</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.438980153224829</v>
+        <v>8.439060574347273</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445438144357098</v>
+        <v>8.445525016329562</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438582675309704</v>
+        <v>8.438668832954871</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418345831435323</v>
+        <v>8.418438110728115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40039076496706</v>
+        <v>8.400513857779886</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372694739282082</v>
+        <v>8.372802856224267</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.334971687498395</v>
+        <v>8.335089096094885</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279247716204496</v>
+        <v>8.279410055956031</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224696473233582</v>
+        <v>8.224868889110887</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172608480402769</v>
+        <v>8.172700962717677</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129877198896956</v>
+        <v>8.129934758736125</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13340569245681</v>
+        <v>8.133385211730758</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186378004527109</v>
+        <v>8.186296405806033</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219328385982712</v>
+        <v>8.219087658203028</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.204067515960601</v>
+        <v>8.203765051723835</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175611875638429</v>
+        <v>8.175286160796464</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130809749981626</v>
+        <v>8.130506736564664</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107204138836352</v>
+        <v>8.106961283262969</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11736332159121</v>
+        <v>8.117185068010414</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16404139003367</v>
+        <v>8.16405054264392</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191799037410471</v>
+        <v>8.191854989413137</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172055397684771</v>
+        <v>8.172173687531021</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.194890901524445</v>
+        <v>8.195170347047274</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.19535720513252</v>
+        <v>8.195897611049087</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.225800388720304</v>
+        <v>8.226438021191914</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.314271885402807</v>
+        <v>8.315125994250462</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.276438169944893</v>
+        <v>8.276931607038144</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.276250045483888</v>
+        <v>8.276929536412826</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.259957711770198</v>
+        <v>8.260621497424289</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.269631588244968</v>
+        <v>8.27039980217555</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.302585878524697</v>
+        <v>8.303558013750909</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.322538923251734</v>
+        <v>8.323599083812653</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.229296854547046</v>
+        <v>8.2303686564575</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.14069811302617</v>
+        <v>8.141610936635487</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.051058242714415</v>
+        <v>8.051639257529144</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007647065723184</v>
+        <v>8.008137903546995</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965560882312989</v>
+        <v>7.965808770712653</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940648194593136</v>
+        <v>7.940818600681307</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944659047909607</v>
+        <v>7.945011841768107</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.9135158033801</v>
+        <v>7.913688851587631</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88695275299238</v>
+        <v>7.887048581555616</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871313249091362</v>
+        <v>7.871468366844423</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.8892145163165</v>
+        <v>7.889623468811497</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.859864435307905</v>
+        <v>7.860439484400549</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.805636246780368</v>
+        <v>7.806292431953962</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773525480025136</v>
+        <v>7.765836877001809</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749531295365526</v>
+        <v>7.743390529696031</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.734246779631433</v>
+        <v>7.729675964760762</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.72018496704299</v>
+        <v>7.715758092765481</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.693897098872604</v>
+        <v>7.689302975027222</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.639986715035942</v>
+        <v>7.637533096689112</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.59203326627542</v>
+        <v>7.591169367502467</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.545449773876206</v>
+        <v>7.545790855659388</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.517571872001858</v>
+        <v>7.517377944695211</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.48521496377177</v>
+        <v>7.483432342607712</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.458092118578807</v>
+        <v>7.458253602273455</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.433985864034</v>
+        <v>7.439919152919758</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.408086398063132</v>
+        <v>7.421448020346212</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.350818955834172</v>
+        <v>7.392516452512044</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.403313387915771</v>
+        <v>7.391314241000259</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370302337942082</v>
+        <v>8.370306724976128</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367917362626018</v>
+        <v>8.367913612966117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394621019849577</v>
+        <v>8.394628562592002</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410823613145412</v>
+        <v>8.410827310422757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196121563384</v>
+        <v>8.424195967451121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428376014257021</v>
+        <v>8.428372488537194</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.42709928830557</v>
+        <v>8.427092410075902</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431487023575826</v>
+        <v>8.431476054856867</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429134361241282</v>
+        <v>8.429097965613431</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439060574347273</v>
+        <v>8.439021035311585</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445525016329562</v>
+        <v>8.445482305490817</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438668832954871</v>
+        <v>8.438626473438569</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418438110728115</v>
+        <v>8.418392735263353</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400513857779886</v>
+        <v>8.400453333377945</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372802856224267</v>
+        <v>8.372749697068031</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335089096094885</v>
+        <v>8.33503135508102</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279410055956031</v>
+        <v>8.279330211163046</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224868889110887</v>
+        <v>8.224784062345275</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172700962717677</v>
+        <v>8.172655465550884</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129934758736125</v>
+        <v>8.129906438580822</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133385211730758</v>
+        <v>8.133395235823514</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186296405806033</v>
+        <v>8.18633648774335</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219087658203028</v>
+        <v>8.219206040890384</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203765051723835</v>
+        <v>8.203913829291869</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175286160796464</v>
+        <v>8.175446407329986</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130506736564664</v>
+        <v>8.130655861277772</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106961283262969</v>
+        <v>8.107080870753778</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117185068010414</v>
+        <v>8.117272936530773</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16405054264392</v>
+        <v>8.164046203078454</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191854989413137</v>
+        <v>8.19182749917532</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172173687531021</v>
+        <v>8.172115564868751</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195170347047274</v>
+        <v>8.19503282655301</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.195897611049087</v>
+        <v>8.195631595200602</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.226438021191914</v>
+        <v>8.226124157891281</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.315125994250462</v>
+        <v>8.314705689312895</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.276931607038144</v>
+        <v>8.27668905734347</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.276929536412826</v>
+        <v>8.276595502702515</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.260621497424289</v>
+        <v>8.260295322879465</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.27039980217555</v>
+        <v>8.270022283219463</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.303558013750909</v>
+        <v>8.303080200514023</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.323599083812653</v>
+        <v>8.323077911277895</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.2303686564575</v>
+        <v>8.229841507432276</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.141610936635487</v>
+        <v>8.141161833423535</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.051639257529144</v>
+        <v>8.051353222210153</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.008137903546995</v>
+        <v>8.007896203903321</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965808770712653</v>
+        <v>7.965686689980079</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940818600681307</v>
+        <v>7.940734737910246</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945011841768107</v>
+        <v>7.944838257673789</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913688851587631</v>
+        <v>7.913603858449145</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887048581555616</v>
+        <v>7.887001716316683</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871468366844423</v>
+        <v>7.871392403018506</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.889623468811497</v>
+        <v>7.889422498633311</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.860439484400549</v>
+        <v>7.860156723683185</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.806292431953962</v>
+        <v>7.805969375707132</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.765836877001809</v>
+        <v>7.773837150314222</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.743390529696031</v>
+        <v>7.74984981087262</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.729675964760762</v>
+        <v>7.735395359119495</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.715758092765481</v>
+        <v>7.722439688289812</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.689302975027222</v>
+        <v>7.697791681659147</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.637533096689112</v>
+        <v>7.645589796946799</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.591169367502467</v>
+        <v>7.598849614899748</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.545790855659388</v>
+        <v>7.553219729157283</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.517377944695211</v>
+        <v>7.525538008261705</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.483432342607712</v>
+        <v>7.495250740456486</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.458253602273455</v>
+        <v>7.466374007317249</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.439919152919758</v>
+        <v>7.441464939776034</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.421448020346212</v>
+        <v>7.41475005994636</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.392516452512044</v>
+        <v>7.364724953897507</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.391314241000259</v>
+        <v>7.451791866984806</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370306724976128</v>
+        <v>8.370298092387838</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367913612966117</v>
+        <v>8.367920989269376</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394628562592002</v>
+        <v>8.394613723776775</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410827310422757</v>
+        <v>8.410820037745451</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424195967451121</v>
+        <v>8.424196272709979</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428372488537194</v>
+        <v>8.428379427821865</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427092410075902</v>
+        <v>8.427105945475036</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431476054856867</v>
+        <v>8.431497637689732</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429097965613431</v>
+        <v>8.429169572878518</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439021035311585</v>
+        <v>8.439098835418569</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445482305490817</v>
+        <v>8.445566347133965</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438626473438569</v>
+        <v>8.43870982356442</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418392735263353</v>
+        <v>8.418482031279758</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400453333377945</v>
+        <v>8.400572436644048</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372749697068031</v>
+        <v>8.372854303548939</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33503135508102</v>
+        <v>8.335145002275597</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279330211163046</v>
+        <v>8.279487376095513</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224784062345275</v>
+        <v>8.224951081809451</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172655465550884</v>
+        <v>8.172745041330453</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129906438580822</v>
+        <v>8.129962201983393</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133395235823514</v>
+        <v>8.133375595074611</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18633648774335</v>
+        <v>8.186257686020207</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.219206040890384</v>
+        <v>8.218973048928815</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203913829291869</v>
+        <v>8.203620952531367</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.175446407329986</v>
+        <v>8.17513089376275</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130655861277772</v>
+        <v>8.13036215937637</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.107080870753778</v>
+        <v>8.106845215888239</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117272936530773</v>
+        <v>8.117099615657157</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164046203078454</v>
+        <v>8.164054446158426</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19182749917532</v>
+        <v>8.191881556106232</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172115564868751</v>
+        <v>8.172229866990723</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19503282655301</v>
+        <v>8.195303663052629</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.195631595200602</v>
+        <v>8.196155627715635</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.226124157891281</v>
+        <v>8.226742423423566</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.314705689312895</v>
+        <v>8.315533417706423</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27668905734347</v>
+        <v>8.277166227138586</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.276595502702515</v>
+        <v>8.277252702603352</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.260295322879465</v>
+        <v>8.26093680404281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.270022283219463</v>
+        <v>8.270764797484881</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.303080200514023</v>
+        <v>8.304020127524096</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.323077911277895</v>
+        <v>8.324103306254578</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.229841507432276</v>
+        <v>8.230879128235738</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.141161833423535</v>
+        <v>8.142046098807622</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.051353222210153</v>
+        <v>8.051916745369756</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.007896203903321</v>
+        <v>8.008372489515086</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965686689980079</v>
+        <v>7.965927286604655</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940734737910246</v>
+        <v>7.940899905700026</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.944838257673789</v>
+        <v>7.945180060598854</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913603858449145</v>
+        <v>7.913770938862936</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887001716316683</v>
+        <v>7.887093472474816</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871392403018506</v>
+        <v>7.871541321078523</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.889422498633311</v>
+        <v>7.889817773384669</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.860156723683185</v>
+        <v>7.860713173003152</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.805969375707132</v>
+        <v>7.806605858550187</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773837150314222</v>
+        <v>7.766145508938683</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.74984981087262</v>
+        <v>7.745732246994837</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.735395359119495</v>
+        <v>7.73324956736229</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.722439688289812</v>
+        <v>7.720657391233464</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.697791681659147</v>
+        <v>7.695444482324149</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.645589796946799</v>
+        <v>7.645796889227965</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.598849614899748</v>
+        <v>7.600956399587054</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.553219729157283</v>
+        <v>7.556823987378845</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.525538008261705</v>
+        <v>7.529332026756461</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.495250740456486</v>
+        <v>7.498129532938563</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.466374007317249</v>
+        <v>7.473339428308197</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.441464939776034</v>
+        <v>7.456575787273013</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.41475005994636</v>
+        <v>7.440745472235392</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.364724953897507</v>
+        <v>7.425110001702889</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.451791866984806</v>
+        <v>7.478668806901401</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370298092387838</v>
+        <v>8.370293981578588</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367920989269376</v>
+        <v>8.367924498849611</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394613723776775</v>
+        <v>8.394606662475276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410820037745451</v>
+        <v>8.410816578299851</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196272709979</v>
+        <v>8.424196420938991</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428379427821865</v>
+        <v>8.428382734497502</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427105945475036</v>
+        <v>8.427112392069517</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431497637689732</v>
+        <v>8.431507914114588</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429169572878518</v>
+        <v>8.429203657337721</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439098835418569</v>
+        <v>8.439135879475003</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445566347133965</v>
+        <v>8.445606363700119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43870982356442</v>
+        <v>8.438749510543069</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418482031279758</v>
+        <v>8.418524565739544</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400572436644048</v>
+        <v>8.400629162221314</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372854303548939</v>
+        <v>8.372904120348412</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335145002275597</v>
+        <v>8.335199159631252</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279487376095513</v>
+        <v>8.279562289301889</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.224951081809451</v>
+        <v>8.225030760921639</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172745041330453</v>
+        <v>8.17278776657326</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129962201983393</v>
+        <v>8.129988808354517</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133375595074611</v>
+        <v>8.133366362599546</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186257686020207</v>
+        <v>8.186220260495505</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218973048928815</v>
+        <v>8.218862035879654</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203620952531367</v>
+        <v>8.203481315175409</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.17513089376275</v>
+        <v>8.174980378646133</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.13036215937637</v>
+        <v>8.130221926077388</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106845215888239</v>
+        <v>8.106732517221426</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117099615657157</v>
+        <v>8.117016484134698</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164054446158426</v>
+        <v>8.164057947801879</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191881556106232</v>
+        <v>8.19190724418185</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172229866990723</v>
+        <v>8.172284198047958</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195303663052629</v>
+        <v>8.195432962799341</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.196155627715635</v>
+        <v>8.196405998335948</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.226742423423566</v>
+        <v>8.22703778333689</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.315533417706423</v>
+        <v>8.315928540256575</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.277166227138586</v>
+        <v>8.277393299592362</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.277252702603352</v>
+        <v>8.277565521846086</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.26093680404281</v>
+        <v>8.261241774458162</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.270764797484881</v>
+        <v>8.271117879337728</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.304020127524096</v>
+        <v>8.304467299325552</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.324103306254578</v>
+        <v>8.324591389061572</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.230879128235738</v>
+        <v>8.231373698376562</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.142046098807622</v>
+        <v>8.142467955285348</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.051916745369756</v>
+        <v>8.052186059573319</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.008372489515086</v>
+        <v>8.008600268238547</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.965927286604655</v>
+        <v>7.966042390550264</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940899905700026</v>
+        <v>7.940978768361158</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945180060598854</v>
+        <v>7.945343158768218</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913770938862936</v>
+        <v>7.913850265970233</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887093472474816</v>
+        <v>7.887136503675896</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871541321078523</v>
+        <v>7.871611433277758</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.889817773384669</v>
+        <v>7.890005736554126</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.860713173003152</v>
+        <v>7.860978216622959</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.806605858550187</v>
+        <v>7.806910073371427</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.766145508938683</v>
+        <v>7.766445487203067</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.745732246994837</v>
+        <v>7.747869507887613</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.73324956736229</v>
+        <v>7.736515946949813</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.720657391233464</v>
+        <v>7.725115652852561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.695444482324149</v>
+        <v>7.701025460510853</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.645796889227965</v>
+        <v>7.653210404365542</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.600956399587054</v>
+        <v>7.609773448041062</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.556823987378845</v>
+        <v>7.566791910407449</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.529332026756461</v>
+        <v>7.540093121316492</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.498129532938563</v>
+        <v>7.511193649098249</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.473339428308197</v>
+        <v>7.486676200438829</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.456575787273013</v>
+        <v>7.471211399902421</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.440745472235392</v>
+        <v>7.457454460541735</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.425110001702889</v>
+        <v>7.4510079061082</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.478668806901401</v>
+        <v>7.522200050295462</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.766445487203067</v>
+        <v>7.774719460788251</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.747869507887613</v>
+        <v>7.753626500984119</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.736515946949813</v>
+        <v>7.74325293961143</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.725115652852561</v>
+        <v>7.733844214226375</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.701025460510853</v>
+        <v>7.712313281526442</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.653210404365542</v>
+        <v>7.665914953111936</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.609773448041062</v>
+        <v>7.623930114303391</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.566791910407449</v>
+        <v>7.581705315896709</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.540093121316492</v>
+        <v>7.556852352872543</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.511193649098249</v>
+        <v>7.532698549360167</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.486676200438829</v>
+        <v>7.504159061092845</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.471211399902421</v>
+        <v>7.478298125499184</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.457454460541735</v>
+        <v>7.45260228520746</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.4510079061082</v>
+        <v>7.425356866791331</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,15 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.522200050295462</v>
+        <v>7.532674303857084</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>7.563134973666759</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370293981578588</v>
+        <v>8.37028999920026</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367924498849611</v>
+        <v>8.367927896942252</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394606662475276</v>
+        <v>8.394599824799441</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410816578299851</v>
+        <v>8.41081322926293</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196420938991</v>
+        <v>8.424196566301156</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428382734497502</v>
+        <v>8.428385939225258</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427112392069517</v>
+        <v>8.427118637921632</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431507914114588</v>
+        <v>8.431517868707676</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429203657337721</v>
+        <v>8.429236667856152</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439135879475003</v>
+        <v>8.439171763652404</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445606363700119</v>
+        <v>8.445645127708513</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438749510543069</v>
+        <v>8.438787955082971</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418524565739544</v>
+        <v>8.41856577865857</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400629162221314</v>
+        <v>8.400684121025465</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372904120348412</v>
+        <v>8.372952382864497</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335199159631252</v>
+        <v>8.335251648882128</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279562289301889</v>
+        <v>8.279634906098448</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225030760921639</v>
+        <v>8.225108039711671</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17278776657326</v>
+        <v>8.172829199705449</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.129988808354517</v>
+        <v>8.130014615485956</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133366362599546</v>
+        <v>8.133357492734962</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186220260495505</v>
+        <v>8.186184065757404</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218862035879654</v>
+        <v>8.218754452765923</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203481315175409</v>
+        <v>8.203345936233058</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174980378646133</v>
+        <v>8.174834401464413</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130221926077388</v>
+        <v>8.130085844932875</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106732517221426</v>
+        <v>8.106623044300832</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.117016484134698</v>
+        <v>8.116935582852063</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164057947801879</v>
+        <v>8.164061078823678</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19190724418185</v>
+        <v>8.191932095747617</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172284198047958</v>
+        <v>8.172336769494958</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195432962799341</v>
+        <v>8.195558423552789</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.196405998335948</v>
+        <v>8.196649055706741</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22703778333689</v>
+        <v>8.227324495496845</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.315928540256575</v>
+        <v>8.316311908265833</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.277393299592362</v>
+        <v>8.27761318224487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.277565521846086</v>
+        <v>8.277868482065639</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.261241774458162</v>
+        <v>8.261536906413726</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.271117879337728</v>
+        <v>8.271459619084204</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.304467299325552</v>
+        <v>8.304900238910461</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.324591389061572</v>
+        <v>8.32506409202642</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.231373698376562</v>
+        <v>8.231853095341769</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.142467955285348</v>
+        <v>8.142877103624706</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.052186059573319</v>
+        <v>8.052447552726019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.008600268238547</v>
+        <v>8.008821528990058</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966042390550264</v>
+        <v>7.966154226882599</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.940978768361158</v>
+        <v>7.941055297210545</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945343158768218</v>
+        <v>7.945501366253595</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913850265970233</v>
+        <v>7.913926969075711</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887136503675896</v>
+        <v>7.887177781405782</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871611433277758</v>
+        <v>7.871678859161863</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890005736554126</v>
+        <v>7.890187661949623</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.860978216622959</v>
+        <v>7.861235016148455</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.806910073371427</v>
+        <v>7.807205470863422</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774719460788251</v>
+        <v>7.76673716268562</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753626500984119</v>
+        <v>7.748063258947755</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.74325293961143</v>
+        <v>7.738654791909685</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.733844214226375</v>
+        <v>7.728055462974751</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.712313281526442</v>
+        <v>7.704709625456666</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.665914953111936</v>
+        <v>7.658291687893284</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.623930114303391</v>
+        <v>7.616699673028426</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.581705315896709</v>
+        <v>7.57441040530005</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.556852352872543</v>
+        <v>7.548399712272888</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.532698549360167</v>
+        <v>7.521329566925695</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.504159061092845</v>
+        <v>7.498318049812474</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.478298125499184</v>
+        <v>7.482131155509258</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.45260228520746</v>
+        <v>7.469755079031157</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.425356866791331</v>
+        <v>7.468659070023988</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.532674303857084</v>
+        <v>7.541222596309622</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.563134973666759</v>
+        <v>7.596657577935288</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.76673716268562</v>
+        <v>7.774997191836128</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.748063258947755</v>
+        <v>7.753804340396368</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.738654791909685</v>
+        <v>7.745163696099977</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.728055462974751</v>
+        <v>7.736535787280594</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.704709625456666</v>
+        <v>7.715731030179343</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.658291687893284</v>
+        <v>7.67089734267513</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.616699673028426</v>
+        <v>7.630839904643435</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.57441040530005</v>
+        <v>7.589691797212128</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.548399712272888</v>
+        <v>7.565977015464143</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.521329566925695</v>
+        <v>7.543880106138363</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.498318049812474</v>
+        <v>7.517161323183275</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.482131155509258</v>
+        <v>7.491021121345374</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.469755079031157</v>
+        <v>7.466386438038739</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.468659070023988</v>
+        <v>7.445195295456312</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.541222596309622</v>
+        <v>7.541530900387005</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.596657577935288</v>
+        <v>7.564752356225528</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37028999920026</v>
+        <v>8.370286139327195</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367927896942252</v>
+        <v>8.367931188774428</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394599824799441</v>
+        <v>8.394593200297766</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41081322926293</v>
+        <v>8.410809985436803</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196566301156</v>
+        <v>8.424196708849268</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428385939225258</v>
+        <v>8.42838904664662</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427118637921632</v>
+        <v>8.427124692261394</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431517868707676</v>
+        <v>8.431527516349085</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429236667856152</v>
+        <v>8.429268654372489</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439171763652404</v>
+        <v>8.439206541566486</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445645127708513</v>
+        <v>8.445682697040738</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438787955082971</v>
+        <v>8.438825214606908</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41856577865857</v>
+        <v>8.418605730643673</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400684121025465</v>
+        <v>8.40073739427198</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.372952382864497</v>
+        <v>8.37299916266241</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335251648882128</v>
+        <v>8.33530254586055</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279634906098448</v>
+        <v>8.279705330352362</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225108039711671</v>
+        <v>8.225183024758046</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172829199705449</v>
+        <v>8.172869398351994</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130014615485956</v>
+        <v>8.1300396587949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133357492734962</v>
+        <v>8.133348965448517</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186184065757404</v>
+        <v>8.186149042395517</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218754452765923</v>
+        <v>8.218650143373033</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203345936233058</v>
+        <v>8.203214624422644</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174834401464413</v>
+        <v>8.174692760839491</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.130085844932875</v>
+        <v>8.129953735257931</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106623044300832</v>
+        <v>8.106516662039514</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116935582852063</v>
+        <v>8.116856825689943</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164061078823678</v>
+        <v>8.164063867825739</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191932095747617</v>
+        <v>8.191956150305849</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172336769494958</v>
+        <v>8.172387664580288</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195558423552789</v>
+        <v>8.195680212392151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.196649055706741</v>
+        <v>8.196885113717924</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.227324495496845</v>
+        <v>8.22760293199109</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.316311908265833</v>
+        <v>8.316684036359437</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27761318224487</v>
+        <v>8.277826210707971</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.277868482065639</v>
+        <v>8.278162041053184</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.261536906413726</v>
+        <v>8.261822666333837</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.271459619084204</v>
+        <v>8.271790552263989</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.304900238910461</v>
+        <v>8.30531961198291</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.32506409202642</v>
+        <v>8.325522128160657</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.231853095341769</v>
+        <v>8.232318003958191</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.142877103624706</v>
+        <v>8.143274106342394</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.052447552726019</v>
+        <v>8.052701557629929</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.008821528990058</v>
+        <v>8.009036545053412</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966154226882599</v>
+        <v>7.966262931960359</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941055297210545</v>
+        <v>7.941129594446694</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945501366253595</v>
+        <v>7.945654899482975</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.913926969075711</v>
+        <v>7.914001175579231</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887177781405782</v>
+        <v>7.887217404283552</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871678859161863</v>
+        <v>7.871743743617348</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890187661949623</v>
+        <v>7.890363834227025</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.861235016148455</v>
+        <v>7.861483948198053</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.807205470863422</v>
+        <v>7.807492423629553</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774997191836128</v>
+        <v>7.767020868060096</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753804340396368</v>
+        <v>7.74825226836021</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.745163696099977</v>
+        <v>7.740755594002965</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.736535787280594</v>
+        <v>7.730918062110575</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.715731030179343</v>
+        <v>7.708238130238249</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.67089734267513</v>
+        <v>7.66299536626912</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.630839904643435</v>
+        <v>7.622793676471478</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.589691797212128</v>
+        <v>7.581538661194059</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.565977015464143</v>
+        <v>7.556158822626651</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.543880106138363</v>
+        <v>7.530697480464417</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.517161323183275</v>
+        <v>7.509025225381909</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.491021121345374</v>
+        <v>7.492200353716271</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.466386438038739</v>
+        <v>7.480993676849605</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.445195295456312</v>
+        <v>7.483898282182132</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.541530900387005</v>
+        <v>7.555116034876596</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.564752356225528</v>
+        <v>7.600478008617188</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.767020868060096</v>
+        <v>7.775267287004266</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.74825226836021</v>
+        <v>7.753977887791955</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.740755594002965</v>
+        <v>7.747677137715715</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.730918062110575</v>
+        <v>7.739929572951043</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.708238130238249</v>
+        <v>7.719863110582495</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.66299536626912</v>
+        <v>7.676595789405089</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.622793676471478</v>
+        <v>7.638057662669409</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.581538661194059</v>
+        <v>7.598368438572058</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.556158822626651</v>
+        <v>7.57579787503798</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.530697480464417</v>
+        <v>7.555725262295169</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.509025225381909</v>
+        <v>7.530777126123565</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.492200353716271</v>
+        <v>7.504634568979748</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.480993676849605</v>
+        <v>7.481058411720818</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.483898282182132</v>
+        <v>7.465153039044515</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.555116034876596</v>
+        <v>7.553149500306457</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.600478008617188</v>
+        <v>7.577720100773208</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370286139327195</v>
+        <v>8.37028239639271</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367931188774428</v>
+        <v>8.367934379251651</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394593200297766</v>
+        <v>8.394586779159697</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410809985436803</v>
+        <v>8.410806841944545</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196708849268</v>
+        <v>8.424196848637614</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42838904664662</v>
+        <v>8.428392061125622</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427124692261394</v>
+        <v>8.427130563761663</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431527516349085</v>
+        <v>8.431536871015821</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429268654372489</v>
+        <v>8.42929966377827</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439206541566486</v>
+        <v>8.439240263579736</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445682697040738</v>
+        <v>8.445719126067431</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438825214606908</v>
+        <v>8.438861343054022</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418605730643673</v>
+        <v>8.418644478653965</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40073739427198</v>
+        <v>8.400789058277248</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37299916266241</v>
+        <v>8.37304452698365</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33530254586055</v>
+        <v>8.335351921875002</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279705330352362</v>
+        <v>8.279773659767706</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225183024758046</v>
+        <v>8.225255816438267</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172869398351994</v>
+        <v>8.172908416768486</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.1300396587949</v>
+        <v>8.130063971640155</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133348965448517</v>
+        <v>8.133340762114234</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186149042395517</v>
+        <v>8.186115134744792</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218650143373033</v>
+        <v>8.218548960811411</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203214624422644</v>
+        <v>8.203087199714215</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174692760839491</v>
+        <v>8.174555267086866</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129953735257931</v>
+        <v>8.129825426638275</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106516662039514</v>
+        <v>8.106413242698494</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116856825689943</v>
+        <v>8.116780130743836</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164063867825739</v>
+        <v>8.164066341014873</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191956150305849</v>
+        <v>8.191979444948927</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172387664580288</v>
+        <v>8.172436961431057</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195680212392151</v>
+        <v>8.195798486924485</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.196885113717924</v>
+        <v>8.197114468666518</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22760293199109</v>
+        <v>8.227873443996803</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.316684036359437</v>
+        <v>8.31704540968407</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.277826210707971</v>
+        <v>8.278032700057684</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.278162041053184</v>
+        <v>8.27844662875215</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.261822666333837</v>
+        <v>8.262099491739228</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.271790552263989</v>
+        <v>8.2721111813579</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.30531961198291</v>
+        <v>8.305726043546709</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.325522128160657</v>
+        <v>8.32596616722781</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.232318003958191</v>
+        <v>8.232769068622456</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.143274106342394</v>
+        <v>8.143659493430778</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.052701557629929</v>
+        <v>8.052948388655302</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009036545053412</v>
+        <v>8.009245574799955</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966262931960359</v>
+        <v>7.966368634707271</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941129594446694</v>
+        <v>7.941201756378845</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945654899482975</v>
+        <v>7.945803962316973</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914001175579231</v>
+        <v>7.914073004805243</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887217404283552</v>
+        <v>7.887255463954224</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871743743617348</v>
+        <v>7.87180622160276</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890363834227025</v>
+        <v>7.890534520520038</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.861483948198053</v>
+        <v>7.861725366919101</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.807492423629553</v>
+        <v>7.807771283894008</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775267287004266</v>
+        <v>7.767296918911304</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753977887791955</v>
+        <v>7.748436697518676</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.747677137715715</v>
+        <v>7.743428995801731</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.739929572951043</v>
+        <v>7.734416665173375</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.719863110582495</v>
+        <v>7.712394572155432</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.676595789405089</v>
+        <v>7.668163631954261</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.638057662669409</v>
+        <v>7.629420894862632</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.598368438572058</v>
+        <v>7.589150889481497</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.57579787503798</v>
+        <v>7.564411741782511</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.555725262295169</v>
+        <v>7.540513233983473</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.530777126123565</v>
+        <v>7.520138956274582</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.504634568979748</v>
+        <v>7.502867060649003</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.481058411720818</v>
+        <v>7.492823299766091</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.465153039044515</v>
+        <v>7.499355940178103</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.553149500306457</v>
+        <v>7.569749734288813</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.577720100773208</v>
+        <v>7.612727079719528</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.767296918911304</v>
+        <v>7.775530050853046</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.748436697518676</v>
+        <v>7.754147286061499</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.743428995801731</v>
+        <v>7.749116596018484</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.734416665173375</v>
+        <v>7.742004722261274</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.712394572155432</v>
+        <v>7.722452263742103</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.668163631954261</v>
+        <v>7.680186076694024</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.629420894862632</v>
+        <v>7.642943345724374</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.589150889481497</v>
+        <v>7.604507035186309</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.564411741782511</v>
+        <v>7.582809450321832</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.540513233983473</v>
+        <v>7.564178545078259</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.520138956274582</v>
+        <v>7.540561380507922</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.502867060649003</v>
+        <v>7.514007177478332</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.492823299766091</v>
+        <v>7.490927875889145</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.499355940178103</v>
+        <v>7.47765470592683</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.569749734288813</v>
+        <v>7.556285204126888</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.612727079719528</v>
+        <v>7.571846735577092</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37028239639271</v>
+        <v>8.370275240709429</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367934379251651</v>
+        <v>8.367940474299184</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394586779159697</v>
+        <v>8.394574510651024</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410806841944545</v>
+        <v>8.410800837914714</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196848637614</v>
+        <v>8.424197120157011</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428392061125622</v>
+        <v>8.428397827446176</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427130563761663</v>
+        <v>8.427141790394142</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431536871015821</v>
+        <v>8.431554753216638</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.42929966377827</v>
+        <v>8.429358924940942</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439240263579736</v>
+        <v>8.439304726523909</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445719126067431</v>
+        <v>8.445788764681632</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438861343054022</v>
+        <v>8.438930406593935</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418644478653965</v>
+        <v>8.418718573945325</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400789058277248</v>
+        <v>8.400887841484149</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37304452698365</v>
+        <v>8.3731312584439</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335351921875002</v>
+        <v>8.335446375590502</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279773659767706</v>
+        <v>8.279904396743833</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225255816438267</v>
+        <v>8.225395192827545</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172908416768486</v>
+        <v>8.172983114519411</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130063971640155</v>
+        <v>8.130110529953184</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133340762114234</v>
+        <v>8.133325259129286</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186115134744792</v>
+        <v>8.186050460933656</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218548960811411</v>
+        <v>8.218355431203058</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.203087199714215</v>
+        <v>8.202843342935031</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174555267086866</v>
+        <v>8.174292015000002</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129825426638275</v>
+        <v>8.129579578030441</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106413242698494</v>
+        <v>8.10621481568373</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116780130743836</v>
+        <v>8.116632619524513</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164066341014873</v>
+        <v>8.164070434134937</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.191979444948927</v>
+        <v>8.192023891864009</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172436961431057</v>
+        <v>8.172531049603228</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195798486924485</v>
+        <v>8.196025080015357</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.197114468666518</v>
+        <v>8.197554173742763</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.227873443996803</v>
+        <v>8.228392003213848</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.31704540968407</v>
+        <v>8.317737697477707</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278032700057684</v>
+        <v>8.278427228172911</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.27844662875215</v>
+        <v>8.278990483123001</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.262099491739228</v>
+        <v>8.262627957551281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.2721111813579</v>
+        <v>8.272723386709668</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.305726043546709</v>
+        <v>8.306502396697701</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.32596616722781</v>
+        <v>8.3268147360059</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.232769068622456</v>
+        <v>8.2336320588464</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.143659493430778</v>
+        <v>8.144397391693026</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.052948388655302</v>
+        <v>8.053421701760266</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009245574799955</v>
+        <v>8.009646640139641</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966368634707271</v>
+        <v>7.966571514668789</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941201756378845</v>
+        <v>7.941340032599649</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945803962316973</v>
+        <v>7.946089434716173</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914073004805243</v>
+        <v>7.914209972049471</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887255463954224</v>
+        <v>7.887327228860936</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.87180622160276</v>
+        <v>7.871924453184702</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890534520520038</v>
+        <v>7.890860423886505</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.861725366919101</v>
+        <v>7.862186978321771</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.807771283894008</v>
+        <v>7.808306041913504</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775530050853046</v>
+        <v>7.767827240158493</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754147286061499</v>
+        <v>7.748792428241737</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749116596018484</v>
+        <v>7.747315929069672</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.742004722261274</v>
+        <v>7.739900542820424</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.722452263742103</v>
+        <v>7.719301656608332</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.680186076694024</v>
+        <v>7.677175809646254</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.642943345724374</v>
+        <v>7.64125850355685</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.604507035186309</v>
+        <v>7.603065703032886</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.582809450321832</v>
+        <v>7.579704891548975</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.564178545078259</v>
+        <v>7.558611122064443</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.540561380507922</v>
+        <v>7.540491580291206</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.514007177478332</v>
+        <v>7.522947848031819</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.490927875889145</v>
+        <v>7.514839534068386</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.47765470592683</v>
+        <v>7.526336649991808</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.556285204126888</v>
+        <v>7.592445401748897</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.571846735577092</v>
+        <v>7.627412173391599</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370275240709429</v>
+        <v>8.370278765162347</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367940474299184</v>
+        <v>8.367937472982181</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394574510651024</v>
+        <v>8.394580552167263</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410800837914714</v>
+        <v>8.410803794205826</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197120157011</v>
+        <v>8.424196985721526</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428397827446176</v>
+        <v>8.428394986769268</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427141790394142</v>
+        <v>8.427136260579537</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431554753216638</v>
+        <v>8.431545945849249</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429358924940942</v>
+        <v>8.429329740146652</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439304726523909</v>
+        <v>8.439272977044377</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445788764681632</v>
+        <v>8.445754465910394</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438930406593935</v>
+        <v>8.438896391139929</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418718573945325</v>
+        <v>8.418682076270997</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400887841484149</v>
+        <v>8.400839184822212</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.3731312584439</v>
+        <v>8.373088539067439</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335446375590502</v>
+        <v>8.335399844042222</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279904396743833</v>
+        <v>8.279839986335308</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225395192827545</v>
+        <v>8.225326509372113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172983114519411</v>
+        <v>8.172946306083334</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130110529953184</v>
+        <v>8.130087585469258</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133325259129286</v>
+        <v>8.133332865393761</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186050460933656</v>
+        <v>8.186082290596191</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218355431203058</v>
+        <v>8.218450766832346</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202843342935031</v>
+        <v>8.202963492516826</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174292015000002</v>
+        <v>8.174421741382568</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129579578030441</v>
+        <v>8.129700758215437</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10621481568373</v>
+        <v>8.106312665400941</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116632619524513</v>
+        <v>8.116705420083026</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164070434134937</v>
+        <v>8.164068522428231</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192023891864009</v>
+        <v>8.192002014537616</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172531049603228</v>
+        <v>8.172484733437411</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196025080015357</v>
+        <v>8.195913395940181</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.197554173742763</v>
+        <v>8.197337400463383</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228392003213848</v>
+        <v>8.228136363219198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.317737697477707</v>
+        <v>8.317396485979319</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278427228172911</v>
+        <v>8.278232946378894</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.278990483123001</v>
+        <v>8.278722649339413</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.262627957551281</v>
+        <v>8.262367793443211</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.272723386709668</v>
+        <v>8.272421978290526</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.306502396697701</v>
+        <v>8.306120120956185</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.3268147360059</v>
+        <v>8.326396838962282</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.2336320588464</v>
+        <v>8.233206896228669</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.144397391693026</v>
+        <v>8.144033764660767</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053421701760266</v>
+        <v>8.053188342984917</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009646640139641</v>
+        <v>8.009448862680413</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966571514668789</v>
+        <v>7.966471457108614</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941340032599649</v>
+        <v>7.941271873845833</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946089434716173</v>
+        <v>7.945948746946754</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914209972049471</v>
+        <v>7.914142568629654</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887327228860936</v>
+        <v>7.887292045677823</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871924453184702</v>
+        <v>7.871866418966191</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890860423886505</v>
+        <v>7.890699971761345</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862186978321771</v>
+        <v>7.861959605630099</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808306041913504</v>
+        <v>7.808042384851517</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.767827240158493</v>
+        <v>7.775785772329221</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.748792428241737</v>
+        <v>7.754312672547901</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.747315929069672</v>
+        <v>7.751247279401535</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.739900542820424</v>
+        <v>7.74489282570737</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.719301656608332</v>
+        <v>7.725894729255324</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.677175809646254</v>
+        <v>7.684697975348191</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.64125850355685</v>
+        <v>7.648827865548578</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.603065703032886</v>
+        <v>7.611611855870589</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.579704891548975</v>
+        <v>7.590821771043345</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.558611122064443</v>
+        <v>7.573694062016007</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.540491580291206</v>
+        <v>7.551431795606431</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.522947848031819</v>
+        <v>7.524748758950825</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.514839534068386</v>
+        <v>7.502220893998702</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.526336649991808</v>
+        <v>7.491515718212295</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.592445401748897</v>
+        <v>7.56287458434247</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.627412173391599</v>
+        <v>7.575639963753626</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370278765162347</v>
+        <v>8.370271818392798</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367937472982181</v>
+        <v>8.36794338728096</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394580552167263</v>
+        <v>8.394568646449891</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410803794205826</v>
+        <v>8.410797969019441</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424196985721526</v>
+        <v>8.424197252000406</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428394986769268</v>
+        <v>8.428400586803619</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427136260579537</v>
+        <v>8.427147160441109</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431545945849249</v>
+        <v>8.431563304767289</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429329740146652</v>
+        <v>8.429387257204828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439272977044377</v>
+        <v>8.439335553995344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445754465910394</v>
+        <v>8.44582206770154</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438896391139929</v>
+        <v>8.438963434375546</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418682076270997</v>
+        <v>8.418754019221756</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400839184822212</v>
+        <v>8.400935091939736</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373088539067439</v>
+        <v>8.37317274120187</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335399844042222</v>
+        <v>8.335491576137013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279839986335308</v>
+        <v>8.279966972755934</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225326509372113</v>
+        <v>8.22546195109283</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.172946306083334</v>
+        <v>8.17301888759715</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130087585469258</v>
+        <v>8.130132833109828</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133332865393761</v>
+        <v>8.133317928246777</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186082290596191</v>
+        <v>8.186019599694644</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218450766832346</v>
+        <v>8.218262831135156</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202963492516826</v>
+        <v>8.202726600087846</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174421741382568</v>
+        <v>8.17416592860997</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129700758215437</v>
+        <v>8.12946174242046</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106312665400941</v>
+        <v>8.10611958508316</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116705420083026</v>
+        <v>8.116561658420974</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164068522428231</v>
+        <v>8.164072096416776</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192002014537616</v>
+        <v>8.192045107800592</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172484733437411</v>
+        <v>8.172575974866295</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.195913395940181</v>
+        <v>8.196133672065976</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.197337400463383</v>
+        <v>8.19776503888356</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228136363219198</v>
+        <v>8.228640660603419</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.317396485979319</v>
+        <v>8.318069452649516</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278232946378894</v>
+        <v>8.278615807641815</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.278722649339413</v>
+        <v>8.279250488274847</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.262367793443211</v>
+        <v>8.262880347284394</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.272421978290526</v>
+        <v>8.273015824065475</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.306120120956185</v>
+        <v>8.306873390929114</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.326396838962282</v>
+        <v>8.327220416590563</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.233206896228669</v>
+        <v>8.234045096173382</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.144033764660767</v>
+        <v>8.144750820015769</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053188342984917</v>
+        <v>8.053648731138377</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009448862680413</v>
+        <v>8.009839126461102</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966471457108614</v>
+        <v>7.966668916833381</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941271873845833</v>
+        <v>7.941406313657124</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.945948746946754</v>
+        <v>7.946226196875463</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914142568629654</v>
+        <v>7.91427531370116</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887292045677823</v>
+        <v>7.887361087537098</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871866418966191</v>
+        <v>7.871980434034086</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.890699971761345</v>
+        <v>7.891016098932593</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.861959605630099</v>
+        <v>7.862407781030837</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808042384851517</v>
+        <v>7.808562553859518</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775785772329221</v>
+        <v>7.768082065359084</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754312672547901</v>
+        <v>7.74896402097737</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751247279401535</v>
+        <v>7.749423455525258</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.74489282570737</v>
+        <v>7.74290460808929</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.725894729255324</v>
+        <v>7.723153529927113</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.684697975348191</v>
+        <v>7.682198638736662</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.648827865548578</v>
+        <v>7.647795273744806</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.611611855870589</v>
+        <v>7.61076013901509</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.590821771043345</v>
+        <v>7.588248560265086</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.573694062016007</v>
+        <v>7.568638218235039</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.551431795606431</v>
+        <v>7.551662510589613</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.524748758950825</v>
+        <v>7.534450910341506</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.502220893998702</v>
+        <v>7.527415498104459</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.491515718212295</v>
+        <v>7.541375358150779</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.56287458434247</v>
+        <v>7.606556847042015</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.575639963753626</v>
+        <v>7.641062757299154</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370271818392798</v>
+        <v>8.370268493836392</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36794338728096</v>
+        <v>8.367946215769393</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394568646449891</v>
+        <v>8.394562951874402</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410797969019441</v>
+        <v>8.410795183703945</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197252000406</v>
+        <v>8.424197381308113</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428400586803619</v>
+        <v>8.42840326828313</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427147160441109</v>
+        <v>8.427152377544129</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431563304767289</v>
+        <v>8.43157161148388</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429387257204828</v>
+        <v>8.429414773736269</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439335553995344</v>
+        <v>8.439365499034128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.44582206770154</v>
+        <v>8.445854417698435</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438963434375546</v>
+        <v>8.438995516872478</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418754019221756</v>
+        <v>8.418788456945455</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400935091939736</v>
+        <v>8.400980996242302</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37317274120187</v>
+        <v>8.373213040233853</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335491576137013</v>
+        <v>8.335535501941798</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279966972755934</v>
+        <v>8.280027791552831</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22546195109283</v>
+        <v>8.22552686381815</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17301888759715</v>
+        <v>8.173053668320877</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130132833109828</v>
+        <v>8.130154521417355</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133317928246777</v>
+        <v>8.133310858668445</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186019599694644</v>
+        <v>8.185989663551844</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218262831135156</v>
+        <v>8.218172850761192</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202726600087846</v>
+        <v>8.20261312148412</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.17416592860997</v>
+        <v>8.174043331637895</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12946174242046</v>
+        <v>8.129347115463567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10611958508316</v>
+        <v>8.106026870751839</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116561658420974</v>
+        <v>8.116492469461907</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164072096416776</v>
+        <v>8.164073527930288</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192045107800592</v>
+        <v>8.192065691436783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172575974866295</v>
+        <v>8.172619570391117</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196133672065976</v>
+        <v>8.196239297858181</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.19776503888356</v>
+        <v>8.197970232950354</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228640660603419</v>
+        <v>8.228882616198513</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.318069452649516</v>
+        <v>8.318392137806946</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278615807641815</v>
+        <v>8.27879893186204</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279250488274847</v>
+        <v>8.279503002415069</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.262880347284394</v>
+        <v>8.263125304643648</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.273015824065475</v>
+        <v>8.273299683509368</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.306873390929114</v>
+        <v>8.307233593801335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.327220416590563</v>
+        <v>8.327614406992058</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.234045096173382</v>
+        <v>8.234446517784624</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.144750820015769</v>
+        <v>8.145094470725354</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053648731138377</v>
+        <v>8.053869683267138</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009839126461102</v>
+        <v>8.01002652954717</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966668916833381</v>
+        <v>7.966763767378882</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941406313657124</v>
+        <v>7.941470793622767</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946226196875463</v>
+        <v>7.946359195273006</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91427531370116</v>
+        <v>7.914338686333048</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887361087537098</v>
+        <v>7.887393690801597</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871980434034086</v>
+        <v>7.872034464196388</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891016098932593</v>
+        <v>7.891167206042063</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862407781030837</v>
+        <v>7.862622293098848</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808562553859518</v>
+        <v>7.808812203902105</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.768082065359084</v>
+        <v>7.768330347399464</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.74896402097737</v>
+        <v>7.749131616313615</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749423455525258</v>
+        <v>7.74944435748417</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.74290460808929</v>
+        <v>7.744799356303307</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.723153529927113</v>
+        <v>7.725975233916637</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.682198638736662</v>
+        <v>7.686540935807719</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.647795273744806</v>
+        <v>7.652825272812791</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.61076013901509</v>
+        <v>7.616146753118565</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.588248560265086</v>
+        <v>7.595292554437135</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.568638218235039</v>
+        <v>7.576886392173002</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.551662510589613</v>
+        <v>7.560811954892202</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.534450910341506</v>
+        <v>7.544607497560611</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.527415498104459</v>
+        <v>7.53740805156464</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.541375358150779</v>
+        <v>7.552642334289368</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.606556847042015</v>
+        <v>7.615073022989606</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,15 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.641062757299154</v>
+        <v>7.645946421738653</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>7.652594001619324</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370268493836392</v>
+        <v>8.370271818392798</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367946215769393</v>
+        <v>8.36794338728096</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394562951874402</v>
+        <v>8.394568646449891</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410795183703945</v>
+        <v>8.410797969019441</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197381308113</v>
+        <v>8.424197252000406</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42840326828313</v>
+        <v>8.428400586803619</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427152377544129</v>
+        <v>8.427147160441109</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43157161148388</v>
+        <v>8.431563304767289</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429414773736269</v>
+        <v>8.429387257204828</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439365499034128</v>
+        <v>8.439335553995344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445854417698435</v>
+        <v>8.44582206770154</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438995516872478</v>
+        <v>8.438963434375546</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418788456945455</v>
+        <v>8.418754019221756</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400980996242302</v>
+        <v>8.400935091939736</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373213040233853</v>
+        <v>8.37317274120187</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335535501941798</v>
+        <v>8.335491576137013</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280027791552831</v>
+        <v>8.279966972755934</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22552686381815</v>
+        <v>8.22546195109283</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173053668320877</v>
+        <v>8.17301888759715</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130154521417355</v>
+        <v>8.130132833109828</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133310858668445</v>
+        <v>8.133317928246777</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185989663551844</v>
+        <v>8.186019599694644</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218172850761192</v>
+        <v>8.218262831135156</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.20261312148412</v>
+        <v>8.202726600087846</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174043331637895</v>
+        <v>8.17416592860997</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129347115463567</v>
+        <v>8.12946174242046</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106026870751839</v>
+        <v>8.10611958508316</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116492469461907</v>
+        <v>8.116561658420974</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164073527930288</v>
+        <v>8.164072096416776</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192065691436783</v>
+        <v>8.192045107800592</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172619570391117</v>
+        <v>8.172575974866295</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196239297858181</v>
+        <v>8.196133672065976</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.197970232950354</v>
+        <v>8.19776503888356</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228882616198513</v>
+        <v>8.228640660603419</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.318392137806946</v>
+        <v>8.318069452649516</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27879893186204</v>
+        <v>8.278615807641815</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279503002415069</v>
+        <v>8.279250488274847</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263125304643648</v>
+        <v>8.262880347284394</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.273299683509368</v>
+        <v>8.273015824065475</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.307233593801335</v>
+        <v>8.306873390929114</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.327614406992058</v>
+        <v>8.327220416590563</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.234446517784624</v>
+        <v>8.234045096173382</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.145094470725354</v>
+        <v>8.144750820015769</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053869683267138</v>
+        <v>8.053648731138377</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.01002652954717</v>
+        <v>8.009839126461102</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966763767378882</v>
+        <v>7.966668916833381</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941470793622767</v>
+        <v>7.941406313657124</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946359195273006</v>
+        <v>7.946226196875463</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914338686333048</v>
+        <v>7.91427531370116</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887393690801597</v>
+        <v>7.887361087537098</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872034464196388</v>
+        <v>7.871980434034086</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891167206042063</v>
+        <v>7.891016098932593</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862622293098848</v>
+        <v>7.862407781030837</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808812203902105</v>
+        <v>7.808562553859518</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.768330347399464</v>
+        <v>7.776277171572994</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749131616313615</v>
+        <v>7.754631933011612</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.74944435748417</v>
+        <v>7.751307876999628</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.744799356303307</v>
+        <v>7.748487547255159</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.725975233916637</v>
+        <v>7.730881383561769</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.686540935807719</v>
+        <v>7.691683085646767</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.652825272812791</v>
+        <v>7.654436999532216</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.616146753118565</v>
+        <v>7.61838096965861</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.595292554437135</v>
+        <v>7.600414070822953</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.576886392173002</v>
+        <v>7.584966935459857</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.560811954892202</v>
+        <v>7.564310686430144</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.544607497560611</v>
+        <v>7.539156521348925</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.53740805156464</v>
+        <v>7.514333821445565</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.552642334289368</v>
+        <v>7.506396990188579</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.615073022989606</v>
+        <v>7.566937037318044</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.645946421738653</v>
+        <v>7.576947453038761</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.652594001619324</v>
+        <v>7.574695793135904</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370271818392798</v>
+        <v>8.370265262910621</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36794338728096</v>
+        <v>8.367948963386842</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394568646449891</v>
+        <v>8.394557419673193</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410797969019441</v>
+        <v>8.410792478370981</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197252000406</v>
+        <v>8.424197508136375</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428400586803619</v>
+        <v>8.4284058751348</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427147160441109</v>
+        <v>8.427157448143861</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431563304767289</v>
+        <v>8.431579683729478</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429387257204828</v>
+        <v>8.42944150924658</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439335553995344</v>
+        <v>8.439394598983405</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.44582206770154</v>
+        <v>8.445885854991193</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438963434375546</v>
+        <v>8.439026694081871</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418754019221756</v>
+        <v>8.418821929450772</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400935091939736</v>
+        <v>8.401025611075774</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37317274120187</v>
+        <v>8.373252205460354</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335491576137013</v>
+        <v>8.335578206140584</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.279966972755934</v>
+        <v>8.280086926050432</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22546195109283</v>
+        <v>8.225590006329512</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17301888759715</v>
+        <v>8.173087497349957</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130132833109828</v>
+        <v>8.130175619918369</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133317928246777</v>
+        <v>8.133304037233437</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.186019599694644</v>
+        <v>8.185960611713877</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218262831135156</v>
+        <v>8.218085380654687</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202726600087846</v>
+        <v>8.202502772449009</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.17416592860997</v>
+        <v>8.173924081672883</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12946174242046</v>
+        <v>8.129235568467237</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10611958508316</v>
+        <v>8.10593657510417</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116561658420974</v>
+        <v>8.11642498848715</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164072096416776</v>
+        <v>8.164074745852428</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192045107800592</v>
+        <v>8.192085670204136</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172575974866295</v>
+        <v>8.172661893836919</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196133672065976</v>
+        <v>8.196342076478746</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.19776503888356</v>
+        <v>8.198169980561381</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228640660603419</v>
+        <v>8.229118136031239</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.318069452649516</v>
+        <v>8.318706118580604</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278615807641815</v>
+        <v>8.278976833858103</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279250488274847</v>
+        <v>8.279748344062359</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.262880347284394</v>
+        <v>8.263363151932253</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.273015824065475</v>
+        <v>8.273575335630714</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.306873390929114</v>
+        <v>8.30758346758336</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.327220416590563</v>
+        <v>8.327997203777535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.234045096173382</v>
+        <v>8.234836805197316</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.144750820015769</v>
+        <v>8.145428742164345</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053648731138377</v>
+        <v>8.05408479718627</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.009839126461102</v>
+        <v>8.010209046640842</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966668916833381</v>
+        <v>7.966856164772914</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941406313657124</v>
+        <v>7.941533544985528</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946226196875463</v>
+        <v>7.946488582991071</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91427531370116</v>
+        <v>7.91440017723639</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887361087537098</v>
+        <v>7.887425103205546</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.871980434034086</v>
+        <v>7.872086639811781</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891016098932593</v>
+        <v>7.891313942381233</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862407781030837</v>
+        <v>7.862830778327112</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808562553859518</v>
+        <v>7.809055260672364</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.776277171572994</v>
+        <v>7.768572330770744</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754631933011612</v>
+        <v>7.749295345563668</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751307876999628</v>
+        <v>7.749465559919653</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.748487547255159</v>
+        <v>7.746501459149794</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.730881383561769</v>
+        <v>7.728509839612218</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.691683085646767</v>
+        <v>7.690482738401487</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.654436999532216</v>
+        <v>7.657337163402577</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.61838096965861</v>
+        <v>7.621876308505657</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.600414070822953</v>
+        <v>7.60167196953538</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.584966935459857</v>
+        <v>7.584327255061428</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.564310686430144</v>
+        <v>7.56905744943287</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.539156521348925</v>
+        <v>7.553744578532605</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.514333821445565</v>
+        <v>7.546300114404682</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.506396990188579</v>
+        <v>7.562360630553152</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.566937037318044</v>
+        <v>7.621832883734399</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.576947453038761</v>
+        <v>7.649188561806591</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.574695793135904</v>
+        <v>7.651185405967354</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370265262910621</v>
+        <v>8.370268493836392</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367948963386842</v>
+        <v>8.367946215769393</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394557419673193</v>
+        <v>8.394562951874402</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410792478370981</v>
+        <v>8.410795183703945</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197508136375</v>
+        <v>8.424197381308113</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.4284058751348</v>
+        <v>8.42840326828313</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427157448143861</v>
+        <v>8.427152377544129</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431579683729478</v>
+        <v>8.43157161148388</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.42944150924658</v>
+        <v>8.429414773736269</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439394598983405</v>
+        <v>8.439365499034128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445885854991193</v>
+        <v>8.445854417698435</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439026694081871</v>
+        <v>8.438995516872478</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418821929450772</v>
+        <v>8.418788456945455</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401025611075774</v>
+        <v>8.400980996242302</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373252205460354</v>
+        <v>8.373213040233853</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335578206140584</v>
+        <v>8.335535501941798</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280086926050432</v>
+        <v>8.280027791552831</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225590006329512</v>
+        <v>8.22552686381815</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173087497349957</v>
+        <v>8.173053668320877</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130175619918369</v>
+        <v>8.130154521417355</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133304037233437</v>
+        <v>8.133310858668445</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185960611713877</v>
+        <v>8.185989663551844</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218085380654687</v>
+        <v>8.218172850761192</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202502772449009</v>
+        <v>8.20261312148412</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173924081672883</v>
+        <v>8.174043331637895</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129235568467237</v>
+        <v>8.129347115463567</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10593657510417</v>
+        <v>8.106026870751839</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11642498848715</v>
+        <v>8.116492469461907</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164074745852428</v>
+        <v>8.164073527930288</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192085670204136</v>
+        <v>8.192065691436783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172661893836919</v>
+        <v>8.172619570391117</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196342076478746</v>
+        <v>8.196239297858181</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198169980561381</v>
+        <v>8.197970232950354</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.229118136031239</v>
+        <v>8.228882616198513</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.318706118580604</v>
+        <v>8.318392137806946</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.278976833858103</v>
+        <v>8.27879893186204</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279748344062359</v>
+        <v>8.279503002415069</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263363151932253</v>
+        <v>8.263125304643648</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.273575335630714</v>
+        <v>8.273299683509368</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.30758346758336</v>
+        <v>8.307233593801335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.327997203777535</v>
+        <v>8.327614406992058</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.234836805197316</v>
+        <v>8.234446517784624</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.145428742164345</v>
+        <v>8.145094470725354</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.05408479718627</v>
+        <v>8.053869683267138</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010209046640842</v>
+        <v>8.01002652954717</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966856164772914</v>
+        <v>7.966763767378882</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941533544985528</v>
+        <v>7.941470793622767</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946488582991071</v>
+        <v>7.946359195273006</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91440017723639</v>
+        <v>7.914338686333048</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887425103205546</v>
+        <v>7.887393690801597</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872086639811781</v>
+        <v>7.872034464196388</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891313942381233</v>
+        <v>7.891167206042063</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862830778327112</v>
+        <v>7.862622293098848</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809055260672364</v>
+        <v>7.808812203902105</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.768572330770744</v>
+        <v>7.776513357471154</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749295345563668</v>
+        <v>7.754786055742644</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749465559919653</v>
+        <v>7.751338202358176</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.746501459149794</v>
+        <v>7.749578032506687</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.728509839612218</v>
+        <v>7.732489459947944</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.690482738401487</v>
+        <v>7.694063664563772</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.657337163402577</v>
+        <v>7.655994243235894</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.621876308505657</v>
+        <v>7.620022750983392</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.60167196953538</v>
+        <v>7.603614314535479</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.584327255061428</v>
+        <v>7.588703234117171</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.56905744943287</v>
+        <v>7.56860913021372</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.553744578532605</v>
+        <v>7.543969006125285</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.546300114404682</v>
+        <v>7.517768891466675</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.562360630553152</v>
+        <v>7.510074115938666</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.621832883734399</v>
+        <v>7.565253066446413</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.649188561806591</v>
+        <v>7.571986403193536</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.651185405967354</v>
+        <v>7.560206912422073</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370268493836392</v>
+        <v>8.370262121715228</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367946215769393</v>
+        <v>8.367951633551591</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394562951874402</v>
+        <v>8.394552043002202</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410795183703945</v>
+        <v>8.410789849626669</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197381308113</v>
+        <v>8.424197632541068</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42840326828313</v>
+        <v>8.428408410430404</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427152377544129</v>
+        <v>8.427162378324416</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43157161148388</v>
+        <v>8.431587531290587</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429414773736269</v>
+        <v>8.429467496506192</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439365499034128</v>
+        <v>8.439422889109187</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445854417698435</v>
+        <v>8.445916417656681</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.438995516872478</v>
+        <v>8.439057003776451</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418788456945455</v>
+        <v>8.418854476734435</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.400980996242302</v>
+        <v>8.401068989987571</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373213040233853</v>
+        <v>8.373290284035598</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335535501941798</v>
+        <v>8.33561973895856</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280027791552831</v>
+        <v>8.280144445189638</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22552686381815</v>
+        <v>8.225651449917585</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173053668320877</v>
+        <v>8.173120413156209</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130154521417355</v>
+        <v>8.130196152315737</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133310858668445</v>
+        <v>8.133297451625868</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185989663551844</v>
+        <v>8.185932405743134</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218172850761192</v>
+        <v>8.218000317389496</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.20261312148412</v>
+        <v>8.202395425596709</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.174043331637895</v>
+        <v>8.173808043923813</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129347115463567</v>
+        <v>8.12912697949659</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.106026870751839</v>
+        <v>8.105848605487941</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116492469461907</v>
+        <v>8.116359154311969</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164073527930288</v>
+        <v>8.16407576601161</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192065691436783</v>
+        <v>8.19210506999128</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172619570391117</v>
+        <v>8.172702999603343</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196239297858181</v>
+        <v>8.196442120769163</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.197970232950354</v>
+        <v>8.198364494689928</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.228882616198513</v>
+        <v>8.229347472309255</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.318392137806946</v>
+        <v>8.319011741279958</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27879893186204</v>
+        <v>8.279149733586273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279503002415069</v>
+        <v>8.279986813963475</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263125304643648</v>
+        <v>8.263594193148784</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.273299683509368</v>
+        <v>8.2738431300471</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.307233593801335</v>
+        <v>8.307923448609898</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.327614406992058</v>
+        <v>8.328369275866493</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.234446517784624</v>
+        <v>8.235216413768788</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.145094470725354</v>
+        <v>8.145754011429998</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.053869683267138</v>
+        <v>8.054294299660441</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.01002652954717</v>
+        <v>8.010386864993778</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966763767378882</v>
+        <v>7.966946202507486</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941470793622767</v>
+        <v>7.941594636391862</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946359195273006</v>
+        <v>7.946614504930683</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914338686333048</v>
+        <v>7.914459868639268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887393690801597</v>
+        <v>7.887455385113581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872034464196388</v>
+        <v>7.872137050980526</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891167206042063</v>
+        <v>7.891456493981679</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.862622293098848</v>
+        <v>7.863033486037489</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.808812203902105</v>
+        <v>7.809291979132901</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.776513357471154</v>
+        <v>7.768808248175858</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754786055742644</v>
+        <v>7.749455334767059</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751338202358176</v>
+        <v>7.749487017305175</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.749578032506687</v>
+        <v>7.747623370085652</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.732489459947944</v>
+        <v>7.730291530984857</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.694063664563772</v>
+        <v>7.693508882645331</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.655994243235894</v>
+        <v>7.660962771881521</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.620022750983392</v>
+        <v>7.626569609332847</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.603614314535479</v>
+        <v>7.606885246445288</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.588703234117171</v>
+        <v>7.59037102151726</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.56860913021372</v>
+        <v>7.575731012936632</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.543969006125285</v>
+        <v>7.561116115847444</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.517768891466675</v>
+        <v>7.553236135313301</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.510074115938666</v>
+        <v>7.569466482971075</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.565253066446413</v>
+        <v>7.62531852379623</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.571986403193536</v>
+        <v>7.648495824340932</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.560206912422073</v>
+        <v>7.641338250101344</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370262121715228</v>
+        <v>8.370259066563611</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367951633551591</v>
+        <v>8.367954229492014</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394552043002202</v>
+        <v>8.394546815396517</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410789849626669</v>
+        <v>8.410787294266338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197632541068</v>
+        <v>8.424197754577554</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428408410430404</v>
+        <v>8.428410877075464</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427162378324416</v>
+        <v>8.427167173837699</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431587531290587</v>
+        <v>8.431595163416716</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429467496506192</v>
+        <v>8.429492766478385</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439422889109187</v>
+        <v>8.439450402742734</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445916417656681</v>
+        <v>8.445946141683404</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439057003776451</v>
+        <v>8.439086481656979</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418854476734435</v>
+        <v>8.418886136614617</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401068989987571</v>
+        <v>8.40111118360247</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373290284035598</v>
+        <v>8.373327320536402</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33561973895856</v>
+        <v>8.335660147906804</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280144445189638</v>
+        <v>8.280200414203307</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225651449917585</v>
+        <v>8.225711262103761</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173120413156209</v>
+        <v>8.173152452168798</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130196152315737</v>
+        <v>8.130216141060874</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133297451625868</v>
+        <v>8.133291090309424</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185932405743134</v>
+        <v>8.185905009389019</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218000317389496</v>
+        <v>8.217917563134787</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202395425596709</v>
+        <v>8.202290960345195</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173808043923813</v>
+        <v>8.173695090718191</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12912697949659</v>
+        <v>8.129021232938939</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105848605487941</v>
+        <v>8.105762873879883</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116359154311969</v>
+        <v>8.116294908562999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16407576601161</v>
+        <v>8.164076603005809</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19210506999128</v>
+        <v>8.192123915249528</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172702999603343</v>
+        <v>8.172742939055865</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196442120769163</v>
+        <v>8.196539537726641</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198364494689928</v>
+        <v>8.198553977405002</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.229347472309255</v>
+        <v>8.229570864297319</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319011741279958</v>
+        <v>8.319309334148214</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279149733586273</v>
+        <v>8.279317838836858</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279986813963475</v>
+        <v>8.280218696313446</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263594193148784</v>
+        <v>8.263818715264163</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.2738431300471</v>
+        <v>8.274103396862422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.307923448609898</v>
+        <v>8.308253949068561</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.328369275866493</v>
+        <v>8.328731066422996</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.235216413768788</v>
+        <v>8.235585774443066</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.145754011429998</v>
+        <v>8.146070635765021</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054294299660441</v>
+        <v>8.054498405950259</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010386864993778</v>
+        <v>8.010560162485319</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966946202507486</v>
+        <v>7.967033969407627</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941594636391862</v>
+        <v>7.941654132897326</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946614504930683</v>
+        <v>7.946737098350364</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914459868639268</v>
+        <v>7.914517838067003</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887455385113581</v>
+        <v>7.887484593028946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872137050980526</v>
+        <v>7.872185782220174</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891456493981679</v>
+        <v>7.891595036511997</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863033486037489</v>
+        <v>7.863230652047895</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809291979132901</v>
+        <v>7.809522601424177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.768808248175858</v>
+        <v>7.769038321214556</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749455334767059</v>
+        <v>7.749611704918811</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749487017305175</v>
+        <v>7.749508688175791</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.747623370085652</v>
+        <v>7.748659524208881</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.730291530984857</v>
+        <v>7.731927431268522</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.693508882645331</v>
+        <v>7.696313117362228</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.660962771881521</v>
+        <v>7.664182484213473</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.626569609332847</v>
+        <v>7.630816911838298</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.606885246445288</v>
+        <v>7.611655031685583</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.59037102151726</v>
+        <v>7.595916440406436</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.575731012936632</v>
+        <v>7.581875832113518</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.561116115847444</v>
+        <v>7.567914417126842</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.553236135313301</v>
+        <v>7.559623699306156</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.569466482971075</v>
+        <v>7.575903924507521</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.62531852379623</v>
+        <v>7.628455311248596</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.648495824340932</v>
+        <v>7.648213911242907</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.641338250101344</v>
+        <v>7.637138379678568</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370259066563611</v>
+        <v>8.370256093968369</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367954229492014</v>
+        <v>8.367956754259577</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394546815396517</v>
+        <v>8.394541730744473</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410787294266338</v>
+        <v>8.41078480926153</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197754577554</v>
+        <v>8.424197874300539</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428410877075464</v>
+        <v>8.428413277820342</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427167173837699</v>
+        <v>8.427171840125764</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431595163416716</v>
+        <v>8.431602588856679</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429492766478385</v>
+        <v>8.429517348442099</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439450402742734</v>
+        <v>8.439477171411424</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445946141683404</v>
+        <v>8.445975061112705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439086481656979</v>
+        <v>8.439115161492367</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418886136614617</v>
+        <v>8.418916944877191</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40111118360247</v>
+        <v>8.401152239819185</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373327320536402</v>
+        <v>8.373363357135782</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335660147906804</v>
+        <v>8.33569947796305</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280200414203307</v>
+        <v>8.280254894861972</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225711262103761</v>
+        <v>8.225769506885456</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173152452168798</v>
+        <v>8.173183648907816</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130216141060874</v>
+        <v>8.13023560743512</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133291090309424</v>
+        <v>8.133284942467842</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185905009389019</v>
+        <v>8.18587838843515</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217917563134787</v>
+        <v>8.217837025282337</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202290960345195</v>
+        <v>8.202189262469112</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173695090718191</v>
+        <v>8.173585101039919</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129021232938939</v>
+        <v>8.12891821910133</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105762873879883</v>
+        <v>8.105679296603228</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116294908562999</v>
+        <v>8.116232195524319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164076603005809</v>
+        <v>8.164077270309058</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192123915249528</v>
+        <v>8.192142229090054</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172742939055865</v>
+        <v>8.17278176073291</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196539537726641</v>
+        <v>8.196634428874846</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198553977405002</v>
+        <v>8.198738620556551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.229570864297319</v>
+        <v>8.22978853913262</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319309334148214</v>
+        <v>8.319599208521025</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279317838836858</v>
+        <v>8.279481346062834</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280218696313446</v>
+        <v>8.280444259876756</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263818715264163</v>
+        <v>8.264036989393606</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274103396862422</v>
+        <v>8.274356448005326</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.308253949068561</v>
+        <v>8.308575358641743</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.328731066422996</v>
+        <v>8.329082994595076</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.235585774443066</v>
+        <v>8.23594529535978</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.146070635765021</v>
+        <v>8.146378953841003</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054498405950259</v>
+        <v>8.054697320526468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010560162485319</v>
+        <v>8.010729108196474</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967033969407627</v>
+        <v>7.967119549917439</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941654132897326</v>
+        <v>7.941712096198618</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946737098350364</v>
+        <v>7.946856493362883</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914517838067003</v>
+        <v>7.914574158672298</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887484593028946</v>
+        <v>7.887512779889345</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872185782220174</v>
+        <v>7.872232912882517</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891595036511997</v>
+        <v>7.891729735986472</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863230652047895</v>
+        <v>7.863422499570317</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809522601424177</v>
+        <v>7.809747357649758</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.769038321214556</v>
+        <v>7.76926276102259</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749611704918811</v>
+        <v>7.749764572190038</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749508688175791</v>
+        <v>7.749530534765007</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.748659524208881</v>
+        <v>7.750800282601181</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.731927431268522</v>
+        <v>7.734681530542983</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.696313117362228</v>
+        <v>7.70017495909804</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.664182484213473</v>
+        <v>7.669173042285875</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.630816911838298</v>
+        <v>7.635336095673361</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.611655031685583</v>
+        <v>7.616412601138205</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.595916440406436</v>
+        <v>7.601250573072605</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.581875832113518</v>
+        <v>7.587734398960661</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.567914417126842</v>
+        <v>7.57441402217097</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.559623699306156</v>
+        <v>7.565187318796315</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.575903924507521</v>
+        <v>7.581292136604779</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.628455311248596</v>
+        <v>7.630649027792076</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.648213911242907</v>
+        <v>7.647606905599048</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.637138379678568</v>
+        <v>7.635007263166639</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370256093968369</v>
+        <v>8.370253200628053</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367956754259577</v>
+        <v>8.367959210740798</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394541730744473</v>
+        <v>8.394536783263867</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41078480926153</v>
+        <v>8.41078239174805</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197874300539</v>
+        <v>8.424197991763972</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428413277820342</v>
+        <v>8.428415615270451</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427171840125764</v>
+        <v>8.427176382341401</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431602588856679</v>
+        <v>8.431609815892024</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429517348442099</v>
+        <v>8.429541270104876</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439477171411424</v>
+        <v>8.439503224959102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445975061112705</v>
+        <v>8.446003208168662</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439115161492367</v>
+        <v>8.439143075248566</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418916944877191</v>
+        <v>8.418946935410368</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401152239819185</v>
+        <v>8.401192203991345</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373363357135782</v>
+        <v>8.373398433762748</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33569947796305</v>
+        <v>8.335737771738209</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280254894861972</v>
+        <v>8.280307945700351</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225769506885456</v>
+        <v>8.22582624496256</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173183648907816</v>
+        <v>8.173214036107503</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.13023560743512</v>
+        <v>8.130254571624896</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133284942467842</v>
+        <v>8.133278997950711</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18587838843515</v>
+        <v>8.185852510559133</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217837025282337</v>
+        <v>8.217758616103175</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202189262469112</v>
+        <v>8.202090223687376</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173585101039919</v>
+        <v>8.173477960102449</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12891821910133</v>
+        <v>8.128817833838308</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105679296603228</v>
+        <v>8.105597794065421</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116232195524319</v>
+        <v>8.116170961993019</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164077270309058</v>
+        <v>8.164077780367698</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192142229090054</v>
+        <v>8.192160033373368</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17278176073291</v>
+        <v>8.172819510536357</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196634428874846</v>
+        <v>8.196726890606977</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198738620556551</v>
+        <v>8.198918606409929</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22978853913262</v>
+        <v>8.230000712579621</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319599208521025</v>
+        <v>8.319881659897485</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279481346062834</v>
+        <v>8.279640441141755</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280444259876756</v>
+        <v>8.280663759018784</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264036989393606</v>
+        <v>8.264249271873336</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274356448005326</v>
+        <v>8.274602578459316</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.308575358641743</v>
+        <v>8.30888804601681</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.329082994595076</v>
+        <v>8.329425457115375</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.23594529535978</v>
+        <v>8.236295363337982</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.146378953841003</v>
+        <v>8.146679286944106</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054697320526468</v>
+        <v>8.054891237732104</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010729108196474</v>
+        <v>8.010893862942662</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967119549917439</v>
+        <v>7.967203024365512</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941712096198618</v>
+        <v>7.941768584847853</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946856493362883</v>
+        <v>7.946972813393812</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914574158672298</v>
+        <v>7.914628899538098</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887512779889345</v>
+        <v>7.887539995336541</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872232912882517</v>
+        <v>7.872278517534323</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891729735986472</v>
+        <v>7.891860749416644</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863422499570317</v>
+        <v>7.863609240038445</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809747357649758</v>
+        <v>7.809966466605426</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.76926276102259</v>
+        <v>7.769481768868541</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749764572190038</v>
+        <v>7.749914048139985</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749530534765007</v>
+        <v>7.749552522676401</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750800282601181</v>
+        <v>7.752804287375852</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.734681530542983</v>
+        <v>7.737236139294901</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.70017495909804</v>
+        <v>7.703737868937933</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.669173042285875</v>
+        <v>7.673795044977674</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.635336095673361</v>
+        <v>7.639457680814716</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.616412601138205</v>
+        <v>7.620743132763669</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.601250573072605</v>
+        <v>7.606083928998629</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.587734398960661</v>
+        <v>7.59303600012751</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.57441402217097</v>
+        <v>7.58028690122863</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.565187318796315</v>
+        <v>7.570139476948988</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.581292136604779</v>
+        <v>7.585946583154238</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.630649027792076</v>
+        <v>7.632273078060065</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.647606905599048</v>
+        <v>7.646709548144758</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.635007263166639</v>
+        <v>7.632795977158539</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B112"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370253200628053</v>
+        <v>8.370262121715228</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367959210740798</v>
+        <v>8.367951633551591</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394536783263867</v>
+        <v>8.394552043002202</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41078239174805</v>
+        <v>8.410789849626669</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197991763972</v>
+        <v>8.424197632541068</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428415615270451</v>
+        <v>8.428408410430404</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427176382341401</v>
+        <v>8.427162378324416</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431609815892024</v>
+        <v>8.431587531290587</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429541270104876</v>
+        <v>8.429467496506192</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439503224959102</v>
+        <v>8.439422889109187</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446003208168662</v>
+        <v>8.445916417656681</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439143075248566</v>
+        <v>8.439057003776451</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418946935410368</v>
+        <v>8.418854476734435</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401192203991345</v>
+        <v>8.401068989987571</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373398433762748</v>
+        <v>8.373290284035598</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335737771738209</v>
+        <v>8.33561973895856</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280307945700351</v>
+        <v>8.280144445189638</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22582624496256</v>
+        <v>8.225651449917585</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173214036107503</v>
+        <v>8.173120413156209</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130254571624896</v>
+        <v>8.130196152315737</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133278997950711</v>
+        <v>8.133297451625868</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185852510559133</v>
+        <v>8.185932405743134</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217758616103175</v>
+        <v>8.218000317389496</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202090223687376</v>
+        <v>8.202395425596709</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173477960102449</v>
+        <v>8.173808043923813</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128817833838308</v>
+        <v>8.12912697949659</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105597794065421</v>
+        <v>8.105848605487941</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116170961993019</v>
+        <v>8.116359154311969</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164077780367698</v>
+        <v>8.16407576601161</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192160033373368</v>
+        <v>8.19210506999128</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172819510536357</v>
+        <v>8.172702999603343</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196726890606977</v>
+        <v>8.196442120769163</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198918606409929</v>
+        <v>8.198364494689928</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230000712579621</v>
+        <v>8.229347472309255</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319881659897485</v>
+        <v>8.319011741279958</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279640441141755</v>
+        <v>8.279149733586273</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280663759018784</v>
+        <v>8.279986813963475</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264249271873336</v>
+        <v>8.263594193148784</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274602578459316</v>
+        <v>8.2738431300471</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.30888804601681</v>
+        <v>8.307923448609898</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.329425457115375</v>
+        <v>8.328369275866493</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.236295363337982</v>
+        <v>8.235216413768788</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.146679286944106</v>
+        <v>8.145754011429998</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054891237732104</v>
+        <v>8.054294299660441</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010893862942662</v>
+        <v>8.010386864993778</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967203024365512</v>
+        <v>7.966946202507486</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941768584847853</v>
+        <v>7.941594636391862</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946972813393812</v>
+        <v>7.946614504930683</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914628899538098</v>
+        <v>7.914459868639268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887539995336541</v>
+        <v>7.887455385113581</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872278517534323</v>
+        <v>7.872137050980526</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891860749416644</v>
+        <v>7.891456493981679</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863609240038445</v>
+        <v>7.863033486037489</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809966466605426</v>
+        <v>7.809291979132901</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.769481768868541</v>
+        <v>7.776967879743528</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.749914048139985</v>
+        <v>7.755083872144338</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749552522676401</v>
+        <v>7.751398739211703</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752804287375852</v>
+        <v>7.750519990135514</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.737236139294901</v>
+        <v>7.73698294865515</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.703737868937933</v>
+        <v>7.701305677695052</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.673795044977674</v>
+        <v>7.664273985645389</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.639457680814716</v>
+        <v>7.630536060666383</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.620743132763669</v>
+        <v>7.614803262412499</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.606083928998629</v>
+        <v>7.602124292681411</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.59303600012751</v>
+        <v>7.583652872394193</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.58028690122863</v>
+        <v>7.560532642836487</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.570139476948988</v>
+        <v>7.534708928034026</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.585946583154238</v>
+        <v>7.52911815556604</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.632273078060065</v>
+        <v>7.579818324238036</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.646709548144758</v>
+        <v>7.592604277753742</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,15 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.632795977158539</v>
+        <v>7.607218145536201</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>7.698493145536201</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370262121715228</v>
+        <v>8.370250383414911</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367951633551591</v>
+        <v>8.367961601668227</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394552043002202</v>
+        <v>8.394531967480052</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410789849626669</v>
+        <v>8.410780039014998</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197632541068</v>
+        <v>8.424198107020946</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428408410430404</v>
+        <v>8.428417891895689</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427162378324416</v>
+        <v>8.427180805367097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431587531290587</v>
+        <v>8.43161685236781</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429467496506192</v>
+        <v>8.429564557706845</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439422889109187</v>
+        <v>8.439528591656957</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445916417656681</v>
+        <v>8.446030613377721</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439057003776451</v>
+        <v>8.43917025320728</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418854476734435</v>
+        <v>8.41897614032877</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401068989987571</v>
+        <v>8.401231119094202</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373290284035598</v>
+        <v>8.373432588249496</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33561973895856</v>
+        <v>8.335775069629911</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280144445189638</v>
+        <v>8.280359622226259</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225651449917585</v>
+        <v>8.225881533946696</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173120413156209</v>
+        <v>8.173243644830084</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130196152315737</v>
+        <v>8.130273052791111</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133297451625868</v>
+        <v>8.133273247223984</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185932405743134</v>
+        <v>8.185827345203752</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.218000317389496</v>
+        <v>8.217682252430915</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202395425596709</v>
+        <v>8.201993741282378</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173808043923813</v>
+        <v>8.173373558954301</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12912697949659</v>
+        <v>8.128719978207281</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105848605487941</v>
+        <v>8.10551829051437</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116359154311969</v>
+        <v>8.11611115714363</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16407576601161</v>
+        <v>8.164078144687405</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19210506999128</v>
+        <v>8.192177348791812</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172702999603343</v>
+        <v>8.172856231906922</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196442120769163</v>
+        <v>8.196817014503591</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198364494689928</v>
+        <v>8.199094108233977</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.229347472309255</v>
+        <v>8.230207589729474</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319011741279958</v>
+        <v>8.320156968931006</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279149733586273</v>
+        <v>8.27979530007709</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.279986813963475</v>
+        <v>8.280877434655734</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263594193148784</v>
+        <v>8.264455805250996</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.2738431300471</v>
+        <v>8.274842067394575</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.307923448609898</v>
+        <v>8.309192360276636</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.328369275866493</v>
+        <v>8.329758829775843</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.235216413768788</v>
+        <v>8.23663634524593</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.145754011429998</v>
+        <v>8.14697194007147</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054294299660441</v>
+        <v>8.055080342396913</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010386864993778</v>
+        <v>8.01105457976859</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.966946202507486</v>
+        <v>7.967284469211341</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941594636391862</v>
+        <v>7.941823654450587</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946614504930683</v>
+        <v>7.947086175605243</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914459868639268</v>
+        <v>7.914682125955677</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887455385113581</v>
+        <v>7.887566285962322</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872137050980526</v>
+        <v>7.872322666305396</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891456493981679</v>
+        <v>7.891988225410985</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863033486037489</v>
+        <v>7.863791073871199</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809291979132901</v>
+        <v>7.810180136456744</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.776967879743528</v>
+        <v>7.769695536711344</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755083872144338</v>
+        <v>7.750060239919489</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751398739211703</v>
+        <v>7.74957462058636</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750519990135514</v>
+        <v>7.752724546501561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.73698294865515</v>
+        <v>7.739861161088489</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.701305677695052</v>
+        <v>7.707936210536787</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.664273985645389</v>
+        <v>7.678807715449915</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.630536060666383</v>
+        <v>7.645469687990321</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.614803262412499</v>
+        <v>7.628445031543815</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.602124292681411</v>
+        <v>7.611747577653883</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.583652872394193</v>
+        <v>7.598862989263388</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.560532642836487</v>
+        <v>7.586428687598922</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.534708928034026</v>
+        <v>7.576735291267716</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.52911815556604</v>
+        <v>7.590400558962113</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.579818324238036</v>
+        <v>7.641750252623988</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.592604277753742</v>
+        <v>7.656832124922978</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.607218145536201</v>
+        <v>7.651496195538187</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.698493145536201</v>
+        <v>7.742771195538186</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370250383414911</v>
+        <v>8.370259066563611</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367961601668227</v>
+        <v>8.367954229492014</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394531967480052</v>
+        <v>8.394546815396517</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410780039014998</v>
+        <v>8.410787294266338</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198107020946</v>
+        <v>8.424197754577554</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428417891895689</v>
+        <v>8.428410877075464</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427180805367097</v>
+        <v>8.427167173837699</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43161685236781</v>
+        <v>8.431595163416716</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429564557706845</v>
+        <v>8.429492766478385</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439528591656957</v>
+        <v>8.439450402742734</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446030613377721</v>
+        <v>8.445946141683404</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43917025320728</v>
+        <v>8.439086481656979</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41897614032877</v>
+        <v>8.418886136614617</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401231119094202</v>
+        <v>8.40111118360247</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373432588249496</v>
+        <v>8.373327320536402</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335775069629911</v>
+        <v>8.335660147906804</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280359622226259</v>
+        <v>8.280200414203307</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225881533946696</v>
+        <v>8.225711262103761</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173243644830084</v>
+        <v>8.173152452168798</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130273052791111</v>
+        <v>8.130216141060874</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133273247223984</v>
+        <v>8.133291090309424</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185827345203752</v>
+        <v>8.185905009389019</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217682252430915</v>
+        <v>8.217917563134787</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201993741282378</v>
+        <v>8.202290960345195</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173373558954301</v>
+        <v>8.173695090718191</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128719978207281</v>
+        <v>8.129021232938939</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10551829051437</v>
+        <v>8.105762873879883</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11611115714363</v>
+        <v>8.116294908562999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078144687405</v>
+        <v>8.164076603005809</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192177348791812</v>
+        <v>8.192123915249528</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172856231906922</v>
+        <v>8.172742939055865</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196817014503591</v>
+        <v>8.196539537726641</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199094108233977</v>
+        <v>8.198553977405002</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230207589729474</v>
+        <v>8.229570864297319</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320156968931006</v>
+        <v>8.319309334148214</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.27979530007709</v>
+        <v>8.279317838836858</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280877434655734</v>
+        <v>8.280218696313446</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264455805250996</v>
+        <v>8.263818715264163</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274842067394575</v>
+        <v>8.274103396862422</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.309192360276636</v>
+        <v>8.308253949068561</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.329758829775843</v>
+        <v>8.328731066422996</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.23663634524593</v>
+        <v>8.235585774443066</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.14697194007147</v>
+        <v>8.146070635765021</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055080342396913</v>
+        <v>8.054498405950259</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.01105457976859</v>
+        <v>8.010560162485319</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967284469211341</v>
+        <v>7.967033969407627</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941823654450587</v>
+        <v>7.941654132897326</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947086175605243</v>
+        <v>7.946737098350364</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914682125955677</v>
+        <v>7.914517838067003</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887566285962322</v>
+        <v>7.887484593028946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872322666305396</v>
+        <v>7.872185782220174</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891988225410985</v>
+        <v>7.891595036511997</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863791073871199</v>
+        <v>7.863230652047895</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810180136456744</v>
+        <v>7.809522601424177</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.769695536711344</v>
+        <v>7.777186653352889</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750060239919489</v>
+        <v>7.755227786613771</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.74957462058636</v>
+        <v>7.751428894119748</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752724546501561</v>
+        <v>7.750461062978631</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.739861161088489</v>
+        <v>7.73984812869288</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.707936210536787</v>
+        <v>7.706057478100028</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.678807715449915</v>
+        <v>7.670394331424763</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.645469687990321</v>
+        <v>7.637790058731364</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.628445031543815</v>
+        <v>7.622709546568167</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.611747577653883</v>
+        <v>7.611253216688986</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.598862989263388</v>
+        <v>7.593777509958032</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.586428687598922</v>
+        <v>7.571585485613439</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.576735291267716</v>
+        <v>7.547123997839452</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.590400558962113</v>
+        <v>7.54288789720656</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.641750252623988</v>
+        <v>7.593225943176241</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.656832124922978</v>
+        <v>7.611694089301509</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.651496195538187</v>
+        <v>7.641589925506411</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.742771195538186</v>
+        <v>7.73286492550641</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370259066563611</v>
+        <v>8.370247639363633</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367954229492014</v>
+        <v>8.367963929630591</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394546815396517</v>
+        <v>8.39452727820578</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410787294266338</v>
+        <v>8.410777748494649</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197754577554</v>
+        <v>8.424198220123639</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428410877075464</v>
+        <v>8.428420110039127</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427167173837699</v>
+        <v>8.427185113832529</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431595163416716</v>
+        <v>8.431623705720972</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429492766478385</v>
+        <v>8.429587236116548</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439450402742734</v>
+        <v>8.439553298305736</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445946141683404</v>
+        <v>8.446057305679011</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439086481656979</v>
+        <v>8.439196724075408</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418886136614617</v>
+        <v>8.419004590087912</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40111118360247</v>
+        <v>8.401269025878459</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373327320536402</v>
+        <v>8.373465856467186</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335660147906804</v>
+        <v>8.33581140996429</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280200414203307</v>
+        <v>8.280409977113603</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225711262103761</v>
+        <v>8.225935428554761</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173152452168798</v>
+        <v>8.17327250457101</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130216141060874</v>
+        <v>8.130291069133378</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133291090309424</v>
+        <v>8.133267681324821</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185905009389019</v>
+        <v>8.185802863458484</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217917563134787</v>
+        <v>8.217607855369405</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202290960345195</v>
+        <v>8.201899717748038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173695090718191</v>
+        <v>8.173271794114068</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.129021232938939</v>
+        <v>8.128624558149093</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105762873879883</v>
+        <v>8.105440713811781</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116294908562999</v>
+        <v>8.116052732400831</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164076603005809</v>
+        <v>8.164078373911995</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192123915249528</v>
+        <v>8.192194194945669</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172742939055865</v>
+        <v>8.172891965985828</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196539537726641</v>
+        <v>8.196904887627245</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198553977405002</v>
+        <v>8.199265290846551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.229570864297319</v>
+        <v>8.230409365648795</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319309334148214</v>
+        <v>8.320425402347004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279317838836858</v>
+        <v>8.279946089644552</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280218696313446</v>
+        <v>8.281085515130469</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.263818715264163</v>
+        <v>8.264656819197731</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274103396862422</v>
+        <v>8.275075179210527</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.308253949068561</v>
+        <v>8.309488632181456</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.328731066422996</v>
+        <v>8.330083468787794</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.235585774443066</v>
+        <v>8.236968589266992</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.146070635765021</v>
+        <v>8.147257202946092</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054498405950259</v>
+        <v>8.055264810407994</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010560162485319</v>
+        <v>8.011211404408309</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967033969407627</v>
+        <v>7.967363957274392</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941654132897326</v>
+        <v>7.941877357849066</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946737098350364</v>
+        <v>7.947196691287732</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914517838067003</v>
+        <v>7.914733899680325</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887484593028946</v>
+        <v>7.887591695533189</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872185782220174</v>
+        <v>7.872365425207197</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891595036511997</v>
+        <v>7.892112304727459</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863230652047895</v>
+        <v>7.863968191177897</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809522601424177</v>
+        <v>7.810388565369134</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.777186653352889</v>
+        <v>7.769904247721442</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755227786613771</v>
+        <v>7.750203250465955</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751428894119748</v>
+        <v>7.749596799974789</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750461062978631</v>
+        <v>7.752647262661492</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.73984812869288</v>
+        <v>7.742367594122019</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.706057478100028</v>
+        <v>7.711915978756396</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.670394331424763</v>
+        <v>7.68355673572826</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.637790058731364</v>
+        <v>7.650704701272371</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.622709546568167</v>
+        <v>7.633073649095167</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.611253216688986</v>
+        <v>7.616718860827442</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.593777509958032</v>
+        <v>7.604034746626541</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.571585485613439</v>
+        <v>7.591919092666979</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.547123997839452</v>
+        <v>7.582638884315262</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.54288789720656</v>
+        <v>7.594195323964978</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.593225943176241</v>
+        <v>7.65011991776038</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.611694089301509</v>
+        <v>7.66548476177239</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.641589925506411</v>
+        <v>7.665542152619807</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.73286492550641</v>
+        <v>7.747129501523514</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370247639363633</v>
+        <v>8.370256093968369</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367963929630591</v>
+        <v>8.367956754259577</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39452727820578</v>
+        <v>8.394541730744473</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410777748494649</v>
+        <v>8.41078480926153</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198220123639</v>
+        <v>8.424197874300539</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428420110039127</v>
+        <v>8.428413277820342</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427185113832529</v>
+        <v>8.427171840125764</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431623705720972</v>
+        <v>8.431602588856679</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429587236116548</v>
+        <v>8.429517348442099</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439553298305736</v>
+        <v>8.439477171411424</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446057305679011</v>
+        <v>8.445975061112705</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439196724075408</v>
+        <v>8.439115161492367</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419004590087912</v>
+        <v>8.418916944877191</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401269025878459</v>
+        <v>8.401152239819185</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373465856467186</v>
+        <v>8.373363357135782</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33581140996429</v>
+        <v>8.33569947796305</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280409977113603</v>
+        <v>8.280254894861972</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225935428554761</v>
+        <v>8.225769506885456</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17327250457101</v>
+        <v>8.173183648907816</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130291069133378</v>
+        <v>8.13023560743512</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133267681324821</v>
+        <v>8.133284942467842</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185802863458484</v>
+        <v>8.18587838843515</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217607855369405</v>
+        <v>8.217837025282337</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201899717748038</v>
+        <v>8.202189262469112</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173271794114068</v>
+        <v>8.173585101039919</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128624558149093</v>
+        <v>8.12891821910133</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105440713811781</v>
+        <v>8.105679296603228</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116052732400831</v>
+        <v>8.116232195524319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078373911995</v>
+        <v>8.164077270309058</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192194194945669</v>
+        <v>8.192142229090054</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172891965985828</v>
+        <v>8.17278176073291</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196904887627245</v>
+        <v>8.196634428874846</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199265290846551</v>
+        <v>8.198738620556551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230409365648795</v>
+        <v>8.22978853913262</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320425402347004</v>
+        <v>8.319599208521025</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279946089644552</v>
+        <v>8.279481346062834</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.281085515130469</v>
+        <v>8.280444259876756</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264656819197731</v>
+        <v>8.264036989393606</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275075179210527</v>
+        <v>8.274356448005326</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.309488632181456</v>
+        <v>8.308575358641743</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.330083468787794</v>
+        <v>8.329082994595076</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.236968589266992</v>
+        <v>8.23594529535978</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.147257202946092</v>
+        <v>8.146378953841003</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055264810407994</v>
+        <v>8.054697320526468</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011211404408309</v>
+        <v>8.010729108196474</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967363957274392</v>
+        <v>7.967119549917439</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941877357849066</v>
+        <v>7.941712096198618</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947196691287732</v>
+        <v>7.946856493362883</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914733899680325</v>
+        <v>7.914574158672298</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887591695533189</v>
+        <v>7.887512779889345</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872365425207197</v>
+        <v>7.872232912882517</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892112304727459</v>
+        <v>7.891729735986472</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863968191177897</v>
+        <v>7.863422499570317</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810388565369134</v>
+        <v>7.809747357649758</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.769904247721442</v>
+        <v>7.777400042779357</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750203250465955</v>
+        <v>7.755368512013666</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749596799974789</v>
+        <v>7.751458940546103</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752647262661492</v>
+        <v>7.750404163346989</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.742367594122019</v>
+        <v>7.744705919627145</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.711915978756396</v>
+        <v>7.713268864452568</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.68355673572826</v>
+        <v>7.679487766587059</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.650704701272371</v>
+        <v>7.649089680993385</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.633073649095167</v>
+        <v>7.634571151822058</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.616718860827442</v>
+        <v>7.625012831143881</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.604034746626541</v>
+        <v>7.608994279432913</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.591919092666979</v>
+        <v>7.588286667475481</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.582638884315262</v>
+        <v>7.565900920036071</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.594195323964978</v>
+        <v>7.565399414076925</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.65011991776038</v>
+        <v>7.617512590079206</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.66548476177239</v>
+        <v>7.644831519133285</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.665542152619807</v>
+        <v>7.694810734084847</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.747129501523514</v>
+        <v>7.881405209145212</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370256093968369</v>
+        <v>8.370244965660927</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367956754259577</v>
+        <v>8.367966197082113</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394541730744473</v>
+        <v>8.394522710522581</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41078480926153</v>
+        <v>8.410775517753128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424197874300539</v>
+        <v>8.424198331123247</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428413277820342</v>
+        <v>8.428422271925051</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427171840125764</v>
+        <v>8.427189312130716</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431602588856679</v>
+        <v>8.431630383006528</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429517348442099</v>
+        <v>8.429609328919369</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439477171411424</v>
+        <v>8.439577370330097</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.445975061112705</v>
+        <v>8.446083312526163</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439115161492367</v>
+        <v>8.439222515086101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.418916944877191</v>
+        <v>8.419032313589927</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401152239819185</v>
+        <v>8.401305963012284</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373363357135782</v>
+        <v>8.373498272451323</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33569947796305</v>
+        <v>8.335846829126975</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280254894861972</v>
+        <v>8.280459060380792</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225769506885456</v>
+        <v>8.225987980788132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173183648907816</v>
+        <v>8.173300643356372</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.13023560743512</v>
+        <v>8.13030863794949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133284942467842</v>
+        <v>8.133262291820232</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18587838843515</v>
+        <v>8.185779037950438</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217837025282337</v>
+        <v>8.217535350022539</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.202189262469112</v>
+        <v>8.201808060464172</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173585101039919</v>
+        <v>8.173172567232378</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12891821910133</v>
+        <v>8.128531484191765</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105679296603228</v>
+        <v>8.105364995222144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116232195524319</v>
+        <v>8.115995641319911</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164077270309058</v>
+        <v>8.164078477894876</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192142229090054</v>
+        <v>8.192210590413477</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17278176073291</v>
+        <v>8.172926751763978</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196634428874846</v>
+        <v>8.196990592795906</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.198738620556551</v>
+        <v>8.199432311121065</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.22978853913262</v>
+        <v>8.230606225981855</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.319599208521025</v>
+        <v>8.320687213793541</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279481346062834</v>
+        <v>8.280092967988359</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.280444259876756</v>
+        <v>8.281288217020883</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264036989393606</v>
+        <v>8.264852531348971</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.274356448005326</v>
+        <v>8.275302164497205</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.308575358641743</v>
+        <v>8.30977717535171</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.329082994595076</v>
+        <v>8.330399712037599</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.23594529535978</v>
+        <v>8.237292426070633</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.146378953841003</v>
+        <v>8.147535350957096</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.054697320526468</v>
+        <v>8.05544480924018</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.010729108196474</v>
+        <v>8.011364475713254</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967119549917439</v>
+        <v>7.967441557947102</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941712096198618</v>
+        <v>7.941929745291956</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.946856493362883</v>
+        <v>7.9473044662232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914574158672298</v>
+        <v>7.914784279166691</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887512779889345</v>
+        <v>7.887616265195869</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872232912882517</v>
+        <v>7.872406856424794</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.891729735986472</v>
+        <v>7.892233120783216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863422499570317</v>
+        <v>7.864140772410122</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.809747357649758</v>
+        <v>7.810591942094305</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.777400042779357</v>
+        <v>7.770108076768167</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755368512013666</v>
+        <v>7.750343178689998</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751458940546103</v>
+        <v>7.749619034880949</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750404163346989</v>
+        <v>7.752572330994398</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.744705919627145</v>
+        <v>7.7467387014027</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.713268864452568</v>
+        <v>7.718133454036489</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.679487766587059</v>
+        <v>7.690987575506782</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.649089680993385</v>
+        <v>7.659349422848816</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.634571151822058</v>
+        <v>7.641505978302179</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.625012831143881</v>
+        <v>7.626108348721607</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.608994279432913</v>
+        <v>7.614154255569104</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.588286667475481</v>
+        <v>7.602899268774628</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.565900920036071</v>
+        <v>7.594706236773494</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.565399414076925</v>
+        <v>7.606460666241971</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.617512590079206</v>
+        <v>7.665041370182161</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.644831519133285</v>
+        <v>7.682432634299844</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.694810734084847</v>
+        <v>7.69184509998898</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.881405209145212</v>
+        <v>7.792174774789556</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370244965660927</v>
+        <v>8.370242359635911</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367966197082113</v>
+        <v>8.367968406351146</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394522710522581</v>
+        <v>8.394518259763593</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410775517753128</v>
+        <v>8.410773344481811</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198331123247</v>
+        <v>8.424198440069947</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428422271925051</v>
+        <v>8.428424379666383</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427189312130716</v>
+        <v>8.427193404432943</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431630383006528</v>
+        <v>8.431636890921776</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429609328919369</v>
+        <v>8.4296308584992</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439577370330097</v>
+        <v>8.439600831865773</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446083312526163</v>
+        <v>8.446108659981393</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439222515086101</v>
+        <v>8.439247652092082</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419032313589927</v>
+        <v>8.419059338281308</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401305963012284</v>
+        <v>8.401341967212593</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373498272451323</v>
+        <v>8.373529868517618</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335846829126975</v>
+        <v>8.33588136168432</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280459060380792</v>
+        <v>8.280506919555851</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225987980788132</v>
+        <v>8.22603924009873</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173300643356372</v>
+        <v>8.173328087833129</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.13030863794949</v>
+        <v>8.130325775690499</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133262291820232</v>
+        <v>8.133257070769261</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185779037950438</v>
+        <v>8.185755842743767</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217535350022539</v>
+        <v>8.217464665244281</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201808060464172</v>
+        <v>8.201718681394905</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173172567232378</v>
+        <v>8.173075784778568</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128531484191765</v>
+        <v>8.128440671175429</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105364995222144</v>
+        <v>8.1052910692162</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115995641319911</v>
+        <v>8.115939839474454</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078477894876</v>
+        <v>8.164078465763899</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192210590413477</v>
+        <v>8.192226552817031</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172926751763978</v>
+        <v>8.172960626219723</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196990592795906</v>
+        <v>8.197074208836906</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199432311121065</v>
+        <v>8.199595318457206</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230606225981855</v>
+        <v>8.230798347510159</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320687213793541</v>
+        <v>8.320942644630616</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280092967988359</v>
+        <v>8.280236085171907</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.281288217020883</v>
+        <v>8.28148574588681</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264852531348971</v>
+        <v>8.265043148080416</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275302164497205</v>
+        <v>8.275523260922707</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.30977717535171</v>
+        <v>8.310058287360722</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.330399712037599</v>
+        <v>8.330707880247214</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.237292426070633</v>
+        <v>8.237608169896728</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.147535350957096</v>
+        <v>8.147806646031704</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.05544480924018</v>
+        <v>8.055620498449439</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011364475713254</v>
+        <v>8.011513926050812</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967441557947102</v>
+        <v>7.967517337393246</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941929745291956</v>
+        <v>7.94198086459167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.9473044662232</v>
+        <v>7.947409601021278</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914784279166691</v>
+        <v>7.91483331978564</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887616265195869</v>
+        <v>7.887640033665451</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872406856424794</v>
+        <v>7.872447018584723</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892233120783216</v>
+        <v>7.892350800125198</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864140772410122</v>
+        <v>7.864308988964962</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810591942094305</v>
+        <v>7.810790446516419</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.770108076768167</v>
+        <v>7.770307190875852</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750343178689998</v>
+        <v>7.750480119653932</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749619034880949</v>
+        <v>7.749641301681843</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752572330994398</v>
+        <v>7.752499652253153</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.7467387014027</v>
+        <v>7.75056476295763</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.718133454036489</v>
+        <v>7.723618667279421</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.690987575506782</v>
+        <v>7.697624276917567</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.659349422848816</v>
+        <v>7.667111685741834</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.641505978302179</v>
+        <v>7.648754120023737</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.626108348721607</v>
+        <v>7.63407872249736</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.614154255569104</v>
+        <v>7.622661388584731</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.602899268774628</v>
+        <v>7.612060695813772</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.594706236773494</v>
+        <v>7.604691269159674</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.606460666241971</v>
+        <v>7.619036233022822</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.665041370182161</v>
+        <v>7.676929741962855</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.682432634299844</v>
+        <v>7.695361619757389</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.69184509998898</v>
+        <v>7.709984788319955</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.792174774789556</v>
+        <v>7.807848231016945</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370242359635911</v>
+        <v>8.370239818751212</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367968406351146</v>
+        <v>8.367970559648128</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394518259763593</v>
+        <v>8.394513921497673</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410773344481811</v>
+        <v>8.410771226489366</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198440069947</v>
+        <v>8.424198547012862</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428424379666383</v>
+        <v>8.428426435271566</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427193404432943</v>
+        <v>8.427197394702572</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431636890921776</v>
+        <v>8.431643235828666</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.4296308584992</v>
+        <v>8.429651846113964</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439600831865773</v>
+        <v>8.43962370584023</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446108659981393</v>
+        <v>8.446133372802533</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439247652092082</v>
+        <v>8.439272159652017</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419059338281308</v>
+        <v>8.419085690243357</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401341967212593</v>
+        <v>8.401377073366547</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373529868517618</v>
+        <v>8.373560675369202</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33588136168432</v>
+        <v>8.335915040495607</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280506919555851</v>
+        <v>8.280553599829366</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22603924009873</v>
+        <v>8.226089253543108</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173328087833129</v>
+        <v>8.173354863352802</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130325775690499</v>
+        <v>8.130342498011867</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133257070769261</v>
+        <v>8.133252010688286</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185755842743767</v>
+        <v>8.18573325324691</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217464665244281</v>
+        <v>8.217395733407194</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201718681394905</v>
+        <v>8.201631496809114</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173075784778568</v>
+        <v>8.172981357749954</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128440671175429</v>
+        <v>8.128352037996713</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.1052910692162</v>
+        <v>8.105218873287738</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115939839474454</v>
+        <v>8.115885284350789</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078465763899</v>
+        <v>8.164078345980268</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192226552817031</v>
+        <v>8.192242098881531</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172960626219723</v>
+        <v>8.172993624446253</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197074208836906</v>
+        <v>8.197155810822974</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199595318457206</v>
+        <v>8.19975445521875</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230798347510159</v>
+        <v>8.230985898672763</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320942644630616</v>
+        <v>8.32119192466312</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280236085171907</v>
+        <v>8.280375583686862</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28148574588681</v>
+        <v>8.28167829696082</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265043148080416</v>
+        <v>8.265228865224868</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275523260922707</v>
+        <v>8.275738694053262</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.310058287360722</v>
+        <v>8.310332250745059</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.330707880247214</v>
+        <v>8.331008278047824</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.237608169896728</v>
+        <v>8.23791611956052</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.147806646031704</v>
+        <v>8.148071337444577</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055620498449439</v>
+        <v>8.055792030132226</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011513926050812</v>
+        <v>8.011659881675754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967517337393246</v>
+        <v>7.967591358732682</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94198086459167</v>
+        <v>7.942030761270409</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947409601021278</v>
+        <v>7.94751219143131</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91483331978564</v>
+        <v>7.914881074024281</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887640033665451</v>
+        <v>7.88766303739789</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872447018584723</v>
+        <v>7.872485967001</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892350800125198</v>
+        <v>7.892465462865164</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864308988964962</v>
+        <v>7.864473003743748</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810790446516419</v>
+        <v>7.810984250161151</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.770307190875852</v>
+        <v>7.770501749650848</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750480119653932</v>
+        <v>7.750614164742316</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749641301681843</v>
+        <v>7.749663578890964</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752499652253153</v>
+        <v>7.752429132447826</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75056476295763</v>
+        <v>7.753977750960217</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.723618667279421</v>
+        <v>7.728814100897104</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.697624276917567</v>
+        <v>7.704328269238035</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.667111685741834</v>
+        <v>7.675791201130673</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.648754120023737</v>
+        <v>7.658132485046563</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.63407872249736</v>
+        <v>7.645053302050734</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.622661388584731</v>
+        <v>7.634831310081379</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.612060695813772</v>
+        <v>7.625314370488031</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.604691269159674</v>
+        <v>7.619101660652898</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.619036233022822</v>
+        <v>7.635163719109066</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.676929741962855</v>
+        <v>7.69303311148332</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.695361619757389</v>
+        <v>7.71248400536774</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.709984788319955</v>
+        <v>7.73142873006678</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.807848231016945</v>
+        <v>7.825558343687801</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370239818751212</v>
+        <v>8.370237340594725</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367970559648128</v>
+        <v>8.36797265907296</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394513921497673</v>
+        <v>8.39450969151471</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410771226489366</v>
+        <v>8.410769161694413</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198547012862</v>
+        <v>8.42419865200004</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428426435271566</v>
+        <v>8.428428440650954</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427197394702572</v>
+        <v>8.427201286707845</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431643235828666</v>
+        <v>8.431649423774536</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429651846113964</v>
+        <v>8.429672311965501</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.43962370584023</v>
+        <v>8.439646014047305</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446133372802533</v>
+        <v>8.446157474523602</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439272159652017</v>
+        <v>8.439296061110461</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419085690243357</v>
+        <v>8.419111394276007</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401377073366547</v>
+        <v>8.401411314644063</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373560675369202</v>
+        <v>8.373590722195926</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335915040495607</v>
+        <v>8.335947896817101</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280553599829366</v>
+        <v>8.28059914419633</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226089253543108</v>
+        <v>8.226138065925472</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173354863352802</v>
+        <v>8.173380994049136</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130342498011867</v>
+        <v>8.130358819820888</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133252010688286</v>
+        <v>8.133247104519178</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18573325324691</v>
+        <v>8.185711246126859</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217395733407194</v>
+        <v>8.217328490187871</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201631496809114</v>
+        <v>8.201546427021043</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172981357749954</v>
+        <v>8.172889201401832</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128352037996713</v>
+        <v>8.128265507371044</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105218873287738</v>
+        <v>8.105148347782688</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115885284350789</v>
+        <v>8.11583193524876</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078345980268</v>
+        <v>8.164078126392162</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192242098881531</v>
+        <v>8.192257244491302</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172993624446253</v>
+        <v>8.173025779769477</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197155810822974</v>
+        <v>8.197235470291837</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.19975445521875</v>
+        <v>8.199909857141115</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230985898672763</v>
+        <v>8.231169040050547</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.32119192466312</v>
+        <v>8.321435272822145</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280375583686862</v>
+        <v>8.280511598924283</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28167829696082</v>
+        <v>8.281866055787757</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265228865224868</v>
+        <v>8.265409868735166</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275738694053262</v>
+        <v>8.275948678111781</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.310332250745059</v>
+        <v>8.310599333939749</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.331008278047824</v>
+        <v>8.331301194974067</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.23791611956052</v>
+        <v>8.238216559384931</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.148071337444577</v>
+        <v>8.148329662569729</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055792030132226</v>
+        <v>8.055959549353467</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011659881675754</v>
+        <v>8.011802463076609</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967591358732682</v>
+        <v>7.967663682213661</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942030761270409</v>
+        <v>7.942079478695768</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.94751219143131</v>
+        <v>7.947612328632094</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914881074024281</v>
+        <v>7.914927591670681</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88766303739789</v>
+        <v>7.887685310748275</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872485967001</v>
+        <v>7.8725237539013</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892465462865164</v>
+        <v>7.89257722308216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864473003743748</v>
+        <v>7.864632971670095</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810984250161151</v>
+        <v>7.811173516670513</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.770501749650848</v>
+        <v>7.770691905681585</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750614164742316</v>
+        <v>7.75074540182483</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749663578890964</v>
+        <v>7.749685846975336</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752429132447826</v>
+        <v>7.752360682514762</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753977750960217</v>
+        <v>7.757195178222042</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.728814100897104</v>
+        <v>7.733702871129102</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.704328269238035</v>
+        <v>7.710612910346591</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.675791201130673</v>
+        <v>7.683354433999765</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.658132485046563</v>
+        <v>7.666854696550576</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.645053302050734</v>
+        <v>7.655227351367304</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.634831310081379</v>
+        <v>7.646096205823239</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.625314370488031</v>
+        <v>7.637556711593227</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.619101660652898</v>
+        <v>7.632357532893185</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.635163719109066</v>
+        <v>7.649769336231934</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.69303311148332</v>
+        <v>7.707247811472275</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.71248400536774</v>
+        <v>7.727177942342187</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.73142873006678</v>
+        <v>7.748516435439333</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.825558343687801</v>
+        <v>7.835786683053147</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370237340594725</v>
+        <v>8.370247639363633</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36797265907296</v>
+        <v>8.367963929630591</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39450969151471</v>
+        <v>8.39452727820578</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410769161694413</v>
+        <v>8.410777748494649</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42419865200004</v>
+        <v>8.424198220123639</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428428440650954</v>
+        <v>8.428420110039127</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427201286707845</v>
+        <v>8.427185113832529</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431649423774536</v>
+        <v>8.431623705720972</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429672311965501</v>
+        <v>8.429587236116548</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439646014047305</v>
+        <v>8.439553298305736</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446157474523602</v>
+        <v>8.446057305679011</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439296061110461</v>
+        <v>8.439196724075408</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419111394276007</v>
+        <v>8.419004590087912</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401411314644063</v>
+        <v>8.401269025878459</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373590722195926</v>
+        <v>8.373465856467186</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335947896817101</v>
+        <v>8.33581140996429</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28059914419633</v>
+        <v>8.280409977113603</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226138065925472</v>
+        <v>8.225935428554761</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173380994049136</v>
+        <v>8.17327250457101</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130358819820888</v>
+        <v>8.130291069133378</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133247104519178</v>
+        <v>8.133267681324821</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185711246126859</v>
+        <v>8.185802863458484</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217328490187871</v>
+        <v>8.217607855369405</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201546427021043</v>
+        <v>8.201899717748038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172889201401832</v>
+        <v>8.173271794114068</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128265507371044</v>
+        <v>8.128624558149093</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105148347782688</v>
+        <v>8.105440713811781</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11583193524876</v>
+        <v>8.116052732400831</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078126392162</v>
+        <v>8.164078373911995</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192257244491302</v>
+        <v>8.192194194945669</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173025779769477</v>
+        <v>8.172891965985828</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197235470291837</v>
+        <v>8.196904887627245</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199909857141115</v>
+        <v>8.199265290846551</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.231169040050547</v>
+        <v>8.230409365648795</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.321435272822145</v>
+        <v>8.320425402347004</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280511598924283</v>
+        <v>8.279946089644552</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.281866055787757</v>
+        <v>8.281085515130469</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265409868735166</v>
+        <v>8.264656819197731</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275948678111781</v>
+        <v>8.275075179210527</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.310599333939749</v>
+        <v>8.309488632181456</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.331301194974067</v>
+        <v>8.330083468787794</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.238216559384931</v>
+        <v>8.236968589266992</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.148329662569729</v>
+        <v>8.147257202946092</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055959549353467</v>
+        <v>8.055264810407994</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011802463076609</v>
+        <v>8.011211404408309</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967663682213661</v>
+        <v>7.967363957274392</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942079478695768</v>
+        <v>7.941877357849066</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947612328632094</v>
+        <v>7.947196691287732</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914927591670681</v>
+        <v>7.914733899680325</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887685310748275</v>
+        <v>7.887591695533189</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.8725237539013</v>
+        <v>7.872365425207197</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.89257722308216</v>
+        <v>7.892112304727459</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864632971670095</v>
+        <v>7.863968191177897</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.811173516670513</v>
+        <v>7.810388565369134</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.770691905681585</v>
+        <v>7.778009796707774</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.75074540182483</v>
+        <v>7.7557725346139</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749685846975336</v>
+        <v>7.751548227053693</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752360682514762</v>
+        <v>7.750244714162294</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.757195178222042</v>
+        <v>7.752525807277644</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.733702871129102</v>
+        <v>7.72951706321172</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.710612910346591</v>
+        <v>7.700806967330127</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.683354433999765</v>
+        <v>7.675375857264763</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.666854696550576</v>
+        <v>7.663773497088672</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.655227351367304</v>
+        <v>7.658034332802034</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.646096205823239</v>
+        <v>7.645636212667231</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.637556711593227</v>
+        <v>7.628429062648329</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.632357532893185</v>
+        <v>7.610697821891047</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.649769336231934</v>
+        <v>7.617549309345454</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.707247811472275</v>
+        <v>7.671414493998592</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.727177942342187</v>
+        <v>7.712026897359899</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.748516435439333</v>
+        <v>7.782144098200167</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,15 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.835786683053147</v>
+        <v>7.933381224888836</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>7.984457333724456</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370247639363633</v>
+        <v>8.37023492287198</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367963929630591</v>
+        <v>8.367974706621828</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39452727820578</v>
+        <v>8.394505565812018</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410777748494649</v>
+        <v>8.410767148118705</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198220123639</v>
+        <v>8.424198755078434</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428420110039127</v>
+        <v>8.428430397622709</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427185113832529</v>
+        <v>8.427205084033737</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431623705720972</v>
+        <v>8.431655460511317</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429587236116548</v>
+        <v>8.429692275264324</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439553298305736</v>
+        <v>8.439667777216423</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446057305679011</v>
+        <v>8.446180987529491</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439196724075408</v>
+        <v>8.439319378671943</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419004590087912</v>
+        <v>8.419136473975517</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401269025878459</v>
+        <v>8.401444722602154</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373465856467186</v>
+        <v>8.373620036766408</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33581140996429</v>
+        <v>8.335979960398561</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280409977113603</v>
+        <v>8.280643593587765</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225935428554761</v>
+        <v>8.226185719930616</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17327250457101</v>
+        <v>8.173406502910254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130291069133378</v>
+        <v>8.130374755320839</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133267681324821</v>
+        <v>8.133242345600053</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185802863458484</v>
+        <v>8.185689799229912</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217607855369405</v>
+        <v>8.217262874367862</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201899717748038</v>
+        <v>8.201463396149395</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173271794114068</v>
+        <v>8.172799234996537</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128624558149093</v>
+        <v>8.128181005611388</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105440713811781</v>
+        <v>8.105079435739555</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.116052732400831</v>
+        <v>8.115779753188384</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078373911995</v>
+        <v>8.164077814283518</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192194194945669</v>
+        <v>8.192272004741454</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172891965985828</v>
+        <v>8.173057123857223</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196904887627245</v>
+        <v>8.19731325545068</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199265290846551</v>
+        <v>8.200061653711023</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230409365648795</v>
+        <v>8.231347924817305</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320425402347004</v>
+        <v>8.321672897798765</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.279946089644552</v>
+        <v>8.280644259611028</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.281085515130469</v>
+        <v>8.282049198817429</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264656819197731</v>
+        <v>8.265586335297815</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275075179210527</v>
+        <v>8.276153416680202</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.309488632181456</v>
+        <v>8.31085979214471</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.330083468787794</v>
+        <v>8.331586906385638</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.236968589266992</v>
+        <v>8.238509760066242</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.147257202946092</v>
+        <v>8.148581847579642</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.055264810407994</v>
+        <v>8.056123194545616</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011211404408309</v>
+        <v>8.011941785298932</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967363957274392</v>
+        <v>7.96773436537359</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941877357849066</v>
+        <v>7.942127058206847</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947196691287732</v>
+        <v>7.947710099501131</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914733899680325</v>
+        <v>7.914972919984617</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887591695533189</v>
+        <v>7.887706886116245</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872365425207197</v>
+        <v>7.872560428635149</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892112304727459</v>
+        <v>7.892686189195258</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.863968191177897</v>
+        <v>7.864789040170617</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810388565369134</v>
+        <v>7.811358402246059</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.778009796707774</v>
+        <v>7.770877804913553</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.7557725346139</v>
+        <v>7.750873915411684</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.751548227053693</v>
+        <v>7.749708088189116</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750244714162294</v>
+        <v>7.75229421800953</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752525807277644</v>
+        <v>7.757002075694899</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.72951706321172</v>
+        <v>7.737199903784232</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.700806967330127</v>
+        <v>7.715297257276732</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.675375857264763</v>
+        <v>7.689158944848071</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.663773497088672</v>
+        <v>7.67440726254857</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.658034332802034</v>
+        <v>7.663921951737088</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.645636212667231</v>
+        <v>7.655840943645845</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.628429062648329</v>
+        <v>7.648372009500257</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.610697821891047</v>
+        <v>7.644287242006461</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.617549309345454</v>
+        <v>7.663140783057139</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.671414493998592</v>
+        <v>7.721279607492043</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.712026897359899</v>
+        <v>7.742276209499521</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.782144098200167</v>
+        <v>7.766871729078349</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.933381224888836</v>
+        <v>7.852218004762573</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.984457333724456</v>
+        <v>7.92548045163498</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37023492287198</v>
+        <v>8.370244965660927</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367974706621828</v>
+        <v>8.367966197082113</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394505565812018</v>
+        <v>8.394522710522581</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410767148118705</v>
+        <v>8.410775517753128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198755078434</v>
+        <v>8.424198331123247</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428430397622709</v>
+        <v>8.428422271925051</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427205084033737</v>
+        <v>8.427189312130716</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431655460511317</v>
+        <v>8.431630383006528</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429692275264324</v>
+        <v>8.429609328919369</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439667777216423</v>
+        <v>8.439577370330097</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446180987529491</v>
+        <v>8.446083312526163</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439319378671943</v>
+        <v>8.439222515086101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419136473975517</v>
+        <v>8.419032313589927</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401444722602154</v>
+        <v>8.401305963012284</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373620036766408</v>
+        <v>8.373498272451323</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335979960398561</v>
+        <v>8.335846829126975</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280643593587765</v>
+        <v>8.280459060380792</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226185719930616</v>
+        <v>8.225987980788132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173406502910254</v>
+        <v>8.173300643356372</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130374755320839</v>
+        <v>8.13030863794949</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133242345600053</v>
+        <v>8.133262291820232</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185689799229912</v>
+        <v>8.185779037950438</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217262874367862</v>
+        <v>8.217535350022539</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201463396149395</v>
+        <v>8.201808060464172</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172799234996537</v>
+        <v>8.173172567232378</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128181005611388</v>
+        <v>8.128531484191765</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105079435739555</v>
+        <v>8.105364995222144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115779753188384</v>
+        <v>8.115995641319911</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164077814283518</v>
+        <v>8.164078477894876</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192272004741454</v>
+        <v>8.192210590413477</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173057123857223</v>
+        <v>8.172926751763978</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19731325545068</v>
+        <v>8.196990592795906</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.200061653711023</v>
+        <v>8.199432311121065</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.231347924817305</v>
+        <v>8.230606225981855</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.321672897798765</v>
+        <v>8.320687213793541</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280644259611028</v>
+        <v>8.280092967988359</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282049198817429</v>
+        <v>8.281288217020883</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265586335297815</v>
+        <v>8.264852531348971</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.276153416680202</v>
+        <v>8.275302164497205</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.31085979214471</v>
+        <v>8.30977717535171</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.331586906385638</v>
+        <v>8.330399712037599</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.238509760066242</v>
+        <v>8.237292426070633</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.148581847579642</v>
+        <v>8.147535350957096</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.056123194545616</v>
+        <v>8.05544480924018</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011941785298932</v>
+        <v>8.011364475713254</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96773436537359</v>
+        <v>7.967441557947102</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942127058206847</v>
+        <v>7.941929745291956</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947710099501131</v>
+        <v>7.9473044662232</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914972919984617</v>
+        <v>7.914784279166691</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887706886116245</v>
+        <v>7.887616265195869</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872560428635149</v>
+        <v>7.872406856424794</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892686189195258</v>
+        <v>7.892233120783216</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864789040170617</v>
+        <v>7.864140772410122</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.811358402246059</v>
+        <v>7.810591942094305</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.770877804913553</v>
+        <v>7.778203497077365</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750873915411684</v>
+        <v>7.755901465929453</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749708088189116</v>
+        <v>7.75157764843593</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.75229421800953</v>
+        <v>7.750195034884417</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.757002075694899</v>
+        <v>7.752349561267592</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.737199903784232</v>
+        <v>7.733561893695411</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.715297257276732</v>
+        <v>7.706427856186849</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.689158944848071</v>
+        <v>7.68224561362926</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.67440726254857</v>
+        <v>7.672495143367781</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.663921951737088</v>
+        <v>7.667895706525325</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.655840943645845</v>
+        <v>7.656628450246618</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.648372009500257</v>
+        <v>7.640456875064357</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.644287242006461</v>
+        <v>7.62402481226358</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.663140783057139</v>
+        <v>7.633104883955612</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.721279607492043</v>
+        <v>7.68756334904307</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.742276209499521</v>
+        <v>7.730846457137611</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.766871729078349</v>
+        <v>7.80336948127865</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.852218004762573</v>
+        <v>7.944624312298354</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.92548045163498</v>
+        <v>8.000516532053037</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370244965660927</v>
+        <v>8.37023256339905</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367966197082113</v>
+        <v>8.367976704193518</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394522710522581</v>
+        <v>8.394501540581729</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410775517753128</v>
+        <v>8.410765183880834</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198331123247</v>
+        <v>8.424198856293902</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428422271925051</v>
+        <v>8.428432307918301</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427189312130716</v>
+        <v>8.427208790092953</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431630383006528</v>
+        <v>8.431661351513348</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429609328919369</v>
+        <v>8.429711754289668</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439577370330097</v>
+        <v>8.439689015076748</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446083312526163</v>
+        <v>8.446203933125229</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439222515086101</v>
+        <v>8.439342133469715</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419032313589927</v>
+        <v>8.419160951806584</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401305963012284</v>
+        <v>8.401477327281729</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373498272451323</v>
+        <v>8.373648645513452</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.335846829126975</v>
+        <v>8.336011259572871</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280459060380792</v>
+        <v>8.280686986993015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.225987980788132</v>
+        <v>8.226232256247588</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173300643356372</v>
+        <v>8.173431411845758</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.13030863794949</v>
+        <v>8.130390318051985</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133262291820232</v>
+        <v>8.133237727638363</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185779037950438</v>
+        <v>8.185668891508332</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217535350022539</v>
+        <v>8.217198827648794</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201808060464172</v>
+        <v>8.201382331893402</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.173172567232378</v>
+        <v>8.172711381569975</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128531484191765</v>
+        <v>8.128098462422116</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105364995222144</v>
+        <v>8.105012082740368</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115995641319911</v>
+        <v>8.115728700822048</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164078477894876</v>
+        <v>8.164077416418522</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192210590413477</v>
+        <v>8.192286393985798</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.172926751763978</v>
+        <v>8.173087686820486</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.196990592795906</v>
+        <v>8.197389231366671</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.199432311121065</v>
+        <v>8.2002099685205</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.230606225981855</v>
+        <v>8.23152269916023</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.320687213793541</v>
+        <v>8.321904998634142</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280092967988359</v>
+        <v>8.280773688214406</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.281288217020883</v>
+        <v>8.282227893954332</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.264852531348971</v>
+        <v>8.265758432901599</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.275302164497205</v>
+        <v>8.276353103350433</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.30977717535171</v>
+        <v>8.311113868128288</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.330399712037599</v>
+        <v>8.331865674322314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.237292426070633</v>
+        <v>8.238795979478622</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.147535350957096</v>
+        <v>8.148828108095874</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.05544480924018</v>
+        <v>8.056283097881074</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.011364475713254</v>
+        <v>8.012077958247232</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967441557947102</v>
+        <v>7.967803463189174</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.941929745291956</v>
+        <v>7.942173539231569</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.9473044662232</v>
+        <v>7.947805586865083</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.914784279166691</v>
+        <v>7.915017103855527</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887616265195869</v>
+        <v>7.887727794079703</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872406856424794</v>
+        <v>7.872596037865724</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892233120783216</v>
+        <v>7.892792464309109</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.864140772410122</v>
+        <v>7.86494134962142</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.810591942094305</v>
+        <v>7.811539056062841</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.778203497077365</v>
+        <v>7.771059587000991</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.755901465929453</v>
+        <v>7.750999786801904</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.75157764843593</v>
+        <v>7.749730286422063</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750195034884417</v>
+        <v>7.752229658821837</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752349561267592</v>
+        <v>7.756813700473458</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.733561893695411</v>
+        <v>7.740578274572939</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.706427856186849</v>
+        <v>7.719812851953701</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.68224561362926</v>
+        <v>7.694732699862229</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.672495143367781</v>
+        <v>7.681371915135013</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.667895706525325</v>
+        <v>7.671934991726669</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.656628450246618</v>
+        <v>7.664972763584677</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.640456875064357</v>
+        <v>7.658593995401354</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.62402481226358</v>
+        <v>7.655585286727623</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.633104883955612</v>
+        <v>7.675714079191081</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.68756334904307</v>
+        <v>7.734324186447055</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.730846457137611</v>
+        <v>7.756099899471645</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.80336948127865</v>
+        <v>7.782942216708569</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.944624312298354</v>
+        <v>7.865084949203982</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>8.000516532053037</v>
+        <v>7.927137227008352</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37023256339905</v>
+        <v>8.370230260095992</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367976704193518</v>
+        <v>8.367978653595292</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394501540581729</v>
+        <v>8.394497612199068</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410765183880834</v>
+        <v>8.41076326719037</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198856293902</v>
+        <v>8.424198955691196</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428432307918301</v>
+        <v>8.428434173187622</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427208790092953</v>
+        <v>8.427212408136171</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431661351513348</v>
+        <v>8.431667101993918</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429711754289668</v>
+        <v>8.429730766445221</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439689015076748</v>
+        <v>8.439709746416813</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446203933125229</v>
+        <v>8.446226331600313</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439342133469715</v>
+        <v>8.439364345629558</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419160951806584</v>
+        <v>8.419184849169351</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401477327281729</v>
+        <v>8.401509157297532</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373648645513452</v>
+        <v>8.373676573613373</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336011259572871</v>
+        <v>8.336041821339361</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280686986993015</v>
+        <v>8.280729361573433</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226232256247588</v>
+        <v>8.226277713684768</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173431411845758</v>
+        <v>8.173455741749155</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130390318051985</v>
+        <v>8.130405520929783</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133237727638363</v>
+        <v>8.133233244686121</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185668891508332</v>
+        <v>8.185648502952358</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217198827648794</v>
+        <v>8.217136294480552</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201382331893402</v>
+        <v>8.201303165324518</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172711381569975</v>
+        <v>8.172625567714249</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128098462422116</v>
+        <v>8.128017810706842</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.105012082740368</v>
+        <v>8.10494623677134</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115728700822048</v>
+        <v>8.115678742351836</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164077416418522</v>
+        <v>8.164076939082211</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192286393985798</v>
+        <v>8.192300425881367</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173087686820486</v>
+        <v>8.173117497307375</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197389231366671</v>
+        <v>8.197463460144611</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.2002099685205</v>
+        <v>8.200354919597196</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23152269916023</v>
+        <v>8.231693502672226</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.321904998634142</v>
+        <v>8.322131765269415</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280773688214406</v>
+        <v>8.280900001317722</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282227893954332</v>
+        <v>8.282402301068068</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265758432901599</v>
+        <v>8.265926321364901</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.276353103350433</v>
+        <v>8.276547922328172</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.311113868128288</v>
+        <v>8.311361792973081</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.331865674322314</v>
+        <v>8.332137748297985</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.238795979478622</v>
+        <v>8.239075463422486</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.148828108095874</v>
+        <v>8.149068649795019</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.056283097881074</v>
+        <v>8.056439385619914</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012077958247232</v>
+        <v>8.012211086967167</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967803463189174</v>
+        <v>7.967871028216727</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942173539231569</v>
+        <v>7.942218959395953</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947805586865083</v>
+        <v>7.947898869732964</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915017103855527</v>
+        <v>7.915060185948861</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887727794079703</v>
+        <v>7.887748063517925</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872596037865724</v>
+        <v>7.872630625746758</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892792464309109</v>
+        <v>7.892896146534529</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.86494134962142</v>
+        <v>7.865090033763173</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.811539056062841</v>
+        <v>7.811715620656362</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771059587000991</v>
+        <v>7.771237385636882</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.750999786801904</v>
+        <v>7.751123094224717</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749730286422063</v>
+        <v>7.749752427061522</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752229658821837</v>
+        <v>7.752166928910651</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.756813700473458</v>
+        <v>7.756629885695954</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.740578274572939</v>
+        <v>7.743440331062143</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.719812851953701</v>
+        <v>7.723711153126234</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.694732699862229</v>
+        <v>7.69966328167288</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.681371915135013</v>
+        <v>7.687397460768673</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.671934991726669</v>
+        <v>7.679113797845581</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.664972763584677</v>
+        <v>7.673149093607307</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.658593995401354</v>
+        <v>7.667696224687599</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.655585286727623</v>
+        <v>7.665524692948183</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.675714079191081</v>
+        <v>7.6864807659007</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.734324186447055</v>
+        <v>7.744887292023368</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.756099899471645</v>
+        <v>7.766656584073674</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.782942216708569</v>
+        <v>7.793885329214249</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.865084949203982</v>
+        <v>7.86970654352437</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.927137227008352</v>
+        <v>7.910256654138956</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370230260095992</v>
+        <v>8.370228010980711</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367978653595292</v>
+        <v>8.367980556548334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394497612199068</v>
+        <v>8.394493777211498</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41076326719037</v>
+        <v>8.410761396342433</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424198955691196</v>
+        <v>8.42419905331397</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428434173187622</v>
+        <v>8.428435995003717</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427212408136171</v>
+        <v>8.427215941261524</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431667101993918</v>
+        <v>8.431672716920637</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429730766445221</v>
+        <v>8.429749328310914</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439709746416813</v>
+        <v>8.439729989139886</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446226331600313</v>
+        <v>8.446248202288496</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439364345629558</v>
+        <v>8.439386034329111</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419184849169351</v>
+        <v>8.419208186461699</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401509157297532</v>
+        <v>8.401540239921736</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373676573613373</v>
+        <v>8.373703845059755</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336041821339361</v>
+        <v>8.336071671441296</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280729361573433</v>
+        <v>8.280770752768214</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226277713684768</v>
+        <v>8.22632212927712</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173455741749155</v>
+        <v>8.173479512556019</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130405520929783</v>
+        <v>8.130420376280469</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133233244686121</v>
+        <v>8.133228891117072</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185648502952358</v>
+        <v>8.185628614527193</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217136294480552</v>
+        <v>8.217075221901403</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201303165324518</v>
+        <v>8.201225830692428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172625567714249</v>
+        <v>8.172541723375119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.128017810706842</v>
+        <v>8.127938986389143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10494623677134</v>
+        <v>8.104881848092496</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115678742351836</v>
+        <v>8.115629843451716</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164076939082211</v>
+        <v>8.164076388117525</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192300425881367</v>
+        <v>8.192314113429783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173117497307375</v>
+        <v>8.173146582590402</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197463460144611</v>
+        <v>8.197536001092756</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.200354919597196</v>
+        <v>8.200496619712798</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.231693502672226</v>
+        <v>8.23186046871815</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.322131765269415</v>
+        <v>8.322353379058493</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.280900001317722</v>
+        <v>8.281023309969118</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282402301068068</v>
+        <v>8.282572572467648</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.265926321364901</v>
+        <v>8.266090152825209</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.276547922328172</v>
+        <v>8.276738048993586</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.311361792973081</v>
+        <v>8.311603786768845</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.332137748297985</v>
+        <v>8.332403366038658</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.239075463422486</v>
+        <v>8.239348446321156</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.149068649795019</v>
+        <v>8.149303668973523</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.056439385619914</v>
+        <v>8.056592178434881</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012211086967167</v>
+        <v>8.012341271909474</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967871028216727</v>
+        <v>7.967937110723406</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942218959395953</v>
+        <v>7.942263354625986</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947898869732964</v>
+        <v>7.947990023513395</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915060185948861</v>
+        <v>7.915102206841697</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887748063517925</v>
+        <v>7.887767721725001</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872630625746758</v>
+        <v>7.872664234085835</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892896146534529</v>
+        <v>7.892997329286272</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865090033763173</v>
+        <v>7.865235220087313</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.811715620656362</v>
+        <v>7.811888232284487</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771237385636882</v>
+        <v>7.771411328862813</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751123094224717</v>
+        <v>7.751243912974295</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749752427061522</v>
+        <v>7.749774496866583</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752166928910651</v>
+        <v>7.752105956057915</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.756629885695954</v>
+        <v>7.756450472063612</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743440331062143</v>
+        <v>7.746105524891655</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.723711153126234</v>
+        <v>7.727359045181069</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.69966328167288</v>
+        <v>7.70425718517914</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.687397460768673</v>
+        <v>7.692969632872787</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.679113797845581</v>
+        <v>7.685708069837904</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.673149093607307</v>
+        <v>7.680664719347273</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.667696224687599</v>
+        <v>7.676095581116355</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.665524692948183</v>
+        <v>7.674744625123899</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.6864807659007</v>
+        <v>7.696468188879919</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.744887292023368</v>
+        <v>7.754711643343777</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.766656584073674</v>
+        <v>7.776541148186832</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.793885329214249</v>
+        <v>7.80412311514784</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.86970654352437</v>
+        <v>7.874873755227886</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.910256654138956</v>
+        <v>7.906343738893532</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370228010980711</v>
+        <v>8.370225814163277</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367980556548334</v>
+        <v>8.367982414692808</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394493777211498</v>
+        <v>8.394490032328608</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410761396342433</v>
+        <v>8.410759569712649</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42419905331397</v>
+        <v>8.424199149204785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428435995003717</v>
+        <v>8.428437774867223</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427215941261524</v>
+        <v>8.427219392423458</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431672716920637</v>
+        <v>8.431678201029749</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429749328310914</v>
+        <v>8.429767455691056</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439729989139886</v>
+        <v>8.439749760315504</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446248202288496</v>
+        <v>8.446269563623389</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439386034329111</v>
+        <v>8.439407217853033</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419208186461699</v>
+        <v>8.419230983137222</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401540239921736</v>
+        <v>8.401570601161739</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373703845059755</v>
+        <v>8.373730482732054</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336071671441296</v>
+        <v>8.33610083443806</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280770752768214</v>
+        <v>8.280811194392898</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22632212927712</v>
+        <v>8.226365538386196</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173479512556019</v>
+        <v>8.173502743298204</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130420376280469</v>
+        <v>8.130434895874252</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133228891117072</v>
+        <v>8.133224661605611</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185628614527193</v>
+        <v>8.185609208114519</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217075221901403</v>
+        <v>8.217015559389168</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201225830692428</v>
+        <v>8.201150265244294</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172541723375119</v>
+        <v>8.172459781663086</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127938986389143</v>
+        <v>8.127861928245112</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104881848092496</v>
+        <v>8.10481886911562</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115629843451716</v>
+        <v>8.115581971194199</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164076388117525</v>
+        <v>8.164075768959227</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192314113429783</v>
+        <v>8.192327469015748</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173146582590402</v>
+        <v>8.173174968647599</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197536001092756</v>
+        <v>8.19760691087766</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.200496619712798</v>
+        <v>8.200635176671286</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23186046871815</v>
+        <v>8.23202372477706</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.322353379058493</v>
+        <v>8.322570013246676</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281023309969118</v>
+        <v>8.281143720005945</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282572572467648</v>
+        <v>8.282738853342618</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266090152825209</v>
+        <v>8.266250072193968</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.276738048993586</v>
+        <v>8.276923650422347</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.311603786768845</v>
+        <v>8.311840059256825</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.332403366038658</v>
+        <v>8.332662754169013</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.239348446321156</v>
+        <v>8.23961515186998</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.149303668973523</v>
+        <v>8.149533353074576</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.056592178434881</v>
+        <v>8.0567415917153</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012341271909474</v>
+        <v>8.012468609176993</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.967937110723406</v>
+        <v>7.968001758810014</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942263354625986</v>
+        <v>7.942306759242609</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.947990023513395</v>
+        <v>7.948079120217217</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915102206841697</v>
+        <v>7.915143205148604</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887767721725001</v>
+        <v>7.887786794514448</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872664234085835</v>
+        <v>7.872696902495306</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.892997329286272</v>
+        <v>7.89309610155977</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865235220087313</v>
+        <v>7.865377030195631</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.811888232284487</v>
+        <v>7.812057021266201</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771411328862813</v>
+        <v>7.771581539360028</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751243912974295</v>
+        <v>7.75136231553823</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749774496866583</v>
+        <v>7.749796483853273</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752105956057915</v>
+        <v>7.752046671639405</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.756450472063612</v>
+        <v>7.756275307427785</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.746105524891655</v>
+        <v>7.747524931177804</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.727359045181069</v>
+        <v>7.729515059333511</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.70425718517914</v>
+        <v>7.707434360871792</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.692969632872787</v>
+        <v>7.696833854437541</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.685708069837904</v>
+        <v>7.690280304918991</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.680664719347273</v>
+        <v>7.68595454676584</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.676095581116355</v>
+        <v>7.682195983640641</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.674744625123899</v>
+        <v>7.681646913692084</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.696468188879919</v>
+        <v>7.703804347552552</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.754711643343777</v>
+        <v>7.761333221089924</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.776541148186832</v>
+        <v>7.782408703455933</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.80412311514784</v>
+        <v>7.80855805671793</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.874873755227886</v>
+        <v>7.87162474505439</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.906343738893532</v>
+        <v>7.886792602289963</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370225814163277</v>
+        <v>8.370223667840644</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367982414692808</v>
+        <v>8.367984229592574</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394490032328608</v>
+        <v>8.394486374412717</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410759569712649</v>
+        <v>8.410757785752457</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199149204785</v>
+        <v>8.424199243405116</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428437774867223</v>
+        <v>8.428439514210476</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427219392423458</v>
+        <v>8.427222764440954</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431678201029749</v>
+        <v>8.431683558839429</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429767455691056</v>
+        <v>8.429785163659176</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439749760315504</v>
+        <v>8.439769076227432</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446269563623389</v>
+        <v>8.446290433190239</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439407217853033</v>
+        <v>8.439427913644378</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419230983137222</v>
+        <v>8.419253257759229</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401570601161739</v>
+        <v>8.401600265832613</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373730482732054</v>
+        <v>8.373756508459504</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33610083443806</v>
+        <v>8.336129333772394</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280811194392898</v>
+        <v>8.280850718731283</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226365538386196</v>
+        <v>8.226407974793446</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173502743298204</v>
+        <v>8.173525452154424</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130434895874252</v>
+        <v>8.130449090956274</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133224661605611</v>
+        <v>8.133220551107346</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185609208114519</v>
+        <v>8.185590266458121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.217015559389168</v>
+        <v>8.216957258722511</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201150265244294</v>
+        <v>8.201076409056171</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172459781663086</v>
+        <v>8.172379678677103</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127861928245112</v>
+        <v>8.127786577746935</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10481886911562</v>
+        <v>8.104757254289943</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115581971194199</v>
+        <v>8.115535093981267</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164075768959227</v>
+        <v>8.164075086664884</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192327469015748</v>
+        <v>8.192340504442864</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173174968647599</v>
+        <v>8.173202680238003</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19760691087766</v>
+        <v>8.197676243668923</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.200635176671286</v>
+        <v>8.20077069357847</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23202372477706</v>
+        <v>8.23218339276219</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.322570013246676</v>
+        <v>8.322781833417693</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281143720005945</v>
+        <v>8.281261332356555</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282738853342618</v>
+        <v>8.282901282173725</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266250072193968</v>
+        <v>8.266406217579515</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.276923650422347</v>
+        <v>8.277104885870299</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.311840059256825</v>
+        <v>8.312070810429372</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.332662754169013</v>
+        <v>8.332916128851604</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.23961515186998</v>
+        <v>8.239875793641611</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.149533353074576</v>
+        <v>8.149757881180038</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.0567415917153</v>
+        <v>8.056887735851493</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012468609176993</v>
+        <v>8.012593190756059</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968001758810014</v>
+        <v>7.96806501852603</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942306759242609</v>
+        <v>7.942349206050438</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948079120217217</v>
+        <v>7.948166228646585</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915143205148604</v>
+        <v>7.915183217638546</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887786794514448</v>
+        <v>7.887805306315843</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872696902495306</v>
+        <v>7.872728668531849</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.89309610155977</v>
+        <v>7.893192548188619</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865377030195631</v>
+        <v>7.865515580135441</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812057021266201</v>
+        <v>7.812222112298851</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771581539360028</v>
+        <v>7.771748134723005</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.75136231553823</v>
+        <v>7.751478371719898</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749796483853273</v>
+        <v>7.749818377189751</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.752046671639405</v>
+        <v>7.751989010411386</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.756275307427785</v>
+        <v>7.75610424640312</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.747524931177804</v>
+        <v>7.748876413718589</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.729515059333511</v>
+        <v>7.731544480842713</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.707434360871792</v>
+        <v>7.710435917381314</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.696833854437541</v>
+        <v>7.700466303764626</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.690280304918991</v>
+        <v>7.69459468267825</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.68595454676584</v>
+        <v>7.690945868668831</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.682195983640641</v>
+        <v>7.687949291778029</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.681646913692084</v>
+        <v>7.688144327779655</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.703804347552552</v>
+        <v>7.710656522719691</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.761333221089924</v>
+        <v>7.76744601790935</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.782408703455933</v>
+        <v>7.787762165022423</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.80855805671793</v>
+        <v>7.812489916052544</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.87162474505439</v>
+        <v>7.868930699980666</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.886792602289963</v>
+        <v>7.873767493103308</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370223667840644</v>
+        <v>8.370221570291701</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367984229592574</v>
+        <v>8.367986002739574</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394486374412717</v>
+        <v>8.394482800470101</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410757785752457</v>
+        <v>8.41075604298473</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199243405116</v>
+        <v>8.424199335955374</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428439514210476</v>
+        <v>8.428441214401351</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427222764440954</v>
+        <v>8.427226060005207</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431683558839429</v>
+        <v>8.431688794662195</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429785163659176</v>
+        <v>8.429802466599744</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439769076227432</v>
+        <v>8.439787952418351</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446290433190239</v>
+        <v>8.446310827774164</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439427913644378</v>
+        <v>8.439448138352455</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419253257759229</v>
+        <v>8.419275028051061</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401600265832613</v>
+        <v>8.401629257624638</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373756508459504</v>
+        <v>8.373781943080665</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336129333772394</v>
+        <v>8.336157191833118</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280850718731283</v>
+        <v>8.280889356621097</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226407974793446</v>
+        <v>8.226449470787372</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173525452154424</v>
+        <v>8.173547656497457</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130449090956274</v>
+        <v>8.130462972275543</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133220551107346</v>
+        <v>8.133216554841098</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185590266458121</v>
+        <v>8.18557177311337</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216957258722511</v>
+        <v>8.216900273851595</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201076409056171</v>
+        <v>8.201004204875643</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172379678677103</v>
+        <v>8.172301353339886</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127786577746935</v>
+        <v>8.127712878916583</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104757254289943</v>
+        <v>8.104696959994971</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115535093981267</v>
+        <v>8.1154891814792</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164075086664884</v>
+        <v>8.164074345943286</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192340504442864</v>
+        <v>8.192353230967022</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173202680238003</v>
+        <v>8.173229740971959</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197676243668923</v>
+        <v>8.197744051274556</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.20077069357847</v>
+        <v>8.200903269094246</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23218339276219</v>
+        <v>8.232339589320368</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.322781833417693</v>
+        <v>8.322988997911551</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281261332356555</v>
+        <v>8.281376243321439</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.282901282173725</v>
+        <v>8.283059991115493</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266406217579515</v>
+        <v>8.266558720680758</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.277104885870299</v>
+        <v>8.277281907224596</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.312070810429372</v>
+        <v>8.312296231088467</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.332916128851604</v>
+        <v>8.333163696382515</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.239875793641611</v>
+        <v>8.240130575650854</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.149757881180038</v>
+        <v>8.149977424469995</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.056887735851493</v>
+        <v>8.057030716501146</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012593190756059</v>
+        <v>8.012715104733314</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96806501852603</v>
+        <v>7.968126933977416</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942349206050438</v>
+        <v>7.94239072642066</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948166228646585</v>
+        <v>7.948251414571571</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915183217638546</v>
+        <v>7.915222279343533</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887805306315843</v>
+        <v>7.887823280264076</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872728668531849</v>
+        <v>7.872759567825684</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893192548188619</v>
+        <v>7.893286750084307</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865515580135441</v>
+        <v>7.865650980712154</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812222112298851</v>
+        <v>7.812383624755501</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771748134723005</v>
+        <v>7.771911227716719</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751478371719898</v>
+        <v>7.751592148755069</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749818377189751</v>
+        <v>7.749840167100539</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751989010411386</v>
+        <v>7.751932910311839</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75610424640312</v>
+        <v>7.755937150004923</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.748876413718589</v>
+        <v>7.748585379556792</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.731544480842713</v>
+        <v>7.733593247044414</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.710435917381314</v>
+        <v>7.713128581745401</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.700466303764626</v>
+        <v>7.703939093749701</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.69459468267825</v>
+        <v>7.699840671188898</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.690945868668831</v>
+        <v>7.697120224955097</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.687949291778029</v>
+        <v>7.695340857765678</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.688144327779655</v>
+        <v>7.696935516367765</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.710656522719691</v>
+        <v>7.72090502038928</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.76744601790935</v>
+        <v>7.777928027686698</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.787762165022423</v>
+        <v>7.801553560872476</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.812489916052544</v>
+        <v>7.828890043937294</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.868930699980666</v>
+        <v>7.886661965220515</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,15 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.873767493103308</v>
+        <v>7.902542823154763</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>7.984930323154762</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370221570291701</v>
+        <v>8.370219519872668</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367986002739574</v>
+        <v>8.367987735557914</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394482800470101</v>
+        <v>8.394479307642847</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41075604298473</v>
+        <v>8.410754339999711</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199335955374</v>
+        <v>8.424199426894905</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428441214401351</v>
+        <v>8.428442876746855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427226060005207</v>
+        <v>8.427229281686785</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431688794662195</v>
+        <v>8.431693912616479</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429802466599744</v>
+        <v>8.429819378247091</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439787952418351</v>
+        <v>8.439806403731541</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446310827774164</v>
+        <v>8.446330763405143</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439448138352455</v>
+        <v>8.439467907877457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419275028051061</v>
+        <v>8.419296310943075</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401629257624638</v>
+        <v>8.401657599166281</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373781943080665</v>
+        <v>8.373806806498958</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336157191833118</v>
+        <v>8.336184430013661</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280889356621097</v>
+        <v>8.280927137534013</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226449470787372</v>
+        <v>8.226490057244989</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173547656497457</v>
+        <v>8.173569372938285</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130462972275543</v>
+        <v>8.130476550111968</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133216554841098</v>
+        <v>8.133212668272261</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18557177311337</v>
+        <v>8.185553712400184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216900273851595</v>
+        <v>8.216844560777334</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.201004204875643</v>
+        <v>8.200933597974842</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172301353339886</v>
+        <v>8.172224747243988</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127712878916583</v>
+        <v>8.127640778188905</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104696959994971</v>
+        <v>8.104637944439954</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.1154891814792</v>
+        <v>8.115444204557139</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164074345943286</v>
+        <v>8.164073551180479</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192353230967022</v>
+        <v>8.192365659327518</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173229740971959</v>
+        <v>8.173256173376611</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197744051274556</v>
+        <v>8.197810383267676</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.200903269094246</v>
+        <v>8.20103299766884</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.232339589320368</v>
+        <v>8.23249242611238</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.322988997911551</v>
+        <v>8.323191658215423</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281376243321439</v>
+        <v>8.281488544835215</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283059991115493</v>
+        <v>8.283215106352944</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266558720680758</v>
+        <v>8.266707707153863</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.277281907224596</v>
+        <v>8.27745485942409</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.312296231088467</v>
+        <v>8.312516503366364</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.333163696382515</v>
+        <v>8.333405653746828</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.240130575650854</v>
+        <v>8.240379692882218</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.149977424469995</v>
+        <v>8.150192146652456</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057030716501146</v>
+        <v>8.057170634838887</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012715104733314</v>
+        <v>8.012834435499089</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968126933977416</v>
+        <v>7.9681875474277</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94239072642066</v>
+        <v>7.942431350368516</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948251414571571</v>
+        <v>7.948334740895248</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915222279343533</v>
+        <v>7.915260423659713</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887823280264076</v>
+        <v>7.887840738281953</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872759567825684</v>
+        <v>7.872789634200294</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893286750084307</v>
+        <v>7.893378784459623</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865650980712154</v>
+        <v>7.865783337781068</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812383624755501</v>
+        <v>7.812541672963755</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.771911227716719</v>
+        <v>7.772070926518713</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751592148755069</v>
+        <v>7.751703711422969</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749840167100539</v>
+        <v>7.749861844779034</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751932910311839</v>
+        <v>7.75187831227518</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755937150004923</v>
+        <v>7.755773885309038</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.748585379556792</v>
+        <v>7.748300407949445</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.733593247044414</v>
+        <v>7.735178025261376</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.713128581745401</v>
+        <v>7.715249368429416</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.703939093749701</v>
+        <v>7.706754020562745</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.699840671188898</v>
+        <v>7.703728097989565</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.697120224955097</v>
+        <v>7.701956066839506</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.695340857765678</v>
+        <v>7.701311785792994</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.696935516367765</v>
+        <v>7.704142787278256</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.72090502038928</v>
+        <v>7.729226059493289</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.777928027686698</v>
+        <v>7.786079994235669</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.801553560872476</v>
+        <v>7.812132729694132</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.828890043937294</v>
+        <v>7.840856243866162</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.886661965220515</v>
+        <v>7.897947119817115</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.902542823154763</v>
+        <v>7.917483055487681</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.984930323154762</v>
+        <v>7.99987055548768</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370219519872668</v>
+        <v>8.370217515012815</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367987735557914</v>
+        <v>8.367989429407679</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394479307642847</v>
+        <v>8.394475893201237</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410754339999711</v>
+        <v>8.410752675451226</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199426894905</v>
+        <v>8.424199516262028</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428442876746855</v>
+        <v>8.428444502496474</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427229281686785</v>
+        <v>8.427232431942315</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431693912616479</v>
+        <v>8.431698916637421</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429819378247091</v>
+        <v>8.429835911721719</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439806403731541</v>
+        <v>8.439824444349773</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446330763405143</v>
+        <v>8.446350255400002</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439467907877457</v>
+        <v>8.439487237412111</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419296310943075</v>
+        <v>8.419317122616473</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401657599166281</v>
+        <v>8.401685312082998</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373806806498958</v>
+        <v>8.373831117734536</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336184430013661</v>
+        <v>8.336211068766765</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280927137534013</v>
+        <v>8.280964089650418</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226490057244989</v>
+        <v>8.226529763707999</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173569372938285</v>
+        <v>8.173590617367342</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130476550111968</v>
+        <v>8.130489834301644</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133212668272261</v>
+        <v>8.133208887097394</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185553712400184</v>
+        <v>8.18553606935923</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216844560777334</v>
+        <v>8.216790077438633</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200933597974842</v>
+        <v>8.200864536013036</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172224747243988</v>
+        <v>8.172149804507802</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127640778188905</v>
+        <v>8.127570224283414</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104637944439954</v>
+        <v>8.104580167569541</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115444204557139</v>
+        <v>8.115400135229109</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164073551180479</v>
+        <v>8.164072706463649</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192365659327518</v>
+        <v>8.192377799776111</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173256173376611</v>
+        <v>8.173281998957005</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197810383267676</v>
+        <v>8.197875287105198</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.20103299766884</v>
+        <v>8.201159969764188</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23249242611238</v>
+        <v>8.23264201007569</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.323191658215423</v>
+        <v>8.323389959329548</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281488544835215</v>
+        <v>8.281598324711094</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283215106352944</v>
+        <v>8.28336674843451</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266707707153863</v>
+        <v>8.266853296954119</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.27745485942409</v>
+        <v>8.277623880851277</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.312516503366364</v>
+        <v>8.312731801211321</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.333405653746828</v>
+        <v>8.333642189137068</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.240379692882218</v>
+        <v>8.240623331782963</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.150192146652456</v>
+        <v>8.150402204365417</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057170634838887</v>
+        <v>8.057307587790369</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012834435499089</v>
+        <v>8.012951263938239</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.9681875474277</v>
+        <v>7.968246899392867</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942431350368516</v>
+        <v>7.942471106625829</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948334740895248</v>
+        <v>7.948416267808121</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915260423659713</v>
+        <v>7.9152976824415</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887840738281953</v>
+        <v>7.887857701156628</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872789634200294</v>
+        <v>7.872818899783469</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893378784459623</v>
+        <v>7.893468725036989</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865783337781068</v>
+        <v>7.865912752519915</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812541672963755</v>
+        <v>7.812696366467416</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772070926518713</v>
+        <v>7.772227334946974</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751703711422969</v>
+        <v>7.751813122152091</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749861844779034</v>
+        <v>7.749883402307409</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.75187831227518</v>
+        <v>7.751825160059377</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755773885309038</v>
+        <v>7.755614325132644</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.748300407949445</v>
+        <v>7.748021316507007</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.735178025261376</v>
+        <v>7.736417790311361</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.715249368429416</v>
+        <v>7.716953225713851</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.706754020562745</v>
+        <v>7.70906933559527</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.703728097989565</v>
+        <v>7.70708749090564</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.701956066839506</v>
+        <v>7.706309808944509</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.701311785792994</v>
+        <v>7.706865770991256</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.704142787278256</v>
+        <v>7.71099917005755</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.729226059493289</v>
+        <v>7.737260209596453</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.786079994235669</v>
+        <v>7.794120001433593</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.812132729694132</v>
+        <v>7.822899008462537</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.840856243866162</v>
+        <v>7.853233742202223</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.897947119817115</v>
+        <v>7.910236028929106</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.917483055487681</v>
+        <v>7.933614764698633</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.99987055548768</v>
+        <v>8.036386520431371</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370217515012815</v>
+        <v>8.370215554210436</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367989429407679</v>
+        <v>8.367991085588484</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394475893201237</v>
+        <v>8.394472554536639</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410752675451226</v>
+        <v>8.410751048053122</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199516262028</v>
+        <v>8.424199604094031</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428444502496474</v>
+        <v>8.428446092845286</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427232431942315</v>
+        <v>8.427235513120715</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431698916637421</v>
+        <v>8.431703810486937</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429835911721719</v>
+        <v>8.429852079564212</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439824444349773</v>
+        <v>8.439842087831639</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446350255400002</v>
+        <v>8.446369318401626</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439487237412111</v>
+        <v>8.439506141480603</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419317122616473</v>
+        <v>8.41933747854427</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401685312082998</v>
+        <v>8.401712417052202</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373831117734536</v>
+        <v>8.373854894972698</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336211068766765</v>
+        <v>8.336237127655581</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.280964089650418</v>
+        <v>8.281000239929323</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226529763707999</v>
+        <v>8.226568618454124</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173590617367342</v>
+        <v>8.173611404993137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130489834301644</v>
+        <v>8.130502834260538</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133208887097394</v>
+        <v>8.133205207229935</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18553606935923</v>
+        <v>8.185518829711079</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216790077438633</v>
+        <v>8.216736783606946</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200864536013036</v>
+        <v>8.200796968908101</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172149804507802</v>
+        <v>8.172076471640777</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127570224283414</v>
+        <v>8.127501168084155</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104580167569541</v>
+        <v>8.104523590975155</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115400135229109</v>
+        <v>8.115356946599272</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164072706463649</v>
+        <v>8.164071815603062</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192377799776111</v>
+        <v>8.192389662104134</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173281998957005</v>
+        <v>8.173307238253123</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197875287105198</v>
+        <v>8.197938808239044</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201159969764188</v>
+        <v>8.20128427206156</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23264201007569</v>
+        <v>8.232788443670758</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.323389959329548</v>
+        <v>8.323584040109974</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281598324711094</v>
+        <v>8.28170566686906</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28336674843451</v>
+        <v>8.283515032582901</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266853296954119</v>
+        <v>8.266995604654916</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.277623880851277</v>
+        <v>8.277789103698099</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.312731801211321</v>
+        <v>8.312942290841107</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.333642189137068</v>
+        <v>8.333873482437465</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.240623331782963</v>
+        <v>8.240861670724275</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.150402204365417</v>
+        <v>8.150607747553297</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057307587790369</v>
+        <v>8.057441668251879</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.012951263938239</v>
+        <v>8.013065667609354</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968246899392867</v>
+        <v>7.968305028730452</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942471106625829</v>
+        <v>7.942510022708925</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948416267808121</v>
+        <v>7.948496052932665</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.9152976824415</v>
+        <v>7.91533408608931</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887857701156628</v>
+        <v>7.88787418861046</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872818899783469</v>
+        <v>7.872847395110345</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893468725036989</v>
+        <v>7.893556642242928</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.865912752519915</v>
+        <v>7.86603932168367</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812696366467416</v>
+        <v>7.812847810272162</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772227334946974</v>
+        <v>7.772380552674566</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.751813122152091</v>
+        <v>7.75192044112098</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749883402307409</v>
+        <v>7.749904832583377</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751825160059377</v>
+        <v>7.751773400084595</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755614325132644</v>
+        <v>7.755458347734539</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.748021316507007</v>
+        <v>7.747747929859377</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.736417790311361</v>
+        <v>7.738388698660274</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.716953225713851</v>
+        <v>7.719467382738509</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.70906933559527</v>
+        <v>7.712131569408045</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.70708749090564</v>
+        <v>7.711143241274846</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.706309808944509</v>
+        <v>7.711268343275306</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.706865770991256</v>
+        <v>7.71289659862383</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.71099917005755</v>
+        <v>7.718196208994988</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.737260209596453</v>
+        <v>7.745500775056437</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.794120001433593</v>
+        <v>7.802278785182026</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.822899008462537</v>
+        <v>7.833246256015284</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.853233742202223</v>
+        <v>7.864766371266631</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.910236028929106</v>
+        <v>7.921227295238806</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.933614764698633</v>
+        <v>7.946802560673069</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.036386520431371</v>
+        <v>8.03991334547182</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370215554210436</v>
+        <v>8.370213636029105</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367991085588484</v>
+        <v>8.367992705342807</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394472554536639</v>
+        <v>8.394469289154872</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410751048053122</v>
+        <v>8.410749456575974</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199604094031</v>
+        <v>8.424199690427216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428446092845286</v>
+        <v>8.428447648936922</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427235513120715</v>
+        <v>8.427238527469051</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431703810486937</v>
+        <v>8.431708597763174</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429852079564212</v>
+        <v>8.429867893766897</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439842087831639</v>
+        <v>8.439859347145504</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446369318401626</v>
+        <v>8.446387966415612</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439506141480603</v>
+        <v>8.439524633974925</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41933747854427</v>
+        <v>8.419357393529616</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401712417052202</v>
+        <v>8.40173893385461</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373854894972698</v>
+        <v>8.373878155609209</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336237127655581</v>
+        <v>8.336262625401506</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281000239929323</v>
+        <v>8.281035614173781</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226568618454124</v>
+        <v>8.226606648563882</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173611404993137</v>
+        <v>8.173631750378386</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130502834260538</v>
+        <v>8.130515559006643</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133205207229935</v>
+        <v>8.133201624786942</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185518829711079</v>
+        <v>8.185501979818113</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216736783606946</v>
+        <v>8.216684640787669</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200796968908101</v>
+        <v>8.200730848716173</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172076471640777</v>
+        <v>8.172004697417131</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127501168084155</v>
+        <v>8.127433562527013</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104523590975155</v>
+        <v>8.104468177811736</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115356946599272</v>
+        <v>8.115314612810241</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164071815603062</v>
+        <v>8.164070882152215</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192389662104134</v>
+        <v>8.192401255667848</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173307238253123</v>
+        <v>8.173331910893136</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.197938808239044</v>
+        <v>8.198000990220486</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.20128427206156</v>
+        <v>8.201405987656379</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.232788443670758</v>
+        <v>8.232931825112168</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.323584040109974</v>
+        <v>8.323774033589885</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.28170566686906</v>
+        <v>8.281810651549115</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283515032582901</v>
+        <v>8.283660068985677</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.266995604654916</v>
+        <v>8.267134739745558</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.277789103698099</v>
+        <v>8.277950654307553</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.312942290841107</v>
+        <v>8.313148131166761</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.333873482437465</v>
+        <v>8.334099705676575</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.240861670724275</v>
+        <v>8.241094880432932</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.150607747553297</v>
+        <v>8.150808919819655</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057441668251879</v>
+        <v>8.057572965296581</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013065667609354</v>
+        <v>8.013177720913145</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968305028730452</v>
+        <v>7.968361972723242</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942510022708925</v>
+        <v>7.942548124982268</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948496052932665</v>
+        <v>7.948574151458747</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91533408608931</v>
+        <v>7.915369663631357</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88787418861046</v>
+        <v>7.887890219366708</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872847395110345</v>
+        <v>7.872875149219157</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893556642242928</v>
+        <v>7.893642603389692</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.86603932168367</v>
+        <v>7.866163137842924</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812847810272162</v>
+        <v>7.812996105076374</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772380552674566</v>
+        <v>7.772530675431895</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.75192044112098</v>
+        <v>7.752025726354241</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749904832583377</v>
+        <v>7.749926129253076</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751773400084595</v>
+        <v>7.751722981282467</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755458347734539</v>
+        <v>7.755305836533577</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.747747929859377</v>
+        <v>7.747480079333924</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.738388698660274</v>
+        <v>7.739683876659299</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.719467382738509</v>
+        <v>7.720983475982022</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.712131569408045</v>
+        <v>7.71378397065142</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.711143241274846</v>
+        <v>7.712379224982</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.711268343275306</v>
+        <v>7.712390496496637</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.71289659862383</v>
+        <v>7.713799208551395</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.718196208994988</v>
+        <v>7.718719902526294</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.745500775056437</v>
+        <v>7.744929947668115</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.802278785182026</v>
+        <v>7.799169751544119</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.833246256015284</v>
+        <v>7.827524512384195</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.864766371266631</v>
+        <v>7.855726201326947</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.921227295238806</v>
+        <v>7.90486147321141</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.946802560673069</v>
+        <v>7.918749781958208</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.03991334547182</v>
+        <v>7.960807860333272</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370213636029105</v>
+        <v>8.370211759094161</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367992705342807</v>
+        <v>8.367994289859086</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394469289154872</v>
+        <v>8.394466094669992</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410749456575974</v>
+        <v>8.41074789984399</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199690427216</v>
+        <v>8.42419977529689</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428447648936922</v>
+        <v>8.428449171866275</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427238527469051</v>
+        <v>8.42724147713797</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431708597763174</v>
+        <v>8.4317132819093</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429867893766897</v>
+        <v>8.429883365803498</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439859347145504</v>
+        <v>8.439876234701282</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446387966415612</v>
+        <v>8.446406212844577</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439524633974925</v>
+        <v>8.439542728188901</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419357393529616</v>
+        <v>8.419376881741638</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40173893385461</v>
+        <v>8.40176488142232</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373878155609209</v>
+        <v>8.373900916292643</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336262625401506</v>
+        <v>8.336287579928953</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281035614173781</v>
+        <v>8.281070237092141</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226606648563882</v>
+        <v>8.226643879983207</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173631750378386</v>
+        <v>8.173651667473912</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130515559006643</v>
+        <v>8.130528017180785</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133201624786942</v>
+        <v>8.133198136076789</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185501979818113</v>
+        <v>8.185485506648959</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216684640787669</v>
+        <v>8.216633612127801</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200730848716173</v>
+        <v>8.200666129518915</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.172004697417131</v>
+        <v>8.171934432757498</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127433562527013</v>
+        <v>8.127367362494006</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104468177811736</v>
+        <v>8.104413892719414</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115314612810241</v>
+        <v>8.115273108994234</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164070882152215</v>
+        <v>8.164069909426368</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192401255667848</v>
+        <v>8.192412589412148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173331910893136</v>
+        <v>8.173356035643216</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198000990220486</v>
+        <v>8.198061874798018</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201405987656379</v>
+        <v>8.201525196241157</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.232931825112168</v>
+        <v>8.233072248585632</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.323774033589885</v>
+        <v>8.323960067280964</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281810651549115</v>
+        <v>8.281913355510632</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283660068985677</v>
+        <v>8.283801963066988</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267134739745558</v>
+        <v>8.267270806909574</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.277950654307553</v>
+        <v>8.278108653492964</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.313148131166761</v>
+        <v>8.31334947418882</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.334099705676575</v>
+        <v>8.334321023450741</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.241094880432932</v>
+        <v>8.241323124395636</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.150808919819655</v>
+        <v>8.151005858757919</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057572965296581</v>
+        <v>8.057701564368237</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013177720913145</v>
+        <v>8.013287495250754</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968361972723242</v>
+        <v>7.968417767158018</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942548124982268</v>
+        <v>7.942585438718147</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948574151458747</v>
+        <v>7.948650616270564</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915369663631357</v>
+        <v>7.915404442800027</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887890219366708</v>
+        <v>7.887905811210508</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872875149219157</v>
+        <v>7.872902189740233</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893642603389692</v>
+        <v>7.893726672845056</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866163137842924</v>
+        <v>7.866284289607039</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.812996105076374</v>
+        <v>7.813141347488124</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772530675431895</v>
+        <v>7.772677795197401</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752025726354241</v>
+        <v>7.752129033813987</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749926129253076</v>
+        <v>7.74994728664961</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751722981282467</v>
+        <v>7.751673854955223</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755305836533577</v>
+        <v>7.75515667984401</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.747480079333924</v>
+        <v>7.747217602650189</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.739683876659299</v>
+        <v>7.740923315343876</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.720983475982022</v>
+        <v>7.722566112719235</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.71378397065142</v>
+        <v>7.71581553416179</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.712379224982</v>
+        <v>7.715385730257207</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.712390496496637</v>
+        <v>7.716462107000027</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.713799208551395</v>
+        <v>7.71886188848033</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.718719902526294</v>
+        <v>7.724718790793547</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.744929947668115</v>
+        <v>7.752121484572724</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.799169751544119</v>
+        <v>7.807519892741813</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.827524512384195</v>
+        <v>7.834455563759761</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.855726201326947</v>
+        <v>7.865291878348388</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.90486147321141</v>
+        <v>7.916667635664852</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.918749781958208</v>
+        <v>7.93677500318608</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.960807860333272</v>
+        <v>7.990860532889023</v>
       </c>
     </row>
   </sheetData>
